--- a/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
+++ b/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <color theme="1"/>
@@ -62,6 +62,11 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -229,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -287,7 +292,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -296,7 +302,7 @@
     <xf numFmtId="0" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6566,21 +6572,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6620,1578 +6629,1879 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="37" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="37" t="inlineStr">
+        <is>
+          <t>Самовыкуп: платим цену с СПП (покупатель), получаем выплату Ozon с цены продавца (СПП финансирует Ozon), товар возвращается на склад → теряем только сборы Ozon сверх компенсации СПП.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="48" customHeight="1">
+      <c r="A7" s="38" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="B6" s="37" t="inlineStr">
+      <c r="B7" s="38" t="inlineStr">
         <is>
           <t>Отзывов, шт</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="C7" s="38" t="inlineStr">
         <is>
           <t>Отзывы, ₽</t>
         </is>
       </c>
-      <c r="D6" s="37" t="inlineStr">
+      <c r="D7" s="38" t="inlineStr">
         <is>
           <t>Заказы конкур., шт</t>
         </is>
       </c>
-      <c r="E6" s="37" t="inlineStr">
+      <c r="E7" s="38" t="inlineStr">
         <is>
           <t>Самовыкупов, шт</t>
         </is>
       </c>
-      <c r="F6" s="37" t="inlineStr">
-        <is>
-          <t>Безвозврат / самовыкуп, ₽</t>
-        </is>
-      </c>
-      <c r="G6" s="37" t="inlineStr">
+      <c r="F7" s="38" t="inlineStr">
+        <is>
+          <t>Цена выкупа (с СПП), ₽</t>
+        </is>
+      </c>
+      <c r="G7" s="38" t="inlineStr">
+        <is>
+          <t>Сборы Ozon / выкуп, ₽</t>
+        </is>
+      </c>
+      <c r="H7" s="38" t="inlineStr">
+        <is>
+          <t>Компенсация СПП, ₽</t>
+        </is>
+      </c>
+      <c r="I7" s="38" t="inlineStr">
+        <is>
+          <t>Безвозврат / выкуп, ₽</t>
+        </is>
+      </c>
+      <c r="J7" s="38" t="inlineStr">
         <is>
           <t>Самовыкупы, ₽</t>
         </is>
       </c>
-      <c r="H6" s="37" t="inlineStr">
+      <c r="K7" s="38" t="inlineStr">
         <is>
           <t>Расходы 1-й мес, ₽</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
+      <c r="L7" s="38" t="inlineStr">
         <is>
           <t>Продаж/мес (со 2-го), шт</t>
         </is>
       </c>
-      <c r="J6" s="37" t="inlineStr">
+      <c r="M7" s="38" t="inlineStr">
         <is>
           <t>Маржа/шт, ₽</t>
         </is>
       </c>
-      <c r="K6" s="37" t="inlineStr">
+      <c r="N7" s="38" t="inlineStr">
         <is>
           <t>Прибыль/мес (со 2-го), ₽</t>
         </is>
       </c>
-      <c r="L6" s="37" t="inlineStr">
+      <c r="O7" s="38" t="inlineStr">
         <is>
           <t>Окупаемость, мес</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="38">
+    <row r="8">
+      <c r="A8" s="39">
         <f>'Юнитка FBO'!A13</f>
         <v/>
       </c>
-      <c r="B7" s="39">
+      <c r="B8" s="40">
         <f>'Юнитка FBO'!C13</f>
         <v/>
       </c>
-      <c r="C7" s="39">
-        <f>B7*$B$2</f>
-        <v/>
-      </c>
-      <c r="D7" s="39">
+      <c r="C8" s="40">
+        <f>B8*$B$2</f>
+        <v/>
+      </c>
+      <c r="D8" s="40">
         <f>'Юнитка FBO'!E13</f>
         <v/>
       </c>
-      <c r="E7" s="39">
-        <f>ROUND(D7*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F7" s="39">
+      <c r="E8" s="40">
+        <f>ROUND(D8*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="40">
+        <f>'Юнитка FBO'!I13</f>
+        <v/>
+      </c>
+      <c r="G8" s="40">
         <f>'Юнитка FBO'!K13+'Юнитка FBO'!N13+'Юнитка FBO'!O13+'Юнитка FBO'!P13+'Юнитка FBO'!Q13+'Юнитка FBO'!R13+'Юнитка FBO'!S13+'Юнитка FBO'!V13+'Юнитка FBO'!X13+'Юнитка FBO'!Y13+'Юнитка FBO'!AK13</f>
         <v/>
       </c>
-      <c r="G7" s="39">
-        <f>E7*F7</f>
-        <v/>
-      </c>
-      <c r="H7" s="39">
-        <f>C7+G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="39">
-        <f>ROUND(D7*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="39">
+      <c r="H8" s="40">
+        <f>'Юнитка FBO'!G13-'Юнитка FBO'!I13</f>
+        <v/>
+      </c>
+      <c r="I8" s="40">
+        <f>MAX(0,G8-H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="40">
+        <f>E8*I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="40">
+        <f>C8+J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="40">
+        <f>ROUND(D8*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="40">
         <f>'Юнитка FBO'!AG13</f>
         <v/>
       </c>
-      <c r="K7" s="39">
-        <f>I7*J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="40">
-        <f>IF(K7&gt;0,H7/K7,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="38">
+      <c r="N8" s="40">
+        <f>L8*M8</f>
+        <v/>
+      </c>
+      <c r="O8" s="41">
+        <f>IF(N8&gt;0,K8/N8,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="39">
         <f>'Юнитка FBO'!A14</f>
         <v/>
       </c>
-      <c r="B8" s="39">
+      <c r="B9" s="40">
         <f>'Юнитка FBO'!C14</f>
         <v/>
       </c>
-      <c r="C8" s="39">
-        <f>B8*$B$2</f>
-        <v/>
-      </c>
-      <c r="D8" s="39">
+      <c r="C9" s="40">
+        <f>B9*$B$2</f>
+        <v/>
+      </c>
+      <c r="D9" s="40">
         <f>'Юнитка FBO'!E14</f>
         <v/>
       </c>
-      <c r="E8" s="39">
-        <f>ROUND(D8*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="39">
+      <c r="E9" s="40">
+        <f>ROUND(D9*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="40">
+        <f>'Юнитка FBO'!I14</f>
+        <v/>
+      </c>
+      <c r="G9" s="40">
         <f>'Юнитка FBO'!K14+'Юнитка FBO'!N14+'Юнитка FBO'!O14+'Юнитка FBO'!P14+'Юнитка FBO'!Q14+'Юнитка FBO'!R14+'Юнитка FBO'!S14+'Юнитка FBO'!V14+'Юнитка FBO'!X14+'Юнитка FBO'!Y14+'Юнитка FBO'!AK14</f>
         <v/>
       </c>
-      <c r="G8" s="39">
-        <f>E8*F8</f>
-        <v/>
-      </c>
-      <c r="H8" s="39">
-        <f>C8+G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="39">
-        <f>ROUND(D8*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="39">
+      <c r="H9" s="40">
+        <f>'Юнитка FBO'!G14-'Юнитка FBO'!I14</f>
+        <v/>
+      </c>
+      <c r="I9" s="40">
+        <f>MAX(0,G9-H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="40">
+        <f>E9*I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="40">
+        <f>C9+J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="40">
+        <f>ROUND(D9*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="40">
         <f>'Юнитка FBO'!AG14</f>
         <v/>
       </c>
-      <c r="K8" s="39">
-        <f>I8*J8</f>
-        <v/>
-      </c>
-      <c r="L8" s="40">
-        <f>IF(K8&gt;0,H8/K8,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="38">
+      <c r="N9" s="40">
+        <f>L9*M9</f>
+        <v/>
+      </c>
+      <c r="O9" s="41">
+        <f>IF(N9&gt;0,K9/N9,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="39">
         <f>'Юнитка FBO'!A15</f>
         <v/>
       </c>
-      <c r="B9" s="39">
+      <c r="B10" s="40">
         <f>'Юнитка FBO'!C15</f>
         <v/>
       </c>
-      <c r="C9" s="39">
-        <f>B9*$B$2</f>
-        <v/>
-      </c>
-      <c r="D9" s="39">
+      <c r="C10" s="40">
+        <f>B10*$B$2</f>
+        <v/>
+      </c>
+      <c r="D10" s="40">
         <f>'Юнитка FBO'!E15</f>
         <v/>
       </c>
-      <c r="E9" s="39">
-        <f>ROUND(D9*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="39">
+      <c r="E10" s="40">
+        <f>ROUND(D10*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="40">
+        <f>'Юнитка FBO'!I15</f>
+        <v/>
+      </c>
+      <c r="G10" s="40">
         <f>'Юнитка FBO'!K15+'Юнитка FBO'!N15+'Юнитка FBO'!O15+'Юнитка FBO'!P15+'Юнитка FBO'!Q15+'Юнитка FBO'!R15+'Юнитка FBO'!S15+'Юнитка FBO'!V15+'Юнитка FBO'!X15+'Юнитка FBO'!Y15+'Юнитка FBO'!AK15</f>
         <v/>
       </c>
-      <c r="G9" s="39">
-        <f>E9*F9</f>
-        <v/>
-      </c>
-      <c r="H9" s="39">
-        <f>C9+G9</f>
-        <v/>
-      </c>
-      <c r="I9" s="39">
-        <f>ROUND(D9*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J9" s="39">
+      <c r="H10" s="40">
+        <f>'Юнитка FBO'!G15-'Юнитка FBO'!I15</f>
+        <v/>
+      </c>
+      <c r="I10" s="40">
+        <f>MAX(0,G10-H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="40">
+        <f>E10*I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="40">
+        <f>C10+J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="40">
+        <f>ROUND(D10*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M10" s="40">
         <f>'Юнитка FBO'!AG15</f>
         <v/>
       </c>
-      <c r="K9" s="39">
-        <f>I9*J9</f>
-        <v/>
-      </c>
-      <c r="L9" s="40">
-        <f>IF(K9&gt;0,H9/K9,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="38">
+      <c r="N10" s="40">
+        <f>L10*M10</f>
+        <v/>
+      </c>
+      <c r="O10" s="41">
+        <f>IF(N10&gt;0,K10/N10,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="39">
         <f>'Юнитка FBO'!A16</f>
         <v/>
       </c>
-      <c r="B10" s="39">
+      <c r="B11" s="40">
         <f>'Юнитка FBO'!C16</f>
         <v/>
       </c>
-      <c r="C10" s="39">
-        <f>B10*$B$2</f>
-        <v/>
-      </c>
-      <c r="D10" s="39">
+      <c r="C11" s="40">
+        <f>B11*$B$2</f>
+        <v/>
+      </c>
+      <c r="D11" s="40">
         <f>'Юнитка FBO'!E16</f>
         <v/>
       </c>
-      <c r="E10" s="39">
-        <f>ROUND(D10*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="39">
+      <c r="E11" s="40">
+        <f>ROUND(D11*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="40">
+        <f>'Юнитка FBO'!I16</f>
+        <v/>
+      </c>
+      <c r="G11" s="40">
         <f>'Юнитка FBO'!K16+'Юнитка FBO'!N16+'Юнитка FBO'!O16+'Юнитка FBO'!P16+'Юнитка FBO'!Q16+'Юнитка FBO'!R16+'Юнитка FBO'!S16+'Юнитка FBO'!V16+'Юнитка FBO'!X16+'Юнитка FBO'!Y16+'Юнитка FBO'!AK16</f>
         <v/>
       </c>
-      <c r="G10" s="39">
-        <f>E10*F10</f>
-        <v/>
-      </c>
-      <c r="H10" s="39">
-        <f>C10+G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="39">
-        <f>ROUND(D10*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="39">
+      <c r="H11" s="40">
+        <f>'Юнитка FBO'!G16-'Юнитка FBO'!I16</f>
+        <v/>
+      </c>
+      <c r="I11" s="40">
+        <f>MAX(0,G11-H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="40">
+        <f>E11*I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="40">
+        <f>C11+J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="40">
+        <f>ROUND(D11*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M11" s="40">
         <f>'Юнитка FBO'!AG16</f>
         <v/>
       </c>
-      <c r="K10" s="39">
-        <f>I10*J10</f>
-        <v/>
-      </c>
-      <c r="L10" s="40">
-        <f>IF(K10&gt;0,H10/K10,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="38">
+      <c r="N11" s="40">
+        <f>L11*M11</f>
+        <v/>
+      </c>
+      <c r="O11" s="41">
+        <f>IF(N11&gt;0,K11/N11,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39">
         <f>'Юнитка FBO'!A17</f>
         <v/>
       </c>
-      <c r="B11" s="39">
+      <c r="B12" s="40">
         <f>'Юнитка FBO'!C17</f>
         <v/>
       </c>
-      <c r="C11" s="39">
-        <f>B11*$B$2</f>
-        <v/>
-      </c>
-      <c r="D11" s="39">
+      <c r="C12" s="40">
+        <f>B12*$B$2</f>
+        <v/>
+      </c>
+      <c r="D12" s="40">
         <f>'Юнитка FBO'!E17</f>
         <v/>
       </c>
-      <c r="E11" s="39">
-        <f>ROUND(D11*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F11" s="39">
+      <c r="E12" s="40">
+        <f>ROUND(D12*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="40">
+        <f>'Юнитка FBO'!I17</f>
+        <v/>
+      </c>
+      <c r="G12" s="40">
         <f>'Юнитка FBO'!K17+'Юнитка FBO'!N17+'Юнитка FBO'!O17+'Юнитка FBO'!P17+'Юнитка FBO'!Q17+'Юнитка FBO'!R17+'Юнитка FBO'!S17+'Юнитка FBO'!V17+'Юнитка FBO'!X17+'Юнитка FBO'!Y17+'Юнитка FBO'!AK17</f>
         <v/>
       </c>
-      <c r="G11" s="39">
-        <f>E11*F11</f>
-        <v/>
-      </c>
-      <c r="H11" s="39">
-        <f>C11+G11</f>
-        <v/>
-      </c>
-      <c r="I11" s="39">
-        <f>ROUND(D11*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J11" s="39">
+      <c r="H12" s="40">
+        <f>'Юнитка FBO'!G17-'Юнитка FBO'!I17</f>
+        <v/>
+      </c>
+      <c r="I12" s="40">
+        <f>MAX(0,G12-H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="40">
+        <f>E12*I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="40">
+        <f>C12+J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="40">
+        <f>ROUND(D12*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M12" s="40">
         <f>'Юнитка FBO'!AG17</f>
         <v/>
       </c>
-      <c r="K11" s="39">
-        <f>I11*J11</f>
-        <v/>
-      </c>
-      <c r="L11" s="40">
-        <f>IF(K11&gt;0,H11/K11,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="38">
+      <c r="N12" s="40">
+        <f>L12*M12</f>
+        <v/>
+      </c>
+      <c r="O12" s="41">
+        <f>IF(N12&gt;0,K12/N12,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="39">
         <f>'Юнитка FBO'!A18</f>
         <v/>
       </c>
-      <c r="B12" s="39">
+      <c r="B13" s="40">
         <f>'Юнитка FBO'!C18</f>
         <v/>
       </c>
-      <c r="C12" s="39">
-        <f>B12*$B$2</f>
-        <v/>
-      </c>
-      <c r="D12" s="39">
+      <c r="C13" s="40">
+        <f>B13*$B$2</f>
+        <v/>
+      </c>
+      <c r="D13" s="40">
         <f>'Юнитка FBO'!E18</f>
         <v/>
       </c>
-      <c r="E12" s="39">
-        <f>ROUND(D12*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F12" s="39">
+      <c r="E13" s="40">
+        <f>ROUND(D13*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="40">
+        <f>'Юнитка FBO'!I18</f>
+        <v/>
+      </c>
+      <c r="G13" s="40">
         <f>'Юнитка FBO'!K18+'Юнитка FBO'!N18+'Юнитка FBO'!O18+'Юнитка FBO'!P18+'Юнитка FBO'!Q18+'Юнитка FBO'!R18+'Юнитка FBO'!S18+'Юнитка FBO'!V18+'Юнитка FBO'!X18+'Юнитка FBO'!Y18+'Юнитка FBO'!AK18</f>
         <v/>
       </c>
-      <c r="G12" s="39">
-        <f>E12*F12</f>
-        <v/>
-      </c>
-      <c r="H12" s="39">
-        <f>C12+G12</f>
-        <v/>
-      </c>
-      <c r="I12" s="39">
-        <f>ROUND(D12*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J12" s="39">
+      <c r="H13" s="40">
+        <f>'Юнитка FBO'!G18-'Юнитка FBO'!I18</f>
+        <v/>
+      </c>
+      <c r="I13" s="40">
+        <f>MAX(0,G13-H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="40">
+        <f>E13*I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="40">
+        <f>C13+J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="40">
+        <f>ROUND(D13*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="40">
         <f>'Юнитка FBO'!AG18</f>
         <v/>
       </c>
-      <c r="K12" s="39">
-        <f>I12*J12</f>
-        <v/>
-      </c>
-      <c r="L12" s="40">
-        <f>IF(K12&gt;0,H12/K12,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="38">
+      <c r="N13" s="40">
+        <f>L13*M13</f>
+        <v/>
+      </c>
+      <c r="O13" s="41">
+        <f>IF(N13&gt;0,K13/N13,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="39">
         <f>'Юнитка FBO'!A19</f>
         <v/>
       </c>
-      <c r="B13" s="39">
+      <c r="B14" s="40">
         <f>'Юнитка FBO'!C19</f>
         <v/>
       </c>
-      <c r="C13" s="39">
-        <f>B13*$B$2</f>
-        <v/>
-      </c>
-      <c r="D13" s="39">
+      <c r="C14" s="40">
+        <f>B14*$B$2</f>
+        <v/>
+      </c>
+      <c r="D14" s="40">
         <f>'Юнитка FBO'!E19</f>
         <v/>
       </c>
-      <c r="E13" s="39">
-        <f>ROUND(D13*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F13" s="39">
+      <c r="E14" s="40">
+        <f>ROUND(D14*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="40">
+        <f>'Юнитка FBO'!I19</f>
+        <v/>
+      </c>
+      <c r="G14" s="40">
         <f>'Юнитка FBO'!K19+'Юнитка FBO'!N19+'Юнитка FBO'!O19+'Юнитка FBO'!P19+'Юнитка FBO'!Q19+'Юнитка FBO'!R19+'Юнитка FBO'!S19+'Юнитка FBO'!V19+'Юнитка FBO'!X19+'Юнитка FBO'!Y19+'Юнитка FBO'!AK19</f>
         <v/>
       </c>
-      <c r="G13" s="39">
-        <f>E13*F13</f>
-        <v/>
-      </c>
-      <c r="H13" s="39">
-        <f>C13+G13</f>
-        <v/>
-      </c>
-      <c r="I13" s="39">
-        <f>ROUND(D13*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J13" s="39">
+      <c r="H14" s="40">
+        <f>'Юнитка FBO'!G19-'Юнитка FBO'!I19</f>
+        <v/>
+      </c>
+      <c r="I14" s="40">
+        <f>MAX(0,G14-H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="40">
+        <f>E14*I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="40">
+        <f>C14+J14</f>
+        <v/>
+      </c>
+      <c r="L14" s="40">
+        <f>ROUND(D14*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="40">
         <f>'Юнитка FBO'!AG19</f>
         <v/>
       </c>
-      <c r="K13" s="39">
-        <f>I13*J13</f>
-        <v/>
-      </c>
-      <c r="L13" s="40">
-        <f>IF(K13&gt;0,H13/K13,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="38">
+      <c r="N14" s="40">
+        <f>L14*M14</f>
+        <v/>
+      </c>
+      <c r="O14" s="41">
+        <f>IF(N14&gt;0,K14/N14,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="39">
         <f>'Юнитка FBO'!A20</f>
         <v/>
       </c>
-      <c r="B14" s="39">
+      <c r="B15" s="40">
         <f>'Юнитка FBO'!C20</f>
         <v/>
       </c>
-      <c r="C14" s="39">
-        <f>B14*$B$2</f>
-        <v/>
-      </c>
-      <c r="D14" s="39">
+      <c r="C15" s="40">
+        <f>B15*$B$2</f>
+        <v/>
+      </c>
+      <c r="D15" s="40">
         <f>'Юнитка FBO'!E20</f>
         <v/>
       </c>
-      <c r="E14" s="39">
-        <f>ROUND(D14*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="39">
+      <c r="E15" s="40">
+        <f>ROUND(D15*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="40">
+        <f>'Юнитка FBO'!I20</f>
+        <v/>
+      </c>
+      <c r="G15" s="40">
         <f>'Юнитка FBO'!K20+'Юнитка FBO'!N20+'Юнитка FBO'!O20+'Юнитка FBO'!P20+'Юнитка FBO'!Q20+'Юнитка FBO'!R20+'Юнитка FBO'!S20+'Юнитка FBO'!V20+'Юнитка FBO'!X20+'Юнитка FBO'!Y20+'Юнитка FBO'!AK20</f>
         <v/>
       </c>
-      <c r="G14" s="39">
-        <f>E14*F14</f>
-        <v/>
-      </c>
-      <c r="H14" s="39">
-        <f>C14+G14</f>
-        <v/>
-      </c>
-      <c r="I14" s="39">
-        <f>ROUND(D14*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J14" s="39">
+      <c r="H15" s="40">
+        <f>'Юнитка FBO'!G20-'Юнитка FBO'!I20</f>
+        <v/>
+      </c>
+      <c r="I15" s="40">
+        <f>MAX(0,G15-H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="40">
+        <f>E15*I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="40">
+        <f>C15+J15</f>
+        <v/>
+      </c>
+      <c r="L15" s="40">
+        <f>ROUND(D15*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M15" s="40">
         <f>'Юнитка FBO'!AG20</f>
         <v/>
       </c>
-      <c r="K14" s="39">
-        <f>I14*J14</f>
-        <v/>
-      </c>
-      <c r="L14" s="40">
-        <f>IF(K14&gt;0,H14/K14,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="38">
+      <c r="N15" s="40">
+        <f>L15*M15</f>
+        <v/>
+      </c>
+      <c r="O15" s="41">
+        <f>IF(N15&gt;0,K15/N15,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39">
         <f>'Юнитка FBO'!A21</f>
         <v/>
       </c>
-      <c r="B15" s="39">
+      <c r="B16" s="40">
         <f>'Юнитка FBO'!C21</f>
         <v/>
       </c>
-      <c r="C15" s="39">
-        <f>B15*$B$2</f>
-        <v/>
-      </c>
-      <c r="D15" s="39">
+      <c r="C16" s="40">
+        <f>B16*$B$2</f>
+        <v/>
+      </c>
+      <c r="D16" s="40">
         <f>'Юнитка FBO'!E21</f>
         <v/>
       </c>
-      <c r="E15" s="39">
-        <f>ROUND(D15*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F15" s="39">
+      <c r="E16" s="40">
+        <f>ROUND(D16*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="40">
+        <f>'Юнитка FBO'!I21</f>
+        <v/>
+      </c>
+      <c r="G16" s="40">
         <f>'Юнитка FBO'!K21+'Юнитка FBO'!N21+'Юнитка FBO'!O21+'Юнитка FBO'!P21+'Юнитка FBO'!Q21+'Юнитка FBO'!R21+'Юнитка FBO'!S21+'Юнитка FBO'!V21+'Юнитка FBO'!X21+'Юнитка FBO'!Y21+'Юнитка FBO'!AK21</f>
         <v/>
       </c>
-      <c r="G15" s="39">
-        <f>E15*F15</f>
-        <v/>
-      </c>
-      <c r="H15" s="39">
-        <f>C15+G15</f>
-        <v/>
-      </c>
-      <c r="I15" s="39">
-        <f>ROUND(D15*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J15" s="39">
+      <c r="H16" s="40">
+        <f>'Юнитка FBO'!G21-'Юнитка FBO'!I21</f>
+        <v/>
+      </c>
+      <c r="I16" s="40">
+        <f>MAX(0,G16-H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="40">
+        <f>E16*I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="40">
+        <f>C16+J16</f>
+        <v/>
+      </c>
+      <c r="L16" s="40">
+        <f>ROUND(D16*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M16" s="40">
         <f>'Юнитка FBO'!AG21</f>
         <v/>
       </c>
-      <c r="K15" s="39">
-        <f>I15*J15</f>
-        <v/>
-      </c>
-      <c r="L15" s="40">
-        <f>IF(K15&gt;0,H15/K15,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="38">
+      <c r="N16" s="40">
+        <f>L16*M16</f>
+        <v/>
+      </c>
+      <c r="O16" s="41">
+        <f>IF(N16&gt;0,K16/N16,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="39">
         <f>'Юнитка FBO'!A22</f>
         <v/>
       </c>
-      <c r="B16" s="39">
+      <c r="B17" s="40">
         <f>'Юнитка FBO'!C22</f>
         <v/>
       </c>
-      <c r="C16" s="39">
-        <f>B16*$B$2</f>
-        <v/>
-      </c>
-      <c r="D16" s="39">
+      <c r="C17" s="40">
+        <f>B17*$B$2</f>
+        <v/>
+      </c>
+      <c r="D17" s="40">
         <f>'Юнитка FBO'!E22</f>
         <v/>
       </c>
-      <c r="E16" s="39">
-        <f>ROUND(D16*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F16" s="39">
+      <c r="E17" s="40">
+        <f>ROUND(D17*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="40">
+        <f>'Юнитка FBO'!I22</f>
+        <v/>
+      </c>
+      <c r="G17" s="40">
         <f>'Юнитка FBO'!K22+'Юнитка FBO'!N22+'Юнитка FBO'!O22+'Юнитка FBO'!P22+'Юнитка FBO'!Q22+'Юнитка FBO'!R22+'Юнитка FBO'!S22+'Юнитка FBO'!V22+'Юнитка FBO'!X22+'Юнитка FBO'!Y22+'Юнитка FBO'!AK22</f>
         <v/>
       </c>
-      <c r="G16" s="39">
-        <f>E16*F16</f>
-        <v/>
-      </c>
-      <c r="H16" s="39">
-        <f>C16+G16</f>
-        <v/>
-      </c>
-      <c r="I16" s="39">
-        <f>ROUND(D16*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J16" s="39">
+      <c r="H17" s="40">
+        <f>'Юнитка FBO'!G22-'Юнитка FBO'!I22</f>
+        <v/>
+      </c>
+      <c r="I17" s="40">
+        <f>MAX(0,G17-H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="40">
+        <f>E17*I17</f>
+        <v/>
+      </c>
+      <c r="K17" s="40">
+        <f>C17+J17</f>
+        <v/>
+      </c>
+      <c r="L17" s="40">
+        <f>ROUND(D17*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M17" s="40">
         <f>'Юнитка FBO'!AG22</f>
         <v/>
       </c>
-      <c r="K16" s="39">
-        <f>I16*J16</f>
-        <v/>
-      </c>
-      <c r="L16" s="40">
-        <f>IF(K16&gt;0,H16/K16,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="38">
+      <c r="N17" s="40">
+        <f>L17*M17</f>
+        <v/>
+      </c>
+      <c r="O17" s="41">
+        <f>IF(N17&gt;0,K17/N17,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39">
         <f>'Юнитка FBO'!A23</f>
         <v/>
       </c>
-      <c r="B17" s="39">
+      <c r="B18" s="40">
         <f>'Юнитка FBO'!C23</f>
         <v/>
       </c>
-      <c r="C17" s="39">
-        <f>B17*$B$2</f>
-        <v/>
-      </c>
-      <c r="D17" s="39">
+      <c r="C18" s="40">
+        <f>B18*$B$2</f>
+        <v/>
+      </c>
+      <c r="D18" s="40">
         <f>'Юнитка FBO'!E23</f>
         <v/>
       </c>
-      <c r="E17" s="39">
-        <f>ROUND(D17*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F17" s="39">
+      <c r="E18" s="40">
+        <f>ROUND(D18*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="40">
+        <f>'Юнитка FBO'!I23</f>
+        <v/>
+      </c>
+      <c r="G18" s="40">
         <f>'Юнитка FBO'!K23+'Юнитка FBO'!N23+'Юнитка FBO'!O23+'Юнитка FBO'!P23+'Юнитка FBO'!Q23+'Юнитка FBO'!R23+'Юнитка FBO'!S23+'Юнитка FBO'!V23+'Юнитка FBO'!X23+'Юнитка FBO'!Y23+'Юнитка FBO'!AK23</f>
         <v/>
       </c>
-      <c r="G17" s="39">
-        <f>E17*F17</f>
-        <v/>
-      </c>
-      <c r="H17" s="39">
-        <f>C17+G17</f>
-        <v/>
-      </c>
-      <c r="I17" s="39">
-        <f>ROUND(D17*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J17" s="39">
+      <c r="H18" s="40">
+        <f>'Юнитка FBO'!G23-'Юнитка FBO'!I23</f>
+        <v/>
+      </c>
+      <c r="I18" s="40">
+        <f>MAX(0,G18-H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="40">
+        <f>E18*I18</f>
+        <v/>
+      </c>
+      <c r="K18" s="40">
+        <f>C18+J18</f>
+        <v/>
+      </c>
+      <c r="L18" s="40">
+        <f>ROUND(D18*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M18" s="40">
         <f>'Юнитка FBO'!AG23</f>
         <v/>
       </c>
-      <c r="K17" s="39">
-        <f>I17*J17</f>
-        <v/>
-      </c>
-      <c r="L17" s="40">
-        <f>IF(K17&gt;0,H17/K17,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="38">
+      <c r="N18" s="40">
+        <f>L18*M18</f>
+        <v/>
+      </c>
+      <c r="O18" s="41">
+        <f>IF(N18&gt;0,K18/N18,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="39">
         <f>'Юнитка FBO'!A24</f>
         <v/>
       </c>
-      <c r="B18" s="39">
+      <c r="B19" s="40">
         <f>'Юнитка FBO'!C24</f>
         <v/>
       </c>
-      <c r="C18" s="39">
-        <f>B18*$B$2</f>
-        <v/>
-      </c>
-      <c r="D18" s="39">
+      <c r="C19" s="40">
+        <f>B19*$B$2</f>
+        <v/>
+      </c>
+      <c r="D19" s="40">
         <f>'Юнитка FBO'!E24</f>
         <v/>
       </c>
-      <c r="E18" s="39">
-        <f>ROUND(D18*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F18" s="39">
+      <c r="E19" s="40">
+        <f>ROUND(D19*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="40">
+        <f>'Юнитка FBO'!I24</f>
+        <v/>
+      </c>
+      <c r="G19" s="40">
         <f>'Юнитка FBO'!K24+'Юнитка FBO'!N24+'Юнитка FBO'!O24+'Юнитка FBO'!P24+'Юнитка FBO'!Q24+'Юнитка FBO'!R24+'Юнитка FBO'!S24+'Юнитка FBO'!V24+'Юнитка FBO'!X24+'Юнитка FBO'!Y24+'Юнитка FBO'!AK24</f>
         <v/>
       </c>
-      <c r="G18" s="39">
-        <f>E18*F18</f>
-        <v/>
-      </c>
-      <c r="H18" s="39">
-        <f>C18+G18</f>
-        <v/>
-      </c>
-      <c r="I18" s="39">
-        <f>ROUND(D18*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J18" s="39">
+      <c r="H19" s="40">
+        <f>'Юнитка FBO'!G24-'Юнитка FBO'!I24</f>
+        <v/>
+      </c>
+      <c r="I19" s="40">
+        <f>MAX(0,G19-H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="40">
+        <f>E19*I19</f>
+        <v/>
+      </c>
+      <c r="K19" s="40">
+        <f>C19+J19</f>
+        <v/>
+      </c>
+      <c r="L19" s="40">
+        <f>ROUND(D19*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M19" s="40">
         <f>'Юнитка FBO'!AG24</f>
         <v/>
       </c>
-      <c r="K18" s="39">
-        <f>I18*J18</f>
-        <v/>
-      </c>
-      <c r="L18" s="40">
-        <f>IF(K18&gt;0,H18/K18,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="38">
+      <c r="N19" s="40">
+        <f>L19*M19</f>
+        <v/>
+      </c>
+      <c r="O19" s="41">
+        <f>IF(N19&gt;0,K19/N19,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="39">
         <f>'Юнитка FBO'!A25</f>
         <v/>
       </c>
-      <c r="B19" s="39">
+      <c r="B20" s="40">
         <f>'Юнитка FBO'!C25</f>
         <v/>
       </c>
-      <c r="C19" s="39">
-        <f>B19*$B$2</f>
-        <v/>
-      </c>
-      <c r="D19" s="39">
+      <c r="C20" s="40">
+        <f>B20*$B$2</f>
+        <v/>
+      </c>
+      <c r="D20" s="40">
         <f>'Юнитка FBO'!E25</f>
         <v/>
       </c>
-      <c r="E19" s="39">
-        <f>ROUND(D19*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F19" s="39">
+      <c r="E20" s="40">
+        <f>ROUND(D20*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="40">
+        <f>'Юнитка FBO'!I25</f>
+        <v/>
+      </c>
+      <c r="G20" s="40">
         <f>'Юнитка FBO'!K25+'Юнитка FBO'!N25+'Юнитка FBO'!O25+'Юнитка FBO'!P25+'Юнитка FBO'!Q25+'Юнитка FBO'!R25+'Юнитка FBO'!S25+'Юнитка FBO'!V25+'Юнитка FBO'!X25+'Юнитка FBO'!Y25+'Юнитка FBO'!AK25</f>
         <v/>
       </c>
-      <c r="G19" s="39">
-        <f>E19*F19</f>
-        <v/>
-      </c>
-      <c r="H19" s="39">
-        <f>C19+G19</f>
-        <v/>
-      </c>
-      <c r="I19" s="39">
-        <f>ROUND(D19*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J19" s="39">
+      <c r="H20" s="40">
+        <f>'Юнитка FBO'!G25-'Юнитка FBO'!I25</f>
+        <v/>
+      </c>
+      <c r="I20" s="40">
+        <f>MAX(0,G20-H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="40">
+        <f>E20*I20</f>
+        <v/>
+      </c>
+      <c r="K20" s="40">
+        <f>C20+J20</f>
+        <v/>
+      </c>
+      <c r="L20" s="40">
+        <f>ROUND(D20*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M20" s="40">
         <f>'Юнитка FBO'!AG25</f>
         <v/>
       </c>
-      <c r="K19" s="39">
-        <f>I19*J19</f>
-        <v/>
-      </c>
-      <c r="L19" s="40">
-        <f>IF(K19&gt;0,H19/K19,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="38">
+      <c r="N20" s="40">
+        <f>L20*M20</f>
+        <v/>
+      </c>
+      <c r="O20" s="41">
+        <f>IF(N20&gt;0,K20/N20,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="39">
         <f>'Юнитка FBO'!A26</f>
         <v/>
       </c>
-      <c r="B20" s="39">
+      <c r="B21" s="40">
         <f>'Юнитка FBO'!C26</f>
         <v/>
       </c>
-      <c r="C20" s="39">
-        <f>B20*$B$2</f>
-        <v/>
-      </c>
-      <c r="D20" s="39">
+      <c r="C21" s="40">
+        <f>B21*$B$2</f>
+        <v/>
+      </c>
+      <c r="D21" s="40">
         <f>'Юнитка FBO'!E26</f>
         <v/>
       </c>
-      <c r="E20" s="39">
-        <f>ROUND(D20*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F20" s="39">
+      <c r="E21" s="40">
+        <f>ROUND(D21*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="40">
+        <f>'Юнитка FBO'!I26</f>
+        <v/>
+      </c>
+      <c r="G21" s="40">
         <f>'Юнитка FBO'!K26+'Юнитка FBO'!N26+'Юнитка FBO'!O26+'Юнитка FBO'!P26+'Юнитка FBO'!Q26+'Юнитка FBO'!R26+'Юнитка FBO'!S26+'Юнитка FBO'!V26+'Юнитка FBO'!X26+'Юнитка FBO'!Y26+'Юнитка FBO'!AK26</f>
         <v/>
       </c>
-      <c r="G20" s="39">
-        <f>E20*F20</f>
-        <v/>
-      </c>
-      <c r="H20" s="39">
-        <f>C20+G20</f>
-        <v/>
-      </c>
-      <c r="I20" s="39">
-        <f>ROUND(D20*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J20" s="39">
+      <c r="H21" s="40">
+        <f>'Юнитка FBO'!G26-'Юнитка FBO'!I26</f>
+        <v/>
+      </c>
+      <c r="I21" s="40">
+        <f>MAX(0,G21-H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="40">
+        <f>E21*I21</f>
+        <v/>
+      </c>
+      <c r="K21" s="40">
+        <f>C21+J21</f>
+        <v/>
+      </c>
+      <c r="L21" s="40">
+        <f>ROUND(D21*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M21" s="40">
         <f>'Юнитка FBO'!AG26</f>
         <v/>
       </c>
-      <c r="K20" s="39">
-        <f>I20*J20</f>
-        <v/>
-      </c>
-      <c r="L20" s="40">
-        <f>IF(K20&gt;0,H20/K20,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="38">
+      <c r="N21" s="40">
+        <f>L21*M21</f>
+        <v/>
+      </c>
+      <c r="O21" s="41">
+        <f>IF(N21&gt;0,K21/N21,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="39">
         <f>'Юнитка FBO'!A27</f>
         <v/>
       </c>
-      <c r="B21" s="39">
+      <c r="B22" s="40">
         <f>'Юнитка FBO'!C27</f>
         <v/>
       </c>
-      <c r="C21" s="39">
-        <f>B21*$B$2</f>
-        <v/>
-      </c>
-      <c r="D21" s="39">
+      <c r="C22" s="40">
+        <f>B22*$B$2</f>
+        <v/>
+      </c>
+      <c r="D22" s="40">
         <f>'Юнитка FBO'!E27</f>
         <v/>
       </c>
-      <c r="E21" s="39">
-        <f>ROUND(D21*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F21" s="39">
+      <c r="E22" s="40">
+        <f>ROUND(D22*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F22" s="40">
+        <f>'Юнитка FBO'!I27</f>
+        <v/>
+      </c>
+      <c r="G22" s="40">
         <f>'Юнитка FBO'!K27+'Юнитка FBO'!N27+'Юнитка FBO'!O27+'Юнитка FBO'!P27+'Юнитка FBO'!Q27+'Юнитка FBO'!R27+'Юнитка FBO'!S27+'Юнитка FBO'!V27+'Юнитка FBO'!X27+'Юнитка FBO'!Y27+'Юнитка FBO'!AK27</f>
         <v/>
       </c>
-      <c r="G21" s="39">
-        <f>E21*F21</f>
-        <v/>
-      </c>
-      <c r="H21" s="39">
-        <f>C21+G21</f>
-        <v/>
-      </c>
-      <c r="I21" s="39">
-        <f>ROUND(D21*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J21" s="39">
+      <c r="H22" s="40">
+        <f>'Юнитка FBO'!G27-'Юнитка FBO'!I27</f>
+        <v/>
+      </c>
+      <c r="I22" s="40">
+        <f>MAX(0,G22-H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="40">
+        <f>E22*I22</f>
+        <v/>
+      </c>
+      <c r="K22" s="40">
+        <f>C22+J22</f>
+        <v/>
+      </c>
+      <c r="L22" s="40">
+        <f>ROUND(D22*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M22" s="40">
         <f>'Юнитка FBO'!AG27</f>
         <v/>
       </c>
-      <c r="K21" s="39">
-        <f>I21*J21</f>
-        <v/>
-      </c>
-      <c r="L21" s="40">
-        <f>IF(K21&gt;0,H21/K21,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="38">
+      <c r="N22" s="40">
+        <f>L22*M22</f>
+        <v/>
+      </c>
+      <c r="O22" s="41">
+        <f>IF(N22&gt;0,K22/N22,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="39">
         <f>'Юнитка FBO'!A28</f>
         <v/>
       </c>
-      <c r="B22" s="39">
+      <c r="B23" s="40">
         <f>'Юнитка FBO'!C28</f>
         <v/>
       </c>
-      <c r="C22" s="39">
-        <f>B22*$B$2</f>
-        <v/>
-      </c>
-      <c r="D22" s="39">
+      <c r="C23" s="40">
+        <f>B23*$B$2</f>
+        <v/>
+      </c>
+      <c r="D23" s="40">
         <f>'Юнитка FBO'!E28</f>
         <v/>
       </c>
-      <c r="E22" s="39">
-        <f>ROUND(D22*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F22" s="39">
+      <c r="E23" s="40">
+        <f>ROUND(D23*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F23" s="40">
+        <f>'Юнитка FBO'!I28</f>
+        <v/>
+      </c>
+      <c r="G23" s="40">
         <f>'Юнитка FBO'!K28+'Юнитка FBO'!N28+'Юнитка FBO'!O28+'Юнитка FBO'!P28+'Юнитка FBO'!Q28+'Юнитка FBO'!R28+'Юнитка FBO'!S28+'Юнитка FBO'!V28+'Юнитка FBO'!X28+'Юнитка FBO'!Y28+'Юнитка FBO'!AK28</f>
         <v/>
       </c>
-      <c r="G22" s="39">
-        <f>E22*F22</f>
-        <v/>
-      </c>
-      <c r="H22" s="39">
-        <f>C22+G22</f>
-        <v/>
-      </c>
-      <c r="I22" s="39">
-        <f>ROUND(D22*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J22" s="39">
+      <c r="H23" s="40">
+        <f>'Юнитка FBO'!G28-'Юнитка FBO'!I28</f>
+        <v/>
+      </c>
+      <c r="I23" s="40">
+        <f>MAX(0,G23-H23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="40">
+        <f>E23*I23</f>
+        <v/>
+      </c>
+      <c r="K23" s="40">
+        <f>C23+J23</f>
+        <v/>
+      </c>
+      <c r="L23" s="40">
+        <f>ROUND(D23*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M23" s="40">
         <f>'Юнитка FBO'!AG28</f>
         <v/>
       </c>
-      <c r="K22" s="39">
-        <f>I22*J22</f>
-        <v/>
-      </c>
-      <c r="L22" s="40">
-        <f>IF(K22&gt;0,H22/K22,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="38">
+      <c r="N23" s="40">
+        <f>L23*M23</f>
+        <v/>
+      </c>
+      <c r="O23" s="41">
+        <f>IF(N23&gt;0,K23/N23,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39">
         <f>'Юнитка FBO'!A29</f>
         <v/>
       </c>
-      <c r="B23" s="39">
+      <c r="B24" s="40">
         <f>'Юнитка FBO'!C29</f>
         <v/>
       </c>
-      <c r="C23" s="39">
-        <f>B23*$B$2</f>
-        <v/>
-      </c>
-      <c r="D23" s="39">
+      <c r="C24" s="40">
+        <f>B24*$B$2</f>
+        <v/>
+      </c>
+      <c r="D24" s="40">
         <f>'Юнитка FBO'!E29</f>
         <v/>
       </c>
-      <c r="E23" s="39">
-        <f>ROUND(D23*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F23" s="39">
+      <c r="E24" s="40">
+        <f>ROUND(D24*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F24" s="40">
+        <f>'Юнитка FBO'!I29</f>
+        <v/>
+      </c>
+      <c r="G24" s="40">
         <f>'Юнитка FBO'!K29+'Юнитка FBO'!N29+'Юнитка FBO'!O29+'Юнитка FBO'!P29+'Юнитка FBO'!Q29+'Юнитка FBO'!R29+'Юнитка FBO'!S29+'Юнитка FBO'!V29+'Юнитка FBO'!X29+'Юнитка FBO'!Y29+'Юнитка FBO'!AK29</f>
         <v/>
       </c>
-      <c r="G23" s="39">
-        <f>E23*F23</f>
-        <v/>
-      </c>
-      <c r="H23" s="39">
-        <f>C23+G23</f>
-        <v/>
-      </c>
-      <c r="I23" s="39">
-        <f>ROUND(D23*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J23" s="39">
+      <c r="H24" s="40">
+        <f>'Юнитка FBO'!G29-'Юнитка FBO'!I29</f>
+        <v/>
+      </c>
+      <c r="I24" s="40">
+        <f>MAX(0,G24-H24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="40">
+        <f>E24*I24</f>
+        <v/>
+      </c>
+      <c r="K24" s="40">
+        <f>C24+J24</f>
+        <v/>
+      </c>
+      <c r="L24" s="40">
+        <f>ROUND(D24*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M24" s="40">
         <f>'Юнитка FBO'!AG29</f>
         <v/>
       </c>
-      <c r="K23" s="39">
-        <f>I23*J23</f>
-        <v/>
-      </c>
-      <c r="L23" s="40">
-        <f>IF(K23&gt;0,H23/K23,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="38">
+      <c r="N24" s="40">
+        <f>L24*M24</f>
+        <v/>
+      </c>
+      <c r="O24" s="41">
+        <f>IF(N24&gt;0,K24/N24,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39">
         <f>'Юнитка FBO'!A30</f>
         <v/>
       </c>
-      <c r="B24" s="39">
+      <c r="B25" s="40">
         <f>'Юнитка FBO'!C30</f>
         <v/>
       </c>
-      <c r="C24" s="39">
-        <f>B24*$B$2</f>
-        <v/>
-      </c>
-      <c r="D24" s="39">
+      <c r="C25" s="40">
+        <f>B25*$B$2</f>
+        <v/>
+      </c>
+      <c r="D25" s="40">
         <f>'Юнитка FBO'!E30</f>
         <v/>
       </c>
-      <c r="E24" s="39">
-        <f>ROUND(D24*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F24" s="39">
+      <c r="E25" s="40">
+        <f>ROUND(D25*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F25" s="40">
+        <f>'Юнитка FBO'!I30</f>
+        <v/>
+      </c>
+      <c r="G25" s="40">
         <f>'Юнитка FBO'!K30+'Юнитка FBO'!N30+'Юнитка FBO'!O30+'Юнитка FBO'!P30+'Юнитка FBO'!Q30+'Юнитка FBO'!R30+'Юнитка FBO'!S30+'Юнитка FBO'!V30+'Юнитка FBO'!X30+'Юнитка FBO'!Y30+'Юнитка FBO'!AK30</f>
         <v/>
       </c>
-      <c r="G24" s="39">
-        <f>E24*F24</f>
-        <v/>
-      </c>
-      <c r="H24" s="39">
-        <f>C24+G24</f>
-        <v/>
-      </c>
-      <c r="I24" s="39">
-        <f>ROUND(D24*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J24" s="39">
+      <c r="H25" s="40">
+        <f>'Юнитка FBO'!G30-'Юнитка FBO'!I30</f>
+        <v/>
+      </c>
+      <c r="I25" s="40">
+        <f>MAX(0,G25-H25)</f>
+        <v/>
+      </c>
+      <c r="J25" s="40">
+        <f>E25*I25</f>
+        <v/>
+      </c>
+      <c r="K25" s="40">
+        <f>C25+J25</f>
+        <v/>
+      </c>
+      <c r="L25" s="40">
+        <f>ROUND(D25*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M25" s="40">
         <f>'Юнитка FBO'!AG30</f>
         <v/>
       </c>
-      <c r="K24" s="39">
-        <f>I24*J24</f>
-        <v/>
-      </c>
-      <c r="L24" s="40">
-        <f>IF(K24&gt;0,H24/K24,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="38">
+      <c r="N25" s="40">
+        <f>L25*M25</f>
+        <v/>
+      </c>
+      <c r="O25" s="41">
+        <f>IF(N25&gt;0,K25/N25,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="39">
         <f>'Юнитка FBO'!A31</f>
         <v/>
       </c>
-      <c r="B25" s="39">
+      <c r="B26" s="40">
         <f>'Юнитка FBO'!C31</f>
         <v/>
       </c>
-      <c r="C25" s="39">
-        <f>B25*$B$2</f>
-        <v/>
-      </c>
-      <c r="D25" s="39">
+      <c r="C26" s="40">
+        <f>B26*$B$2</f>
+        <v/>
+      </c>
+      <c r="D26" s="40">
         <f>'Юнитка FBO'!E31</f>
         <v/>
       </c>
-      <c r="E25" s="39">
-        <f>ROUND(D25*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F25" s="39">
+      <c r="E26" s="40">
+        <f>ROUND(D26*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F26" s="40">
+        <f>'Юнитка FBO'!I31</f>
+        <v/>
+      </c>
+      <c r="G26" s="40">
         <f>'Юнитка FBO'!K31+'Юнитка FBO'!N31+'Юнитка FBO'!O31+'Юнитка FBO'!P31+'Юнитка FBO'!Q31+'Юнитка FBO'!R31+'Юнитка FBO'!S31+'Юнитка FBO'!V31+'Юнитка FBO'!X31+'Юнитка FBO'!Y31+'Юнитка FBO'!AK31</f>
         <v/>
       </c>
-      <c r="G25" s="39">
-        <f>E25*F25</f>
-        <v/>
-      </c>
-      <c r="H25" s="39">
-        <f>C25+G25</f>
-        <v/>
-      </c>
-      <c r="I25" s="39">
-        <f>ROUND(D25*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J25" s="39">
+      <c r="H26" s="40">
+        <f>'Юнитка FBO'!G31-'Юнитка FBO'!I31</f>
+        <v/>
+      </c>
+      <c r="I26" s="40">
+        <f>MAX(0,G26-H26)</f>
+        <v/>
+      </c>
+      <c r="J26" s="40">
+        <f>E26*I26</f>
+        <v/>
+      </c>
+      <c r="K26" s="40">
+        <f>C26+J26</f>
+        <v/>
+      </c>
+      <c r="L26" s="40">
+        <f>ROUND(D26*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M26" s="40">
         <f>'Юнитка FBO'!AG31</f>
         <v/>
       </c>
-      <c r="K25" s="39">
-        <f>I25*J25</f>
-        <v/>
-      </c>
-      <c r="L25" s="40">
-        <f>IF(K25&gt;0,H25/K25,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="38">
+      <c r="N26" s="40">
+        <f>L26*M26</f>
+        <v/>
+      </c>
+      <c r="O26" s="41">
+        <f>IF(N26&gt;0,K26/N26,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39">
         <f>'Юнитка FBO'!A32</f>
         <v/>
       </c>
-      <c r="B26" s="39">
+      <c r="B27" s="40">
         <f>'Юнитка FBO'!C32</f>
         <v/>
       </c>
-      <c r="C26" s="39">
-        <f>B26*$B$2</f>
-        <v/>
-      </c>
-      <c r="D26" s="39">
+      <c r="C27" s="40">
+        <f>B27*$B$2</f>
+        <v/>
+      </c>
+      <c r="D27" s="40">
         <f>'Юнитка FBO'!E32</f>
         <v/>
       </c>
-      <c r="E26" s="39">
-        <f>ROUND(D26*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F26" s="39">
+      <c r="E27" s="40">
+        <f>ROUND(D27*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F27" s="40">
+        <f>'Юнитка FBO'!I32</f>
+        <v/>
+      </c>
+      <c r="G27" s="40">
         <f>'Юнитка FBO'!K32+'Юнитка FBO'!N32+'Юнитка FBO'!O32+'Юнитка FBO'!P32+'Юнитка FBO'!Q32+'Юнитка FBO'!R32+'Юнитка FBO'!S32+'Юнитка FBO'!V32+'Юнитка FBO'!X32+'Юнитка FBO'!Y32+'Юнитка FBO'!AK32</f>
         <v/>
       </c>
-      <c r="G26" s="39">
-        <f>E26*F26</f>
-        <v/>
-      </c>
-      <c r="H26" s="39">
-        <f>C26+G26</f>
-        <v/>
-      </c>
-      <c r="I26" s="39">
-        <f>ROUND(D26*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J26" s="39">
+      <c r="H27" s="40">
+        <f>'Юнитка FBO'!G32-'Юнитка FBO'!I32</f>
+        <v/>
+      </c>
+      <c r="I27" s="40">
+        <f>MAX(0,G27-H27)</f>
+        <v/>
+      </c>
+      <c r="J27" s="40">
+        <f>E27*I27</f>
+        <v/>
+      </c>
+      <c r="K27" s="40">
+        <f>C27+J27</f>
+        <v/>
+      </c>
+      <c r="L27" s="40">
+        <f>ROUND(D27*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M27" s="40">
         <f>'Юнитка FBO'!AG32</f>
         <v/>
       </c>
-      <c r="K26" s="39">
-        <f>I26*J26</f>
-        <v/>
-      </c>
-      <c r="L26" s="40">
-        <f>IF(K26&gt;0,H26/K26,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="38">
+      <c r="N27" s="40">
+        <f>L27*M27</f>
+        <v/>
+      </c>
+      <c r="O27" s="41">
+        <f>IF(N27&gt;0,K27/N27,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="39">
         <f>'Юнитка FBO'!A33</f>
         <v/>
       </c>
-      <c r="B27" s="39">
+      <c r="B28" s="40">
         <f>'Юнитка FBO'!C33</f>
         <v/>
       </c>
-      <c r="C27" s="39">
-        <f>B27*$B$2</f>
-        <v/>
-      </c>
-      <c r="D27" s="39">
+      <c r="C28" s="40">
+        <f>B28*$B$2</f>
+        <v/>
+      </c>
+      <c r="D28" s="40">
         <f>'Юнитка FBO'!E33</f>
         <v/>
       </c>
-      <c r="E27" s="39">
-        <f>ROUND(D27*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F27" s="39">
+      <c r="E28" s="40">
+        <f>ROUND(D28*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F28" s="40">
+        <f>'Юнитка FBO'!I33</f>
+        <v/>
+      </c>
+      <c r="G28" s="40">
         <f>'Юнитка FBO'!K33+'Юнитка FBO'!N33+'Юнитка FBO'!O33+'Юнитка FBO'!P33+'Юнитка FBO'!Q33+'Юнитка FBO'!R33+'Юнитка FBO'!S33+'Юнитка FBO'!V33+'Юнитка FBO'!X33+'Юнитка FBO'!Y33+'Юнитка FBO'!AK33</f>
         <v/>
       </c>
-      <c r="G27" s="39">
-        <f>E27*F27</f>
-        <v/>
-      </c>
-      <c r="H27" s="39">
-        <f>C27+G27</f>
-        <v/>
-      </c>
-      <c r="I27" s="39">
-        <f>ROUND(D27*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J27" s="39">
+      <c r="H28" s="40">
+        <f>'Юнитка FBO'!G33-'Юнитка FBO'!I33</f>
+        <v/>
+      </c>
+      <c r="I28" s="40">
+        <f>MAX(0,G28-H28)</f>
+        <v/>
+      </c>
+      <c r="J28" s="40">
+        <f>E28*I28</f>
+        <v/>
+      </c>
+      <c r="K28" s="40">
+        <f>C28+J28</f>
+        <v/>
+      </c>
+      <c r="L28" s="40">
+        <f>ROUND(D28*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M28" s="40">
         <f>'Юнитка FBO'!AG33</f>
         <v/>
       </c>
-      <c r="K27" s="39">
-        <f>I27*J27</f>
-        <v/>
-      </c>
-      <c r="L27" s="40">
-        <f>IF(K27&gt;0,H27/K27,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="38">
+      <c r="N28" s="40">
+        <f>L28*M28</f>
+        <v/>
+      </c>
+      <c r="O28" s="41">
+        <f>IF(N28&gt;0,K28/N28,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="39">
         <f>'Юнитка FBO'!A34</f>
         <v/>
       </c>
-      <c r="B28" s="39">
+      <c r="B29" s="40">
         <f>'Юнитка FBO'!C34</f>
         <v/>
       </c>
-      <c r="C28" s="39">
-        <f>B28*$B$2</f>
-        <v/>
-      </c>
-      <c r="D28" s="39">
+      <c r="C29" s="40">
+        <f>B29*$B$2</f>
+        <v/>
+      </c>
+      <c r="D29" s="40">
         <f>'Юнитка FBO'!E34</f>
         <v/>
       </c>
-      <c r="E28" s="39">
-        <f>ROUND(D28*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F28" s="39">
+      <c r="E29" s="40">
+        <f>ROUND(D29*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F29" s="40">
+        <f>'Юнитка FBO'!I34</f>
+        <v/>
+      </c>
+      <c r="G29" s="40">
         <f>'Юнитка FBO'!K34+'Юнитка FBO'!N34+'Юнитка FBO'!O34+'Юнитка FBO'!P34+'Юнитка FBO'!Q34+'Юнитка FBO'!R34+'Юнитка FBO'!S34+'Юнитка FBO'!V34+'Юнитка FBO'!X34+'Юнитка FBO'!Y34+'Юнитка FBO'!AK34</f>
         <v/>
       </c>
-      <c r="G28" s="39">
-        <f>E28*F28</f>
-        <v/>
-      </c>
-      <c r="H28" s="39">
-        <f>C28+G28</f>
-        <v/>
-      </c>
-      <c r="I28" s="39">
-        <f>ROUND(D28*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J28" s="39">
+      <c r="H29" s="40">
+        <f>'Юнитка FBO'!G34-'Юнитка FBO'!I34</f>
+        <v/>
+      </c>
+      <c r="I29" s="40">
+        <f>MAX(0,G29-H29)</f>
+        <v/>
+      </c>
+      <c r="J29" s="40">
+        <f>E29*I29</f>
+        <v/>
+      </c>
+      <c r="K29" s="40">
+        <f>C29+J29</f>
+        <v/>
+      </c>
+      <c r="L29" s="40">
+        <f>ROUND(D29*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M29" s="40">
         <f>'Юнитка FBO'!AG34</f>
         <v/>
       </c>
-      <c r="K28" s="39">
-        <f>I28*J28</f>
-        <v/>
-      </c>
-      <c r="L28" s="40">
-        <f>IF(K28&gt;0,H28/K28,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="38">
+      <c r="N29" s="40">
+        <f>L29*M29</f>
+        <v/>
+      </c>
+      <c r="O29" s="41">
+        <f>IF(N29&gt;0,K29/N29,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="39">
         <f>'Юнитка FBO'!A35</f>
         <v/>
       </c>
-      <c r="B29" s="39">
+      <c r="B30" s="40">
         <f>'Юнитка FBO'!C35</f>
         <v/>
       </c>
-      <c r="C29" s="39">
-        <f>B29*$B$2</f>
-        <v/>
-      </c>
-      <c r="D29" s="39">
+      <c r="C30" s="40">
+        <f>B30*$B$2</f>
+        <v/>
+      </c>
+      <c r="D30" s="40">
         <f>'Юнитка FBO'!E35</f>
         <v/>
       </c>
-      <c r="E29" s="39">
-        <f>ROUND(D29*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F29" s="39">
+      <c r="E30" s="40">
+        <f>ROUND(D30*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F30" s="40">
+        <f>'Юнитка FBO'!I35</f>
+        <v/>
+      </c>
+      <c r="G30" s="40">
         <f>'Юнитка FBO'!K35+'Юнитка FBO'!N35+'Юнитка FBO'!O35+'Юнитка FBO'!P35+'Юнитка FBO'!Q35+'Юнитка FBO'!R35+'Юнитка FBO'!S35+'Юнитка FBO'!V35+'Юнитка FBO'!X35+'Юнитка FBO'!Y35+'Юнитка FBO'!AK35</f>
         <v/>
       </c>
-      <c r="G29" s="39">
-        <f>E29*F29</f>
-        <v/>
-      </c>
-      <c r="H29" s="39">
-        <f>C29+G29</f>
-        <v/>
-      </c>
-      <c r="I29" s="39">
-        <f>ROUND(D29*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="J29" s="39">
+      <c r="H30" s="40">
+        <f>'Юнитка FBO'!G35-'Юнитка FBO'!I35</f>
+        <v/>
+      </c>
+      <c r="I30" s="40">
+        <f>MAX(0,G30-H30)</f>
+        <v/>
+      </c>
+      <c r="J30" s="40">
+        <f>E30*I30</f>
+        <v/>
+      </c>
+      <c r="K30" s="40">
+        <f>C30+J30</f>
+        <v/>
+      </c>
+      <c r="L30" s="40">
+        <f>ROUND(D30*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M30" s="40">
         <f>'Юнитка FBO'!AG35</f>
         <v/>
       </c>
-      <c r="K29" s="39">
-        <f>I29*J29</f>
-        <v/>
-      </c>
-      <c r="L29" s="40">
-        <f>IF(K29&gt;0,H29/K29,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="41" t="inlineStr">
+      <c r="N30" s="40">
+        <f>L30*M30</f>
+        <v/>
+      </c>
+      <c r="O30" s="41">
+        <f>IF(N30&gt;0,K30/N30,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="42" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B30" s="42">
-        <f>SUM(B7:B29)</f>
-        <v/>
-      </c>
-      <c r="C30" s="42">
-        <f>SUM(C7:C29)</f>
-        <v/>
-      </c>
-      <c r="D30" s="42">
-        <f>SUM(D7:D29)</f>
-        <v/>
-      </c>
-      <c r="E30" s="42">
-        <f>SUM(E7:E29)</f>
-        <v/>
-      </c>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="42">
-        <f>SUM(G7:G29)</f>
-        <v/>
-      </c>
-      <c r="H30" s="42">
-        <f>SUM(H7:H29)</f>
-        <v/>
-      </c>
-      <c r="I30" s="42">
-        <f>SUM(I7:I29)</f>
-        <v/>
-      </c>
-      <c r="J30" s="41" t="n"/>
-      <c r="K30" s="42">
-        <f>SUM(K7:K29)</f>
-        <v/>
-      </c>
-      <c r="L30" s="43">
-        <f>IF(K30&gt;0,H30/K30,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="44" t="inlineStr">
+      <c r="B31" s="43">
+        <f>SUM(B8:B30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="43">
+        <f>SUM(C8:C30)</f>
+        <v/>
+      </c>
+      <c r="D31" s="43">
+        <f>SUM(D8:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="43">
+        <f>SUM(E8:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="42" t="n"/>
+      <c r="G31" s="42" t="n"/>
+      <c r="H31" s="42" t="n"/>
+      <c r="I31" s="42" t="n"/>
+      <c r="J31" s="43">
+        <f>SUM(J8:J30)</f>
+        <v/>
+      </c>
+      <c r="K31" s="43">
+        <f>SUM(K8:K30)</f>
+        <v/>
+      </c>
+      <c r="L31" s="43">
+        <f>SUM(L8:L30)</f>
+        <v/>
+      </c>
+      <c r="M31" s="42" t="n"/>
+      <c r="N31" s="43">
+        <f>SUM(N8:N30)</f>
+        <v/>
+      </c>
+      <c r="O31" s="44">
+        <f>IF(N31&gt;0,K31/N31,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="45" t="inlineStr">
         <is>
           <t>Денежный поток по месяцам</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="37" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="38" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B34" s="37" t="inlineStr">
+      <c r="B35" s="38" t="inlineStr">
         <is>
           <t>Расходы (накрутка), ₽</t>
         </is>
       </c>
-      <c r="C34" s="37" t="inlineStr">
+      <c r="C35" s="38" t="inlineStr">
         <is>
           <t>Прибыль от продаж, ₽</t>
         </is>
       </c>
-      <c r="D34" s="37" t="inlineStr">
+      <c r="D35" s="38" t="inlineStr">
         <is>
           <t>Чистый поток, ₽</t>
         </is>
       </c>
-      <c r="E34" s="37" t="inlineStr">
+      <c r="E35" s="38" t="inlineStr">
         <is>
           <t>Накопительно, ₽</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="38" t="n">
+    <row r="36">
+      <c r="A36" s="39" t="n">
         <v>1</v>
       </c>
-      <c r="B35" s="39">
-        <f>$H$30</f>
-        <v/>
-      </c>
-      <c r="C35" s="39" t="n">
+      <c r="B36" s="40">
+        <f>$K$31</f>
+        <v/>
+      </c>
+      <c r="C36" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D35" s="39">
-        <f>C35-B35</f>
-        <v/>
-      </c>
-      <c r="E35" s="39">
-        <f>D35</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="38" t="n">
+      <c r="D36" s="40">
+        <f>C36-B36</f>
+        <v/>
+      </c>
+      <c r="E36" s="40">
+        <f>D36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="n">
         <v>2</v>
       </c>
-      <c r="B36" s="39" t="n">
+      <c r="B37" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C36" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D36" s="39">
-        <f>C36-B36</f>
-        <v/>
-      </c>
-      <c r="E36" s="39">
-        <f>E35+D36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="38" t="n">
+      <c r="C37" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D37" s="40">
+        <f>C37-B37</f>
+        <v/>
+      </c>
+      <c r="E37" s="40">
+        <f>E36+D37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="n">
         <v>3</v>
       </c>
-      <c r="B37" s="39" t="n">
+      <c r="B38" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C37" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D37" s="39">
-        <f>C37-B37</f>
-        <v/>
-      </c>
-      <c r="E37" s="39">
-        <f>E36+D37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="38" t="n">
+      <c r="C38" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D38" s="40">
+        <f>C38-B38</f>
+        <v/>
+      </c>
+      <c r="E38" s="40">
+        <f>E37+D38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="n">
         <v>4</v>
       </c>
-      <c r="B38" s="39" t="n">
+      <c r="B39" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D38" s="39">
-        <f>C38-B38</f>
-        <v/>
-      </c>
-      <c r="E38" s="39">
-        <f>E37+D38</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="38" t="n">
+      <c r="C39" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D39" s="40">
+        <f>C39-B39</f>
+        <v/>
+      </c>
+      <c r="E39" s="40">
+        <f>E38+D39</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="n">
         <v>5</v>
       </c>
-      <c r="B39" s="39" t="n">
+      <c r="B40" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D39" s="39">
-        <f>C39-B39</f>
-        <v/>
-      </c>
-      <c r="E39" s="39">
-        <f>E38+D39</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="38" t="n">
+      <c r="C40" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D40" s="40">
+        <f>C40-B40</f>
+        <v/>
+      </c>
+      <c r="E40" s="40">
+        <f>E39+D40</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="n">
         <v>6</v>
       </c>
-      <c r="B40" s="39" t="n">
+      <c r="B41" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D40" s="39">
-        <f>C40-B40</f>
-        <v/>
-      </c>
-      <c r="E40" s="39">
-        <f>E39+D40</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="38" t="n">
+      <c r="C41" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D41" s="40">
+        <f>C41-B41</f>
+        <v/>
+      </c>
+      <c r="E41" s="40">
+        <f>E40+D41</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="n">
         <v>7</v>
       </c>
-      <c r="B41" s="39" t="n">
+      <c r="B42" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D41" s="39">
-        <f>C41-B41</f>
-        <v/>
-      </c>
-      <c r="E41" s="39">
-        <f>E40+D41</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="38" t="n">
+      <c r="C42" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D42" s="40">
+        <f>C42-B42</f>
+        <v/>
+      </c>
+      <c r="E42" s="40">
+        <f>E41+D42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="n">
         <v>8</v>
       </c>
-      <c r="B42" s="39" t="n">
+      <c r="B43" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C42" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D42" s="39">
-        <f>C42-B42</f>
-        <v/>
-      </c>
-      <c r="E42" s="39">
-        <f>E41+D42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="38" t="n">
+      <c r="C43" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D43" s="40">
+        <f>C43-B43</f>
+        <v/>
+      </c>
+      <c r="E43" s="40">
+        <f>E42+D43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="39" t="n">
         <v>9</v>
       </c>
-      <c r="B43" s="39" t="n">
+      <c r="B44" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C43" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D43" s="39">
-        <f>C43-B43</f>
-        <v/>
-      </c>
-      <c r="E43" s="39">
-        <f>E42+D43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="38" t="n">
+      <c r="C44" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D44" s="40">
+        <f>C44-B44</f>
+        <v/>
+      </c>
+      <c r="E44" s="40">
+        <f>E43+D44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="39" t="n">
         <v>10</v>
       </c>
-      <c r="B44" s="39" t="n">
+      <c r="B45" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C44" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D44" s="39">
-        <f>C44-B44</f>
-        <v/>
-      </c>
-      <c r="E44" s="39">
-        <f>E43+D44</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="38" t="n">
+      <c r="C45" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D45" s="40">
+        <f>C45-B45</f>
+        <v/>
+      </c>
+      <c r="E45" s="40">
+        <f>E44+D45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="39" t="n">
         <v>11</v>
       </c>
-      <c r="B45" s="39" t="n">
+      <c r="B46" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C45" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D45" s="39">
-        <f>C45-B45</f>
-        <v/>
-      </c>
-      <c r="E45" s="39">
-        <f>E44+D45</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="38" t="n">
+      <c r="C46" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D46" s="40">
+        <f>C46-B46</f>
+        <v/>
+      </c>
+      <c r="E46" s="40">
+        <f>E45+D46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="39" t="n">
         <v>12</v>
       </c>
-      <c r="B46" s="39" t="n">
+      <c r="B47" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C46" s="39">
-        <f>$K$30</f>
-        <v/>
-      </c>
-      <c r="D46" s="39">
-        <f>C46-B46</f>
-        <v/>
-      </c>
-      <c r="E46" s="39">
-        <f>E45+D46</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="34" t="inlineStr">
-        <is>
-          <t>Разовые расходы на раскрутку (1-й мес), ₽</t>
-        </is>
-      </c>
-      <c r="B48" s="42">
-        <f>$H$30</f>
+      <c r="C47" s="40">
+        <f>$N$31</f>
+        <v/>
+      </c>
+      <c r="D47" s="40">
+        <f>C47-B47</f>
+        <v/>
+      </c>
+      <c r="E47" s="40">
+        <f>E46+D47</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="34" t="inlineStr">
         <is>
-          <t>Прибыль в месяц (со 2-го мес), ₽</t>
-        </is>
-      </c>
-      <c r="B49" s="42">
-        <f>$K$30</f>
+          <t>Разовые расходы на раскрутку (1-й мес), ₽</t>
+        </is>
+      </c>
+      <c r="B49" s="43">
+        <f>$K$31</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="34" t="inlineStr">
         <is>
-          <t>Окупаемость раскрутки, мес продаж</t>
+          <t>Прибыль в месяц (со 2-го мес), ₽</t>
         </is>
       </c>
       <c r="B50" s="43">
-        <f>IF($K$30&gt;0,$H$30/$K$30,"—")</f>
+        <f>$N$31</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="34" t="inlineStr">
         <is>
+          <t>Окупаемость раскрутки, мес продаж</t>
+        </is>
+      </c>
+      <c r="B51" s="44">
+        <f>IF($N$31&gt;0,$K$31/$N$31,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="34" t="inlineStr">
+        <is>
           <t>Выход в плюс с запуска, мес</t>
         </is>
       </c>
-      <c r="B51" s="43">
-        <f>IF($K$30&gt;0,1+$H$30/$K$30,"—")</f>
+      <c r="B52" s="44">
+        <f>IF($N$31&gt;0,1+$K$31/$N$31,"—")</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
+++ b/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
@@ -6572,7 +6572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6630,158 +6630,106 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
-        <is>
-          <t>Самовыкуп: платим цену с СПП (покупатель), получаем выплату Ozon с цены продавца (СПП финансирует Ozon), товар возвращается на склад → теряем только сборы Ozon сверх компенсации СПП.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="38" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
+        <is>
+          <t>Прочие расходы на 1 самовыкуп, ₽ (забор с ПВЗ, оформление)</t>
+        </is>
+      </c>
+      <c r="B5" s="35" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>Самовыкуп: платим цену с СПП (покупатель), получаем выплату Ozon с цены продавца (СПП финансирует Ozon), товар возвращается на склад → теряем только сборы Ozon сверх компенсации СПП + прочие расходы.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="48" customHeight="1">
+      <c r="A8" s="38" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="B7" s="38" t="inlineStr">
+      <c r="B8" s="38" t="inlineStr">
         <is>
           <t>Отзывов, шт</t>
         </is>
       </c>
-      <c r="C7" s="38" t="inlineStr">
+      <c r="C8" s="38" t="inlineStr">
         <is>
           <t>Отзывы, ₽</t>
         </is>
       </c>
-      <c r="D7" s="38" t="inlineStr">
+      <c r="D8" s="38" t="inlineStr">
         <is>
           <t>Заказы конкур., шт</t>
         </is>
       </c>
-      <c r="E7" s="38" t="inlineStr">
+      <c r="E8" s="38" t="inlineStr">
         <is>
           <t>Самовыкупов, шт</t>
         </is>
       </c>
-      <c r="F7" s="38" t="inlineStr">
+      <c r="F8" s="38" t="inlineStr">
         <is>
           <t>Цена выкупа (с СПП), ₽</t>
         </is>
       </c>
-      <c r="G7" s="38" t="inlineStr">
+      <c r="G8" s="38" t="inlineStr">
         <is>
           <t>Сборы Ozon / выкуп, ₽</t>
         </is>
       </c>
-      <c r="H7" s="38" t="inlineStr">
+      <c r="H8" s="38" t="inlineStr">
         <is>
           <t>Компенсация СПП, ₽</t>
         </is>
       </c>
-      <c r="I7" s="38" t="inlineStr">
+      <c r="I8" s="38" t="inlineStr">
         <is>
           <t>Безвозврат / выкуп, ₽</t>
         </is>
       </c>
-      <c r="J7" s="38" t="inlineStr">
+      <c r="J8" s="38" t="inlineStr">
         <is>
           <t>Самовыкупы, ₽</t>
         </is>
       </c>
-      <c r="K7" s="38" t="inlineStr">
+      <c r="K8" s="38" t="inlineStr">
         <is>
           <t>Расходы 1-й мес, ₽</t>
         </is>
       </c>
-      <c r="L7" s="38" t="inlineStr">
+      <c r="L8" s="38" t="inlineStr">
         <is>
           <t>Продаж/мес (со 2-го), шт</t>
         </is>
       </c>
-      <c r="M7" s="38" t="inlineStr">
+      <c r="M8" s="38" t="inlineStr">
         <is>
           <t>Маржа/шт, ₽</t>
         </is>
       </c>
-      <c r="N7" s="38" t="inlineStr">
+      <c r="N8" s="38" t="inlineStr">
         <is>
           <t>Прибыль/мес (со 2-го), ₽</t>
         </is>
       </c>
-      <c r="O7" s="38" t="inlineStr">
+      <c r="O8" s="38" t="inlineStr">
         <is>
           <t>Окупаемость, мес</t>
         </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="39">
-        <f>'Юнитка FBO'!A13</f>
-        <v/>
-      </c>
-      <c r="B8" s="40">
-        <f>'Юнитка FBO'!C13</f>
-        <v/>
-      </c>
-      <c r="C8" s="40">
-        <f>B8*$B$2</f>
-        <v/>
-      </c>
-      <c r="D8" s="40">
-        <f>'Юнитка FBO'!E13</f>
-        <v/>
-      </c>
-      <c r="E8" s="40">
-        <f>ROUND(D8*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F8" s="40">
-        <f>'Юнитка FBO'!I13</f>
-        <v/>
-      </c>
-      <c r="G8" s="40">
-        <f>'Юнитка FBO'!K13+'Юнитка FBO'!N13+'Юнитка FBO'!O13+'Юнитка FBO'!P13+'Юнитка FBO'!Q13+'Юнитка FBO'!R13+'Юнитка FBO'!S13+'Юнитка FBO'!V13+'Юнитка FBO'!X13+'Юнитка FBO'!Y13+'Юнитка FBO'!AK13</f>
-        <v/>
-      </c>
-      <c r="H8" s="40">
-        <f>'Юнитка FBO'!G13-'Юнитка FBO'!I13</f>
-        <v/>
-      </c>
-      <c r="I8" s="40">
-        <f>MAX(0,G8-H8)</f>
-        <v/>
-      </c>
-      <c r="J8" s="40">
-        <f>E8*I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="40">
-        <f>C8+J8</f>
-        <v/>
-      </c>
-      <c r="L8" s="40">
-        <f>ROUND(D8*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="M8" s="40">
-        <f>'Юнитка FBO'!AG13</f>
-        <v/>
-      </c>
-      <c r="N8" s="40">
-        <f>L8*M8</f>
-        <v/>
-      </c>
-      <c r="O8" s="41">
-        <f>IF(N8&gt;0,K8/N8,"—")</f>
-        <v/>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="39">
-        <f>'Юнитка FBO'!A14</f>
+        <f>'Юнитка FBO'!A13</f>
         <v/>
       </c>
       <c r="B9" s="40">
-        <f>'Юнитка FBO'!C14</f>
+        <f>'Юнитка FBO'!C13</f>
         <v/>
       </c>
       <c r="C9" s="40">
@@ -6789,7 +6737,7 @@
         <v/>
       </c>
       <c r="D9" s="40">
-        <f>'Юнитка FBO'!E14</f>
+        <f>'Юнитка FBO'!E13</f>
         <v/>
       </c>
       <c r="E9" s="40">
@@ -6797,19 +6745,19 @@
         <v/>
       </c>
       <c r="F9" s="40">
-        <f>'Юнитка FBO'!I14</f>
+        <f>'Юнитка FBO'!I13</f>
         <v/>
       </c>
       <c r="G9" s="40">
-        <f>'Юнитка FBO'!K14+'Юнитка FBO'!N14+'Юнитка FBO'!O14+'Юнитка FBO'!P14+'Юнитка FBO'!Q14+'Юнитка FBO'!R14+'Юнитка FBO'!S14+'Юнитка FBO'!V14+'Юнитка FBO'!X14+'Юнитка FBO'!Y14+'Юнитка FBO'!AK14</f>
+        <f>'Юнитка FBO'!K13+'Юнитка FBO'!N13+'Юнитка FBO'!O13+'Юнитка FBO'!P13+'Юнитка FBO'!Q13+'Юнитка FBO'!R13+'Юнитка FBO'!S13+'Юнитка FBO'!V13+'Юнитка FBO'!X13+'Юнитка FBO'!Y13+'Юнитка FBO'!AK13</f>
         <v/>
       </c>
       <c r="H9" s="40">
-        <f>'Юнитка FBO'!G14-'Юнитка FBO'!I14</f>
+        <f>'Юнитка FBO'!G13-'Юнитка FBO'!I13</f>
         <v/>
       </c>
       <c r="I9" s="40">
-        <f>MAX(0,G9-H9)</f>
+        <f>MAX(0,G9-H9)+$B$5</f>
         <v/>
       </c>
       <c r="J9" s="40">
@@ -6825,7 +6773,7 @@
         <v/>
       </c>
       <c r="M9" s="40">
-        <f>'Юнитка FBO'!AG14</f>
+        <f>'Юнитка FBO'!AG13</f>
         <v/>
       </c>
       <c r="N9" s="40">
@@ -6839,11 +6787,11 @@
     </row>
     <row r="10">
       <c r="A10" s="39">
-        <f>'Юнитка FBO'!A15</f>
+        <f>'Юнитка FBO'!A14</f>
         <v/>
       </c>
       <c r="B10" s="40">
-        <f>'Юнитка FBO'!C15</f>
+        <f>'Юнитка FBO'!C14</f>
         <v/>
       </c>
       <c r="C10" s="40">
@@ -6851,7 +6799,7 @@
         <v/>
       </c>
       <c r="D10" s="40">
-        <f>'Юнитка FBO'!E15</f>
+        <f>'Юнитка FBO'!E14</f>
         <v/>
       </c>
       <c r="E10" s="40">
@@ -6859,19 +6807,19 @@
         <v/>
       </c>
       <c r="F10" s="40">
-        <f>'Юнитка FBO'!I15</f>
+        <f>'Юнитка FBO'!I14</f>
         <v/>
       </c>
       <c r="G10" s="40">
-        <f>'Юнитка FBO'!K15+'Юнитка FBO'!N15+'Юнитка FBO'!O15+'Юнитка FBO'!P15+'Юнитка FBO'!Q15+'Юнитка FBO'!R15+'Юнитка FBO'!S15+'Юнитка FBO'!V15+'Юнитка FBO'!X15+'Юнитка FBO'!Y15+'Юнитка FBO'!AK15</f>
+        <f>'Юнитка FBO'!K14+'Юнитка FBO'!N14+'Юнитка FBO'!O14+'Юнитка FBO'!P14+'Юнитка FBO'!Q14+'Юнитка FBO'!R14+'Юнитка FBO'!S14+'Юнитка FBO'!V14+'Юнитка FBO'!X14+'Юнитка FBO'!Y14+'Юнитка FBO'!AK14</f>
         <v/>
       </c>
       <c r="H10" s="40">
-        <f>'Юнитка FBO'!G15-'Юнитка FBO'!I15</f>
+        <f>'Юнитка FBO'!G14-'Юнитка FBO'!I14</f>
         <v/>
       </c>
       <c r="I10" s="40">
-        <f>MAX(0,G10-H10)</f>
+        <f>MAX(0,G10-H10)+$B$5</f>
         <v/>
       </c>
       <c r="J10" s="40">
@@ -6887,7 +6835,7 @@
         <v/>
       </c>
       <c r="M10" s="40">
-        <f>'Юнитка FBO'!AG15</f>
+        <f>'Юнитка FBO'!AG14</f>
         <v/>
       </c>
       <c r="N10" s="40">
@@ -6901,11 +6849,11 @@
     </row>
     <row r="11">
       <c r="A11" s="39">
-        <f>'Юнитка FBO'!A16</f>
+        <f>'Юнитка FBO'!A15</f>
         <v/>
       </c>
       <c r="B11" s="40">
-        <f>'Юнитка FBO'!C16</f>
+        <f>'Юнитка FBO'!C15</f>
         <v/>
       </c>
       <c r="C11" s="40">
@@ -6913,7 +6861,7 @@
         <v/>
       </c>
       <c r="D11" s="40">
-        <f>'Юнитка FBO'!E16</f>
+        <f>'Юнитка FBO'!E15</f>
         <v/>
       </c>
       <c r="E11" s="40">
@@ -6921,19 +6869,19 @@
         <v/>
       </c>
       <c r="F11" s="40">
-        <f>'Юнитка FBO'!I16</f>
+        <f>'Юнитка FBO'!I15</f>
         <v/>
       </c>
       <c r="G11" s="40">
-        <f>'Юнитка FBO'!K16+'Юнитка FBO'!N16+'Юнитка FBO'!O16+'Юнитка FBO'!P16+'Юнитка FBO'!Q16+'Юнитка FBO'!R16+'Юнитка FBO'!S16+'Юнитка FBO'!V16+'Юнитка FBO'!X16+'Юнитка FBO'!Y16+'Юнитка FBO'!AK16</f>
+        <f>'Юнитка FBO'!K15+'Юнитка FBO'!N15+'Юнитка FBO'!O15+'Юнитка FBO'!P15+'Юнитка FBO'!Q15+'Юнитка FBO'!R15+'Юнитка FBO'!S15+'Юнитка FBO'!V15+'Юнитка FBO'!X15+'Юнитка FBO'!Y15+'Юнитка FBO'!AK15</f>
         <v/>
       </c>
       <c r="H11" s="40">
-        <f>'Юнитка FBO'!G16-'Юнитка FBO'!I16</f>
+        <f>'Юнитка FBO'!G15-'Юнитка FBO'!I15</f>
         <v/>
       </c>
       <c r="I11" s="40">
-        <f>MAX(0,G11-H11)</f>
+        <f>MAX(0,G11-H11)+$B$5</f>
         <v/>
       </c>
       <c r="J11" s="40">
@@ -6949,7 +6897,7 @@
         <v/>
       </c>
       <c r="M11" s="40">
-        <f>'Юнитка FBO'!AG16</f>
+        <f>'Юнитка FBO'!AG15</f>
         <v/>
       </c>
       <c r="N11" s="40">
@@ -6963,11 +6911,11 @@
     </row>
     <row r="12">
       <c r="A12" s="39">
-        <f>'Юнитка FBO'!A17</f>
+        <f>'Юнитка FBO'!A16</f>
         <v/>
       </c>
       <c r="B12" s="40">
-        <f>'Юнитка FBO'!C17</f>
+        <f>'Юнитка FBO'!C16</f>
         <v/>
       </c>
       <c r="C12" s="40">
@@ -6975,7 +6923,7 @@
         <v/>
       </c>
       <c r="D12" s="40">
-        <f>'Юнитка FBO'!E17</f>
+        <f>'Юнитка FBO'!E16</f>
         <v/>
       </c>
       <c r="E12" s="40">
@@ -6983,19 +6931,19 @@
         <v/>
       </c>
       <c r="F12" s="40">
-        <f>'Юнитка FBO'!I17</f>
+        <f>'Юнитка FBO'!I16</f>
         <v/>
       </c>
       <c r="G12" s="40">
-        <f>'Юнитка FBO'!K17+'Юнитка FBO'!N17+'Юнитка FBO'!O17+'Юнитка FBO'!P17+'Юнитка FBO'!Q17+'Юнитка FBO'!R17+'Юнитка FBO'!S17+'Юнитка FBO'!V17+'Юнитка FBO'!X17+'Юнитка FBO'!Y17+'Юнитка FBO'!AK17</f>
+        <f>'Юнитка FBO'!K16+'Юнитка FBO'!N16+'Юнитка FBO'!O16+'Юнитка FBO'!P16+'Юнитка FBO'!Q16+'Юнитка FBO'!R16+'Юнитка FBO'!S16+'Юнитка FBO'!V16+'Юнитка FBO'!X16+'Юнитка FBO'!Y16+'Юнитка FBO'!AK16</f>
         <v/>
       </c>
       <c r="H12" s="40">
-        <f>'Юнитка FBO'!G17-'Юнитка FBO'!I17</f>
+        <f>'Юнитка FBO'!G16-'Юнитка FBO'!I16</f>
         <v/>
       </c>
       <c r="I12" s="40">
-        <f>MAX(0,G12-H12)</f>
+        <f>MAX(0,G12-H12)+$B$5</f>
         <v/>
       </c>
       <c r="J12" s="40">
@@ -7011,7 +6959,7 @@
         <v/>
       </c>
       <c r="M12" s="40">
-        <f>'Юнитка FBO'!AG17</f>
+        <f>'Юнитка FBO'!AG16</f>
         <v/>
       </c>
       <c r="N12" s="40">
@@ -7025,11 +6973,11 @@
     </row>
     <row r="13">
       <c r="A13" s="39">
-        <f>'Юнитка FBO'!A18</f>
+        <f>'Юнитка FBO'!A17</f>
         <v/>
       </c>
       <c r="B13" s="40">
-        <f>'Юнитка FBO'!C18</f>
+        <f>'Юнитка FBO'!C17</f>
         <v/>
       </c>
       <c r="C13" s="40">
@@ -7037,7 +6985,7 @@
         <v/>
       </c>
       <c r="D13" s="40">
-        <f>'Юнитка FBO'!E18</f>
+        <f>'Юнитка FBO'!E17</f>
         <v/>
       </c>
       <c r="E13" s="40">
@@ -7045,19 +6993,19 @@
         <v/>
       </c>
       <c r="F13" s="40">
-        <f>'Юнитка FBO'!I18</f>
+        <f>'Юнитка FBO'!I17</f>
         <v/>
       </c>
       <c r="G13" s="40">
-        <f>'Юнитка FBO'!K18+'Юнитка FBO'!N18+'Юнитка FBO'!O18+'Юнитка FBO'!P18+'Юнитка FBO'!Q18+'Юнитка FBO'!R18+'Юнитка FBO'!S18+'Юнитка FBO'!V18+'Юнитка FBO'!X18+'Юнитка FBO'!Y18+'Юнитка FBO'!AK18</f>
+        <f>'Юнитка FBO'!K17+'Юнитка FBO'!N17+'Юнитка FBO'!O17+'Юнитка FBO'!P17+'Юнитка FBO'!Q17+'Юнитка FBO'!R17+'Юнитка FBO'!S17+'Юнитка FBO'!V17+'Юнитка FBO'!X17+'Юнитка FBO'!Y17+'Юнитка FBO'!AK17</f>
         <v/>
       </c>
       <c r="H13" s="40">
-        <f>'Юнитка FBO'!G18-'Юнитка FBO'!I18</f>
+        <f>'Юнитка FBO'!G17-'Юнитка FBO'!I17</f>
         <v/>
       </c>
       <c r="I13" s="40">
-        <f>MAX(0,G13-H13)</f>
+        <f>MAX(0,G13-H13)+$B$5</f>
         <v/>
       </c>
       <c r="J13" s="40">
@@ -7073,7 +7021,7 @@
         <v/>
       </c>
       <c r="M13" s="40">
-        <f>'Юнитка FBO'!AG18</f>
+        <f>'Юнитка FBO'!AG17</f>
         <v/>
       </c>
       <c r="N13" s="40">
@@ -7087,11 +7035,11 @@
     </row>
     <row r="14">
       <c r="A14" s="39">
-        <f>'Юнитка FBO'!A19</f>
+        <f>'Юнитка FBO'!A18</f>
         <v/>
       </c>
       <c r="B14" s="40">
-        <f>'Юнитка FBO'!C19</f>
+        <f>'Юнитка FBO'!C18</f>
         <v/>
       </c>
       <c r="C14" s="40">
@@ -7099,7 +7047,7 @@
         <v/>
       </c>
       <c r="D14" s="40">
-        <f>'Юнитка FBO'!E19</f>
+        <f>'Юнитка FBO'!E18</f>
         <v/>
       </c>
       <c r="E14" s="40">
@@ -7107,19 +7055,19 @@
         <v/>
       </c>
       <c r="F14" s="40">
-        <f>'Юнитка FBO'!I19</f>
+        <f>'Юнитка FBO'!I18</f>
         <v/>
       </c>
       <c r="G14" s="40">
-        <f>'Юнитка FBO'!K19+'Юнитка FBO'!N19+'Юнитка FBO'!O19+'Юнитка FBO'!P19+'Юнитка FBO'!Q19+'Юнитка FBO'!R19+'Юнитка FBO'!S19+'Юнитка FBO'!V19+'Юнитка FBO'!X19+'Юнитка FBO'!Y19+'Юнитка FBO'!AK19</f>
+        <f>'Юнитка FBO'!K18+'Юнитка FBO'!N18+'Юнитка FBO'!O18+'Юнитка FBO'!P18+'Юнитка FBO'!Q18+'Юнитка FBO'!R18+'Юнитка FBO'!S18+'Юнитка FBO'!V18+'Юнитка FBO'!X18+'Юнитка FBO'!Y18+'Юнитка FBO'!AK18</f>
         <v/>
       </c>
       <c r="H14" s="40">
-        <f>'Юнитка FBO'!G19-'Юнитка FBO'!I19</f>
+        <f>'Юнитка FBO'!G18-'Юнитка FBO'!I18</f>
         <v/>
       </c>
       <c r="I14" s="40">
-        <f>MAX(0,G14-H14)</f>
+        <f>MAX(0,G14-H14)+$B$5</f>
         <v/>
       </c>
       <c r="J14" s="40">
@@ -7135,7 +7083,7 @@
         <v/>
       </c>
       <c r="M14" s="40">
-        <f>'Юнитка FBO'!AG19</f>
+        <f>'Юнитка FBO'!AG18</f>
         <v/>
       </c>
       <c r="N14" s="40">
@@ -7149,11 +7097,11 @@
     </row>
     <row r="15">
       <c r="A15" s="39">
-        <f>'Юнитка FBO'!A20</f>
+        <f>'Юнитка FBO'!A19</f>
         <v/>
       </c>
       <c r="B15" s="40">
-        <f>'Юнитка FBO'!C20</f>
+        <f>'Юнитка FBO'!C19</f>
         <v/>
       </c>
       <c r="C15" s="40">
@@ -7161,7 +7109,7 @@
         <v/>
       </c>
       <c r="D15" s="40">
-        <f>'Юнитка FBO'!E20</f>
+        <f>'Юнитка FBO'!E19</f>
         <v/>
       </c>
       <c r="E15" s="40">
@@ -7169,19 +7117,19 @@
         <v/>
       </c>
       <c r="F15" s="40">
-        <f>'Юнитка FBO'!I20</f>
+        <f>'Юнитка FBO'!I19</f>
         <v/>
       </c>
       <c r="G15" s="40">
-        <f>'Юнитка FBO'!K20+'Юнитка FBO'!N20+'Юнитка FBO'!O20+'Юнитка FBO'!P20+'Юнитка FBO'!Q20+'Юнитка FBO'!R20+'Юнитка FBO'!S20+'Юнитка FBO'!V20+'Юнитка FBO'!X20+'Юнитка FBO'!Y20+'Юнитка FBO'!AK20</f>
+        <f>'Юнитка FBO'!K19+'Юнитка FBO'!N19+'Юнитка FBO'!O19+'Юнитка FBO'!P19+'Юнитка FBO'!Q19+'Юнитка FBO'!R19+'Юнитка FBO'!S19+'Юнитка FBO'!V19+'Юнитка FBO'!X19+'Юнитка FBO'!Y19+'Юнитка FBO'!AK19</f>
         <v/>
       </c>
       <c r="H15" s="40">
-        <f>'Юнитка FBO'!G20-'Юнитка FBO'!I20</f>
+        <f>'Юнитка FBO'!G19-'Юнитка FBO'!I19</f>
         <v/>
       </c>
       <c r="I15" s="40">
-        <f>MAX(0,G15-H15)</f>
+        <f>MAX(0,G15-H15)+$B$5</f>
         <v/>
       </c>
       <c r="J15" s="40">
@@ -7197,7 +7145,7 @@
         <v/>
       </c>
       <c r="M15" s="40">
-        <f>'Юнитка FBO'!AG20</f>
+        <f>'Юнитка FBO'!AG19</f>
         <v/>
       </c>
       <c r="N15" s="40">
@@ -7211,11 +7159,11 @@
     </row>
     <row r="16">
       <c r="A16" s="39">
-        <f>'Юнитка FBO'!A21</f>
+        <f>'Юнитка FBO'!A20</f>
         <v/>
       </c>
       <c r="B16" s="40">
-        <f>'Юнитка FBO'!C21</f>
+        <f>'Юнитка FBO'!C20</f>
         <v/>
       </c>
       <c r="C16" s="40">
@@ -7223,7 +7171,7 @@
         <v/>
       </c>
       <c r="D16" s="40">
-        <f>'Юнитка FBO'!E21</f>
+        <f>'Юнитка FBO'!E20</f>
         <v/>
       </c>
       <c r="E16" s="40">
@@ -7231,19 +7179,19 @@
         <v/>
       </c>
       <c r="F16" s="40">
-        <f>'Юнитка FBO'!I21</f>
+        <f>'Юнитка FBO'!I20</f>
         <v/>
       </c>
       <c r="G16" s="40">
-        <f>'Юнитка FBO'!K21+'Юнитка FBO'!N21+'Юнитка FBO'!O21+'Юнитка FBO'!P21+'Юнитка FBO'!Q21+'Юнитка FBO'!R21+'Юнитка FBO'!S21+'Юнитка FBO'!V21+'Юнитка FBO'!X21+'Юнитка FBO'!Y21+'Юнитка FBO'!AK21</f>
+        <f>'Юнитка FBO'!K20+'Юнитка FBO'!N20+'Юнитка FBO'!O20+'Юнитка FBO'!P20+'Юнитка FBO'!Q20+'Юнитка FBO'!R20+'Юнитка FBO'!S20+'Юнитка FBO'!V20+'Юнитка FBO'!X20+'Юнитка FBO'!Y20+'Юнитка FBO'!AK20</f>
         <v/>
       </c>
       <c r="H16" s="40">
-        <f>'Юнитка FBO'!G21-'Юнитка FBO'!I21</f>
+        <f>'Юнитка FBO'!G20-'Юнитка FBO'!I20</f>
         <v/>
       </c>
       <c r="I16" s="40">
-        <f>MAX(0,G16-H16)</f>
+        <f>MAX(0,G16-H16)+$B$5</f>
         <v/>
       </c>
       <c r="J16" s="40">
@@ -7259,7 +7207,7 @@
         <v/>
       </c>
       <c r="M16" s="40">
-        <f>'Юнитка FBO'!AG21</f>
+        <f>'Юнитка FBO'!AG20</f>
         <v/>
       </c>
       <c r="N16" s="40">
@@ -7273,11 +7221,11 @@
     </row>
     <row r="17">
       <c r="A17" s="39">
-        <f>'Юнитка FBO'!A22</f>
+        <f>'Юнитка FBO'!A21</f>
         <v/>
       </c>
       <c r="B17" s="40">
-        <f>'Юнитка FBO'!C22</f>
+        <f>'Юнитка FBO'!C21</f>
         <v/>
       </c>
       <c r="C17" s="40">
@@ -7285,7 +7233,7 @@
         <v/>
       </c>
       <c r="D17" s="40">
-        <f>'Юнитка FBO'!E22</f>
+        <f>'Юнитка FBO'!E21</f>
         <v/>
       </c>
       <c r="E17" s="40">
@@ -7293,19 +7241,19 @@
         <v/>
       </c>
       <c r="F17" s="40">
-        <f>'Юнитка FBO'!I22</f>
+        <f>'Юнитка FBO'!I21</f>
         <v/>
       </c>
       <c r="G17" s="40">
-        <f>'Юнитка FBO'!K22+'Юнитка FBO'!N22+'Юнитка FBO'!O22+'Юнитка FBO'!P22+'Юнитка FBO'!Q22+'Юнитка FBO'!R22+'Юнитка FBO'!S22+'Юнитка FBO'!V22+'Юнитка FBO'!X22+'Юнитка FBO'!Y22+'Юнитка FBO'!AK22</f>
+        <f>'Юнитка FBO'!K21+'Юнитка FBO'!N21+'Юнитка FBO'!O21+'Юнитка FBO'!P21+'Юнитка FBO'!Q21+'Юнитка FBO'!R21+'Юнитка FBO'!S21+'Юнитка FBO'!V21+'Юнитка FBO'!X21+'Юнитка FBO'!Y21+'Юнитка FBO'!AK21</f>
         <v/>
       </c>
       <c r="H17" s="40">
-        <f>'Юнитка FBO'!G22-'Юнитка FBO'!I22</f>
+        <f>'Юнитка FBO'!G21-'Юнитка FBO'!I21</f>
         <v/>
       </c>
       <c r="I17" s="40">
-        <f>MAX(0,G17-H17)</f>
+        <f>MAX(0,G17-H17)+$B$5</f>
         <v/>
       </c>
       <c r="J17" s="40">
@@ -7321,7 +7269,7 @@
         <v/>
       </c>
       <c r="M17" s="40">
-        <f>'Юнитка FBO'!AG22</f>
+        <f>'Юнитка FBO'!AG21</f>
         <v/>
       </c>
       <c r="N17" s="40">
@@ -7335,11 +7283,11 @@
     </row>
     <row r="18">
       <c r="A18" s="39">
-        <f>'Юнитка FBO'!A23</f>
+        <f>'Юнитка FBO'!A22</f>
         <v/>
       </c>
       <c r="B18" s="40">
-        <f>'Юнитка FBO'!C23</f>
+        <f>'Юнитка FBO'!C22</f>
         <v/>
       </c>
       <c r="C18" s="40">
@@ -7347,7 +7295,7 @@
         <v/>
       </c>
       <c r="D18" s="40">
-        <f>'Юнитка FBO'!E23</f>
+        <f>'Юнитка FBO'!E22</f>
         <v/>
       </c>
       <c r="E18" s="40">
@@ -7355,19 +7303,19 @@
         <v/>
       </c>
       <c r="F18" s="40">
-        <f>'Юнитка FBO'!I23</f>
+        <f>'Юнитка FBO'!I22</f>
         <v/>
       </c>
       <c r="G18" s="40">
-        <f>'Юнитка FBO'!K23+'Юнитка FBO'!N23+'Юнитка FBO'!O23+'Юнитка FBO'!P23+'Юнитка FBO'!Q23+'Юнитка FBO'!R23+'Юнитка FBO'!S23+'Юнитка FBO'!V23+'Юнитка FBO'!X23+'Юнитка FBO'!Y23+'Юнитка FBO'!AK23</f>
+        <f>'Юнитка FBO'!K22+'Юнитка FBO'!N22+'Юнитка FBO'!O22+'Юнитка FBO'!P22+'Юнитка FBO'!Q22+'Юнитка FBO'!R22+'Юнитка FBO'!S22+'Юнитка FBO'!V22+'Юнитка FBO'!X22+'Юнитка FBO'!Y22+'Юнитка FBO'!AK22</f>
         <v/>
       </c>
       <c r="H18" s="40">
-        <f>'Юнитка FBO'!G23-'Юнитка FBO'!I23</f>
+        <f>'Юнитка FBO'!G22-'Юнитка FBO'!I22</f>
         <v/>
       </c>
       <c r="I18" s="40">
-        <f>MAX(0,G18-H18)</f>
+        <f>MAX(0,G18-H18)+$B$5</f>
         <v/>
       </c>
       <c r="J18" s="40">
@@ -7383,7 +7331,7 @@
         <v/>
       </c>
       <c r="M18" s="40">
-        <f>'Юнитка FBO'!AG23</f>
+        <f>'Юнитка FBO'!AG22</f>
         <v/>
       </c>
       <c r="N18" s="40">
@@ -7397,11 +7345,11 @@
     </row>
     <row r="19">
       <c r="A19" s="39">
-        <f>'Юнитка FBO'!A24</f>
+        <f>'Юнитка FBO'!A23</f>
         <v/>
       </c>
       <c r="B19" s="40">
-        <f>'Юнитка FBO'!C24</f>
+        <f>'Юнитка FBO'!C23</f>
         <v/>
       </c>
       <c r="C19" s="40">
@@ -7409,7 +7357,7 @@
         <v/>
       </c>
       <c r="D19" s="40">
-        <f>'Юнитка FBO'!E24</f>
+        <f>'Юнитка FBO'!E23</f>
         <v/>
       </c>
       <c r="E19" s="40">
@@ -7417,19 +7365,19 @@
         <v/>
       </c>
       <c r="F19" s="40">
-        <f>'Юнитка FBO'!I24</f>
+        <f>'Юнитка FBO'!I23</f>
         <v/>
       </c>
       <c r="G19" s="40">
-        <f>'Юнитка FBO'!K24+'Юнитка FBO'!N24+'Юнитка FBO'!O24+'Юнитка FBO'!P24+'Юнитка FBO'!Q24+'Юнитка FBO'!R24+'Юнитка FBO'!S24+'Юнитка FBO'!V24+'Юнитка FBO'!X24+'Юнитка FBO'!Y24+'Юнитка FBO'!AK24</f>
+        <f>'Юнитка FBO'!K23+'Юнитка FBO'!N23+'Юнитка FBO'!O23+'Юнитка FBO'!P23+'Юнитка FBO'!Q23+'Юнитка FBO'!R23+'Юнитка FBO'!S23+'Юнитка FBO'!V23+'Юнитка FBO'!X23+'Юнитка FBO'!Y23+'Юнитка FBO'!AK23</f>
         <v/>
       </c>
       <c r="H19" s="40">
-        <f>'Юнитка FBO'!G24-'Юнитка FBO'!I24</f>
+        <f>'Юнитка FBO'!G23-'Юнитка FBO'!I23</f>
         <v/>
       </c>
       <c r="I19" s="40">
-        <f>MAX(0,G19-H19)</f>
+        <f>MAX(0,G19-H19)+$B$5</f>
         <v/>
       </c>
       <c r="J19" s="40">
@@ -7445,7 +7393,7 @@
         <v/>
       </c>
       <c r="M19" s="40">
-        <f>'Юнитка FBO'!AG24</f>
+        <f>'Юнитка FBO'!AG23</f>
         <v/>
       </c>
       <c r="N19" s="40">
@@ -7459,11 +7407,11 @@
     </row>
     <row r="20">
       <c r="A20" s="39">
-        <f>'Юнитка FBO'!A25</f>
+        <f>'Юнитка FBO'!A24</f>
         <v/>
       </c>
       <c r="B20" s="40">
-        <f>'Юнитка FBO'!C25</f>
+        <f>'Юнитка FBO'!C24</f>
         <v/>
       </c>
       <c r="C20" s="40">
@@ -7471,7 +7419,7 @@
         <v/>
       </c>
       <c r="D20" s="40">
-        <f>'Юнитка FBO'!E25</f>
+        <f>'Юнитка FBO'!E24</f>
         <v/>
       </c>
       <c r="E20" s="40">
@@ -7479,19 +7427,19 @@
         <v/>
       </c>
       <c r="F20" s="40">
-        <f>'Юнитка FBO'!I25</f>
+        <f>'Юнитка FBO'!I24</f>
         <v/>
       </c>
       <c r="G20" s="40">
-        <f>'Юнитка FBO'!K25+'Юнитка FBO'!N25+'Юнитка FBO'!O25+'Юнитка FBO'!P25+'Юнитка FBO'!Q25+'Юнитка FBO'!R25+'Юнитка FBO'!S25+'Юнитка FBO'!V25+'Юнитка FBO'!X25+'Юнитка FBO'!Y25+'Юнитка FBO'!AK25</f>
+        <f>'Юнитка FBO'!K24+'Юнитка FBO'!N24+'Юнитка FBO'!O24+'Юнитка FBO'!P24+'Юнитка FBO'!Q24+'Юнитка FBO'!R24+'Юнитка FBO'!S24+'Юнитка FBO'!V24+'Юнитка FBO'!X24+'Юнитка FBO'!Y24+'Юнитка FBO'!AK24</f>
         <v/>
       </c>
       <c r="H20" s="40">
-        <f>'Юнитка FBO'!G25-'Юнитка FBO'!I25</f>
+        <f>'Юнитка FBO'!G24-'Юнитка FBO'!I24</f>
         <v/>
       </c>
       <c r="I20" s="40">
-        <f>MAX(0,G20-H20)</f>
+        <f>MAX(0,G20-H20)+$B$5</f>
         <v/>
       </c>
       <c r="J20" s="40">
@@ -7507,7 +7455,7 @@
         <v/>
       </c>
       <c r="M20" s="40">
-        <f>'Юнитка FBO'!AG25</f>
+        <f>'Юнитка FBO'!AG24</f>
         <v/>
       </c>
       <c r="N20" s="40">
@@ -7521,11 +7469,11 @@
     </row>
     <row r="21">
       <c r="A21" s="39">
-        <f>'Юнитка FBO'!A26</f>
+        <f>'Юнитка FBO'!A25</f>
         <v/>
       </c>
       <c r="B21" s="40">
-        <f>'Юнитка FBO'!C26</f>
+        <f>'Юнитка FBO'!C25</f>
         <v/>
       </c>
       <c r="C21" s="40">
@@ -7533,7 +7481,7 @@
         <v/>
       </c>
       <c r="D21" s="40">
-        <f>'Юнитка FBO'!E26</f>
+        <f>'Юнитка FBO'!E25</f>
         <v/>
       </c>
       <c r="E21" s="40">
@@ -7541,19 +7489,19 @@
         <v/>
       </c>
       <c r="F21" s="40">
-        <f>'Юнитка FBO'!I26</f>
+        <f>'Юнитка FBO'!I25</f>
         <v/>
       </c>
       <c r="G21" s="40">
-        <f>'Юнитка FBO'!K26+'Юнитка FBO'!N26+'Юнитка FBO'!O26+'Юнитка FBO'!P26+'Юнитка FBO'!Q26+'Юнитка FBO'!R26+'Юнитка FBO'!S26+'Юнитка FBO'!V26+'Юнитка FBO'!X26+'Юнитка FBO'!Y26+'Юнитка FBO'!AK26</f>
+        <f>'Юнитка FBO'!K25+'Юнитка FBO'!N25+'Юнитка FBO'!O25+'Юнитка FBO'!P25+'Юнитка FBO'!Q25+'Юнитка FBO'!R25+'Юнитка FBO'!S25+'Юнитка FBO'!V25+'Юнитка FBO'!X25+'Юнитка FBO'!Y25+'Юнитка FBO'!AK25</f>
         <v/>
       </c>
       <c r="H21" s="40">
-        <f>'Юнитка FBO'!G26-'Юнитка FBO'!I26</f>
+        <f>'Юнитка FBO'!G25-'Юнитка FBO'!I25</f>
         <v/>
       </c>
       <c r="I21" s="40">
-        <f>MAX(0,G21-H21)</f>
+        <f>MAX(0,G21-H21)+$B$5</f>
         <v/>
       </c>
       <c r="J21" s="40">
@@ -7569,7 +7517,7 @@
         <v/>
       </c>
       <c r="M21" s="40">
-        <f>'Юнитка FBO'!AG26</f>
+        <f>'Юнитка FBO'!AG25</f>
         <v/>
       </c>
       <c r="N21" s="40">
@@ -7583,11 +7531,11 @@
     </row>
     <row r="22">
       <c r="A22" s="39">
-        <f>'Юнитка FBO'!A27</f>
+        <f>'Юнитка FBO'!A26</f>
         <v/>
       </c>
       <c r="B22" s="40">
-        <f>'Юнитка FBO'!C27</f>
+        <f>'Юнитка FBO'!C26</f>
         <v/>
       </c>
       <c r="C22" s="40">
@@ -7595,7 +7543,7 @@
         <v/>
       </c>
       <c r="D22" s="40">
-        <f>'Юнитка FBO'!E27</f>
+        <f>'Юнитка FBO'!E26</f>
         <v/>
       </c>
       <c r="E22" s="40">
@@ -7603,19 +7551,19 @@
         <v/>
       </c>
       <c r="F22" s="40">
-        <f>'Юнитка FBO'!I27</f>
+        <f>'Юнитка FBO'!I26</f>
         <v/>
       </c>
       <c r="G22" s="40">
-        <f>'Юнитка FBO'!K27+'Юнитка FBO'!N27+'Юнитка FBO'!O27+'Юнитка FBO'!P27+'Юнитка FBO'!Q27+'Юнитка FBO'!R27+'Юнитка FBO'!S27+'Юнитка FBO'!V27+'Юнитка FBO'!X27+'Юнитка FBO'!Y27+'Юнитка FBO'!AK27</f>
+        <f>'Юнитка FBO'!K26+'Юнитка FBO'!N26+'Юнитка FBO'!O26+'Юнитка FBO'!P26+'Юнитка FBO'!Q26+'Юнитка FBO'!R26+'Юнитка FBO'!S26+'Юнитка FBO'!V26+'Юнитка FBO'!X26+'Юнитка FBO'!Y26+'Юнитка FBO'!AK26</f>
         <v/>
       </c>
       <c r="H22" s="40">
-        <f>'Юнитка FBO'!G27-'Юнитка FBO'!I27</f>
+        <f>'Юнитка FBO'!G26-'Юнитка FBO'!I26</f>
         <v/>
       </c>
       <c r="I22" s="40">
-        <f>MAX(0,G22-H22)</f>
+        <f>MAX(0,G22-H22)+$B$5</f>
         <v/>
       </c>
       <c r="J22" s="40">
@@ -7631,7 +7579,7 @@
         <v/>
       </c>
       <c r="M22" s="40">
-        <f>'Юнитка FBO'!AG27</f>
+        <f>'Юнитка FBO'!AG26</f>
         <v/>
       </c>
       <c r="N22" s="40">
@@ -7645,11 +7593,11 @@
     </row>
     <row r="23">
       <c r="A23" s="39">
-        <f>'Юнитка FBO'!A28</f>
+        <f>'Юнитка FBO'!A27</f>
         <v/>
       </c>
       <c r="B23" s="40">
-        <f>'Юнитка FBO'!C28</f>
+        <f>'Юнитка FBO'!C27</f>
         <v/>
       </c>
       <c r="C23" s="40">
@@ -7657,7 +7605,7 @@
         <v/>
       </c>
       <c r="D23" s="40">
-        <f>'Юнитка FBO'!E28</f>
+        <f>'Юнитка FBO'!E27</f>
         <v/>
       </c>
       <c r="E23" s="40">
@@ -7665,19 +7613,19 @@
         <v/>
       </c>
       <c r="F23" s="40">
-        <f>'Юнитка FBO'!I28</f>
+        <f>'Юнитка FBO'!I27</f>
         <v/>
       </c>
       <c r="G23" s="40">
-        <f>'Юнитка FBO'!K28+'Юнитка FBO'!N28+'Юнитка FBO'!O28+'Юнитка FBO'!P28+'Юнитка FBO'!Q28+'Юнитка FBO'!R28+'Юнитка FBO'!S28+'Юнитка FBO'!V28+'Юнитка FBO'!X28+'Юнитка FBO'!Y28+'Юнитка FBO'!AK28</f>
+        <f>'Юнитка FBO'!K27+'Юнитка FBO'!N27+'Юнитка FBO'!O27+'Юнитка FBO'!P27+'Юнитка FBO'!Q27+'Юнитка FBO'!R27+'Юнитка FBO'!S27+'Юнитка FBO'!V27+'Юнитка FBO'!X27+'Юнитка FBO'!Y27+'Юнитка FBO'!AK27</f>
         <v/>
       </c>
       <c r="H23" s="40">
-        <f>'Юнитка FBO'!G28-'Юнитка FBO'!I28</f>
+        <f>'Юнитка FBO'!G27-'Юнитка FBO'!I27</f>
         <v/>
       </c>
       <c r="I23" s="40">
-        <f>MAX(0,G23-H23)</f>
+        <f>MAX(0,G23-H23)+$B$5</f>
         <v/>
       </c>
       <c r="J23" s="40">
@@ -7693,7 +7641,7 @@
         <v/>
       </c>
       <c r="M23" s="40">
-        <f>'Юнитка FBO'!AG28</f>
+        <f>'Юнитка FBO'!AG27</f>
         <v/>
       </c>
       <c r="N23" s="40">
@@ -7707,11 +7655,11 @@
     </row>
     <row r="24">
       <c r="A24" s="39">
-        <f>'Юнитка FBO'!A29</f>
+        <f>'Юнитка FBO'!A28</f>
         <v/>
       </c>
       <c r="B24" s="40">
-        <f>'Юнитка FBO'!C29</f>
+        <f>'Юнитка FBO'!C28</f>
         <v/>
       </c>
       <c r="C24" s="40">
@@ -7719,7 +7667,7 @@
         <v/>
       </c>
       <c r="D24" s="40">
-        <f>'Юнитка FBO'!E29</f>
+        <f>'Юнитка FBO'!E28</f>
         <v/>
       </c>
       <c r="E24" s="40">
@@ -7727,19 +7675,19 @@
         <v/>
       </c>
       <c r="F24" s="40">
-        <f>'Юнитка FBO'!I29</f>
+        <f>'Юнитка FBO'!I28</f>
         <v/>
       </c>
       <c r="G24" s="40">
-        <f>'Юнитка FBO'!K29+'Юнитка FBO'!N29+'Юнитка FBO'!O29+'Юнитка FBO'!P29+'Юнитка FBO'!Q29+'Юнитка FBO'!R29+'Юнитка FBO'!S29+'Юнитка FBO'!V29+'Юнитка FBO'!X29+'Юнитка FBO'!Y29+'Юнитка FBO'!AK29</f>
+        <f>'Юнитка FBO'!K28+'Юнитка FBO'!N28+'Юнитка FBO'!O28+'Юнитка FBO'!P28+'Юнитка FBO'!Q28+'Юнитка FBO'!R28+'Юнитка FBO'!S28+'Юнитка FBO'!V28+'Юнитка FBO'!X28+'Юнитка FBO'!Y28+'Юнитка FBO'!AK28</f>
         <v/>
       </c>
       <c r="H24" s="40">
-        <f>'Юнитка FBO'!G29-'Юнитка FBO'!I29</f>
+        <f>'Юнитка FBO'!G28-'Юнитка FBO'!I28</f>
         <v/>
       </c>
       <c r="I24" s="40">
-        <f>MAX(0,G24-H24)</f>
+        <f>MAX(0,G24-H24)+$B$5</f>
         <v/>
       </c>
       <c r="J24" s="40">
@@ -7755,7 +7703,7 @@
         <v/>
       </c>
       <c r="M24" s="40">
-        <f>'Юнитка FBO'!AG29</f>
+        <f>'Юнитка FBO'!AG28</f>
         <v/>
       </c>
       <c r="N24" s="40">
@@ -7769,11 +7717,11 @@
     </row>
     <row r="25">
       <c r="A25" s="39">
-        <f>'Юнитка FBO'!A30</f>
+        <f>'Юнитка FBO'!A29</f>
         <v/>
       </c>
       <c r="B25" s="40">
-        <f>'Юнитка FBO'!C30</f>
+        <f>'Юнитка FBO'!C29</f>
         <v/>
       </c>
       <c r="C25" s="40">
@@ -7781,7 +7729,7 @@
         <v/>
       </c>
       <c r="D25" s="40">
-        <f>'Юнитка FBO'!E30</f>
+        <f>'Юнитка FBO'!E29</f>
         <v/>
       </c>
       <c r="E25" s="40">
@@ -7789,19 +7737,19 @@
         <v/>
       </c>
       <c r="F25" s="40">
-        <f>'Юнитка FBO'!I30</f>
+        <f>'Юнитка FBO'!I29</f>
         <v/>
       </c>
       <c r="G25" s="40">
-        <f>'Юнитка FBO'!K30+'Юнитка FBO'!N30+'Юнитка FBO'!O30+'Юнитка FBO'!P30+'Юнитка FBO'!Q30+'Юнитка FBO'!R30+'Юнитка FBO'!S30+'Юнитка FBO'!V30+'Юнитка FBO'!X30+'Юнитка FBO'!Y30+'Юнитка FBO'!AK30</f>
+        <f>'Юнитка FBO'!K29+'Юнитка FBO'!N29+'Юнитка FBO'!O29+'Юнитка FBO'!P29+'Юнитка FBO'!Q29+'Юнитка FBO'!R29+'Юнитка FBO'!S29+'Юнитка FBO'!V29+'Юнитка FBO'!X29+'Юнитка FBO'!Y29+'Юнитка FBO'!AK29</f>
         <v/>
       </c>
       <c r="H25" s="40">
-        <f>'Юнитка FBO'!G30-'Юнитка FBO'!I30</f>
+        <f>'Юнитка FBO'!G29-'Юнитка FBO'!I29</f>
         <v/>
       </c>
       <c r="I25" s="40">
-        <f>MAX(0,G25-H25)</f>
+        <f>MAX(0,G25-H25)+$B$5</f>
         <v/>
       </c>
       <c r="J25" s="40">
@@ -7817,7 +7765,7 @@
         <v/>
       </c>
       <c r="M25" s="40">
-        <f>'Юнитка FBO'!AG30</f>
+        <f>'Юнитка FBO'!AG29</f>
         <v/>
       </c>
       <c r="N25" s="40">
@@ -7831,11 +7779,11 @@
     </row>
     <row r="26">
       <c r="A26" s="39">
-        <f>'Юнитка FBO'!A31</f>
+        <f>'Юнитка FBO'!A30</f>
         <v/>
       </c>
       <c r="B26" s="40">
-        <f>'Юнитка FBO'!C31</f>
+        <f>'Юнитка FBO'!C30</f>
         <v/>
       </c>
       <c r="C26" s="40">
@@ -7843,7 +7791,7 @@
         <v/>
       </c>
       <c r="D26" s="40">
-        <f>'Юнитка FBO'!E31</f>
+        <f>'Юнитка FBO'!E30</f>
         <v/>
       </c>
       <c r="E26" s="40">
@@ -7851,19 +7799,19 @@
         <v/>
       </c>
       <c r="F26" s="40">
-        <f>'Юнитка FBO'!I31</f>
+        <f>'Юнитка FBO'!I30</f>
         <v/>
       </c>
       <c r="G26" s="40">
-        <f>'Юнитка FBO'!K31+'Юнитка FBO'!N31+'Юнитка FBO'!O31+'Юнитка FBO'!P31+'Юнитка FBO'!Q31+'Юнитка FBO'!R31+'Юнитка FBO'!S31+'Юнитка FBO'!V31+'Юнитка FBO'!X31+'Юнитка FBO'!Y31+'Юнитка FBO'!AK31</f>
+        <f>'Юнитка FBO'!K30+'Юнитка FBO'!N30+'Юнитка FBO'!O30+'Юнитка FBO'!P30+'Юнитка FBO'!Q30+'Юнитка FBO'!R30+'Юнитка FBO'!S30+'Юнитка FBO'!V30+'Юнитка FBO'!X30+'Юнитка FBO'!Y30+'Юнитка FBO'!AK30</f>
         <v/>
       </c>
       <c r="H26" s="40">
-        <f>'Юнитка FBO'!G31-'Юнитка FBO'!I31</f>
+        <f>'Юнитка FBO'!G30-'Юнитка FBO'!I30</f>
         <v/>
       </c>
       <c r="I26" s="40">
-        <f>MAX(0,G26-H26)</f>
+        <f>MAX(0,G26-H26)+$B$5</f>
         <v/>
       </c>
       <c r="J26" s="40">
@@ -7879,7 +7827,7 @@
         <v/>
       </c>
       <c r="M26" s="40">
-        <f>'Юнитка FBO'!AG31</f>
+        <f>'Юнитка FBO'!AG30</f>
         <v/>
       </c>
       <c r="N26" s="40">
@@ -7893,11 +7841,11 @@
     </row>
     <row r="27">
       <c r="A27" s="39">
-        <f>'Юнитка FBO'!A32</f>
+        <f>'Юнитка FBO'!A31</f>
         <v/>
       </c>
       <c r="B27" s="40">
-        <f>'Юнитка FBO'!C32</f>
+        <f>'Юнитка FBO'!C31</f>
         <v/>
       </c>
       <c r="C27" s="40">
@@ -7905,7 +7853,7 @@
         <v/>
       </c>
       <c r="D27" s="40">
-        <f>'Юнитка FBO'!E32</f>
+        <f>'Юнитка FBO'!E31</f>
         <v/>
       </c>
       <c r="E27" s="40">
@@ -7913,19 +7861,19 @@
         <v/>
       </c>
       <c r="F27" s="40">
-        <f>'Юнитка FBO'!I32</f>
+        <f>'Юнитка FBO'!I31</f>
         <v/>
       </c>
       <c r="G27" s="40">
-        <f>'Юнитка FBO'!K32+'Юнитка FBO'!N32+'Юнитка FBO'!O32+'Юнитка FBO'!P32+'Юнитка FBO'!Q32+'Юнитка FBO'!R32+'Юнитка FBO'!S32+'Юнитка FBO'!V32+'Юнитка FBO'!X32+'Юнитка FBO'!Y32+'Юнитка FBO'!AK32</f>
+        <f>'Юнитка FBO'!K31+'Юнитка FBO'!N31+'Юнитка FBO'!O31+'Юнитка FBO'!P31+'Юнитка FBO'!Q31+'Юнитка FBO'!R31+'Юнитка FBO'!S31+'Юнитка FBO'!V31+'Юнитка FBO'!X31+'Юнитка FBO'!Y31+'Юнитка FBO'!AK31</f>
         <v/>
       </c>
       <c r="H27" s="40">
-        <f>'Юнитка FBO'!G32-'Юнитка FBO'!I32</f>
+        <f>'Юнитка FBO'!G31-'Юнитка FBO'!I31</f>
         <v/>
       </c>
       <c r="I27" s="40">
-        <f>MAX(0,G27-H27)</f>
+        <f>MAX(0,G27-H27)+$B$5</f>
         <v/>
       </c>
       <c r="J27" s="40">
@@ -7941,7 +7889,7 @@
         <v/>
       </c>
       <c r="M27" s="40">
-        <f>'Юнитка FBO'!AG32</f>
+        <f>'Юнитка FBO'!AG31</f>
         <v/>
       </c>
       <c r="N27" s="40">
@@ -7955,11 +7903,11 @@
     </row>
     <row r="28">
       <c r="A28" s="39">
-        <f>'Юнитка FBO'!A33</f>
+        <f>'Юнитка FBO'!A32</f>
         <v/>
       </c>
       <c r="B28" s="40">
-        <f>'Юнитка FBO'!C33</f>
+        <f>'Юнитка FBO'!C32</f>
         <v/>
       </c>
       <c r="C28" s="40">
@@ -7967,7 +7915,7 @@
         <v/>
       </c>
       <c r="D28" s="40">
-        <f>'Юнитка FBO'!E33</f>
+        <f>'Юнитка FBO'!E32</f>
         <v/>
       </c>
       <c r="E28" s="40">
@@ -7975,19 +7923,19 @@
         <v/>
       </c>
       <c r="F28" s="40">
-        <f>'Юнитка FBO'!I33</f>
+        <f>'Юнитка FBO'!I32</f>
         <v/>
       </c>
       <c r="G28" s="40">
-        <f>'Юнитка FBO'!K33+'Юнитка FBO'!N33+'Юнитка FBO'!O33+'Юнитка FBO'!P33+'Юнитка FBO'!Q33+'Юнитка FBO'!R33+'Юнитка FBO'!S33+'Юнитка FBO'!V33+'Юнитка FBO'!X33+'Юнитка FBO'!Y33+'Юнитка FBO'!AK33</f>
+        <f>'Юнитка FBO'!K32+'Юнитка FBO'!N32+'Юнитка FBO'!O32+'Юнитка FBO'!P32+'Юнитка FBO'!Q32+'Юнитка FBO'!R32+'Юнитка FBO'!S32+'Юнитка FBO'!V32+'Юнитка FBO'!X32+'Юнитка FBO'!Y32+'Юнитка FBO'!AK32</f>
         <v/>
       </c>
       <c r="H28" s="40">
-        <f>'Юнитка FBO'!G33-'Юнитка FBO'!I33</f>
+        <f>'Юнитка FBO'!G32-'Юнитка FBO'!I32</f>
         <v/>
       </c>
       <c r="I28" s="40">
-        <f>MAX(0,G28-H28)</f>
+        <f>MAX(0,G28-H28)+$B$5</f>
         <v/>
       </c>
       <c r="J28" s="40">
@@ -8003,7 +7951,7 @@
         <v/>
       </c>
       <c r="M28" s="40">
-        <f>'Юнитка FBO'!AG33</f>
+        <f>'Юнитка FBO'!AG32</f>
         <v/>
       </c>
       <c r="N28" s="40">
@@ -8017,11 +7965,11 @@
     </row>
     <row r="29">
       <c r="A29" s="39">
-        <f>'Юнитка FBO'!A34</f>
+        <f>'Юнитка FBO'!A33</f>
         <v/>
       </c>
       <c r="B29" s="40">
-        <f>'Юнитка FBO'!C34</f>
+        <f>'Юнитка FBO'!C33</f>
         <v/>
       </c>
       <c r="C29" s="40">
@@ -8029,7 +7977,7 @@
         <v/>
       </c>
       <c r="D29" s="40">
-        <f>'Юнитка FBO'!E34</f>
+        <f>'Юнитка FBO'!E33</f>
         <v/>
       </c>
       <c r="E29" s="40">
@@ -8037,19 +7985,19 @@
         <v/>
       </c>
       <c r="F29" s="40">
-        <f>'Юнитка FBO'!I34</f>
+        <f>'Юнитка FBO'!I33</f>
         <v/>
       </c>
       <c r="G29" s="40">
-        <f>'Юнитка FBO'!K34+'Юнитка FBO'!N34+'Юнитка FBO'!O34+'Юнитка FBO'!P34+'Юнитка FBO'!Q34+'Юнитка FBO'!R34+'Юнитка FBO'!S34+'Юнитка FBO'!V34+'Юнитка FBO'!X34+'Юнитка FBO'!Y34+'Юнитка FBO'!AK34</f>
+        <f>'Юнитка FBO'!K33+'Юнитка FBO'!N33+'Юнитка FBO'!O33+'Юнитка FBO'!P33+'Юнитка FBO'!Q33+'Юнитка FBO'!R33+'Юнитка FBO'!S33+'Юнитка FBO'!V33+'Юнитка FBO'!X33+'Юнитка FBO'!Y33+'Юнитка FBO'!AK33</f>
         <v/>
       </c>
       <c r="H29" s="40">
-        <f>'Юнитка FBO'!G34-'Юнитка FBO'!I34</f>
+        <f>'Юнитка FBO'!G33-'Юнитка FBO'!I33</f>
         <v/>
       </c>
       <c r="I29" s="40">
-        <f>MAX(0,G29-H29)</f>
+        <f>MAX(0,G29-H29)+$B$5</f>
         <v/>
       </c>
       <c r="J29" s="40">
@@ -8065,7 +8013,7 @@
         <v/>
       </c>
       <c r="M29" s="40">
-        <f>'Юнитка FBO'!AG34</f>
+        <f>'Юнитка FBO'!AG33</f>
         <v/>
       </c>
       <c r="N29" s="40">
@@ -8079,11 +8027,11 @@
     </row>
     <row r="30">
       <c r="A30" s="39">
-        <f>'Юнитка FBO'!A35</f>
+        <f>'Юнитка FBO'!A34</f>
         <v/>
       </c>
       <c r="B30" s="40">
-        <f>'Юнитка FBO'!C35</f>
+        <f>'Юнитка FBO'!C34</f>
         <v/>
       </c>
       <c r="C30" s="40">
@@ -8091,7 +8039,7 @@
         <v/>
       </c>
       <c r="D30" s="40">
-        <f>'Юнитка FBO'!E35</f>
+        <f>'Юнитка FBO'!E34</f>
         <v/>
       </c>
       <c r="E30" s="40">
@@ -8099,19 +8047,19 @@
         <v/>
       </c>
       <c r="F30" s="40">
-        <f>'Юнитка FBO'!I35</f>
+        <f>'Юнитка FBO'!I34</f>
         <v/>
       </c>
       <c r="G30" s="40">
-        <f>'Юнитка FBO'!K35+'Юнитка FBO'!N35+'Юнитка FBO'!O35+'Юнитка FBO'!P35+'Юнитка FBO'!Q35+'Юнитка FBO'!R35+'Юнитка FBO'!S35+'Юнитка FBO'!V35+'Юнитка FBO'!X35+'Юнитка FBO'!Y35+'Юнитка FBO'!AK35</f>
+        <f>'Юнитка FBO'!K34+'Юнитка FBO'!N34+'Юнитка FBO'!O34+'Юнитка FBO'!P34+'Юнитка FBO'!Q34+'Юнитка FBO'!R34+'Юнитка FBO'!S34+'Юнитка FBO'!V34+'Юнитка FBO'!X34+'Юнитка FBO'!Y34+'Юнитка FBO'!AK34</f>
         <v/>
       </c>
       <c r="H30" s="40">
-        <f>'Юнитка FBO'!G35-'Юнитка FBO'!I35</f>
+        <f>'Юнитка FBO'!G34-'Юнитка FBO'!I34</f>
         <v/>
       </c>
       <c r="I30" s="40">
-        <f>MAX(0,G30-H30)</f>
+        <f>MAX(0,G30-H30)+$B$5</f>
         <v/>
       </c>
       <c r="J30" s="40">
@@ -8127,7 +8075,7 @@
         <v/>
       </c>
       <c r="M30" s="40">
-        <f>'Юнитка FBO'!AG35</f>
+        <f>'Юнитка FBO'!AG34</f>
         <v/>
       </c>
       <c r="N30" s="40">
@@ -8140,136 +8088,178 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="42" t="inlineStr">
+      <c r="A31" s="39">
+        <f>'Юнитка FBO'!A35</f>
+        <v/>
+      </c>
+      <c r="B31" s="40">
+        <f>'Юнитка FBO'!C35</f>
+        <v/>
+      </c>
+      <c r="C31" s="40">
+        <f>B31*$B$2</f>
+        <v/>
+      </c>
+      <c r="D31" s="40">
+        <f>'Юнитка FBO'!E35</f>
+        <v/>
+      </c>
+      <c r="E31" s="40">
+        <f>ROUND(D31*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F31" s="40">
+        <f>'Юнитка FBO'!I35</f>
+        <v/>
+      </c>
+      <c r="G31" s="40">
+        <f>'Юнитка FBO'!K35+'Юнитка FBO'!N35+'Юнитка FBO'!O35+'Юнитка FBO'!P35+'Юнитка FBO'!Q35+'Юнитка FBO'!R35+'Юнитка FBO'!S35+'Юнитка FBO'!V35+'Юнитка FBO'!X35+'Юнитка FBO'!Y35+'Юнитка FBO'!AK35</f>
+        <v/>
+      </c>
+      <c r="H31" s="40">
+        <f>'Юнитка FBO'!G35-'Юнитка FBO'!I35</f>
+        <v/>
+      </c>
+      <c r="I31" s="40">
+        <f>MAX(0,G31-H31)+$B$5</f>
+        <v/>
+      </c>
+      <c r="J31" s="40">
+        <f>E31*I31</f>
+        <v/>
+      </c>
+      <c r="K31" s="40">
+        <f>C31+J31</f>
+        <v/>
+      </c>
+      <c r="L31" s="40">
+        <f>ROUND(D31*$B$4,0)</f>
+        <v/>
+      </c>
+      <c r="M31" s="40">
+        <f>'Юнитка FBO'!AG35</f>
+        <v/>
+      </c>
+      <c r="N31" s="40">
+        <f>L31*M31</f>
+        <v/>
+      </c>
+      <c r="O31" s="41">
+        <f>IF(N31&gt;0,K31/N31,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="42" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B31" s="43">
-        <f>SUM(B8:B30)</f>
-        <v/>
-      </c>
-      <c r="C31" s="43">
-        <f>SUM(C8:C30)</f>
-        <v/>
-      </c>
-      <c r="D31" s="43">
-        <f>SUM(D8:D30)</f>
-        <v/>
-      </c>
-      <c r="E31" s="43">
-        <f>SUM(E8:E30)</f>
-        <v/>
-      </c>
-      <c r="F31" s="42" t="n"/>
-      <c r="G31" s="42" t="n"/>
-      <c r="H31" s="42" t="n"/>
-      <c r="I31" s="42" t="n"/>
-      <c r="J31" s="43">
-        <f>SUM(J8:J30)</f>
-        <v/>
-      </c>
-      <c r="K31" s="43">
-        <f>SUM(K8:K30)</f>
-        <v/>
-      </c>
-      <c r="L31" s="43">
-        <f>SUM(L8:L30)</f>
-        <v/>
-      </c>
-      <c r="M31" s="42" t="n"/>
-      <c r="N31" s="43">
-        <f>SUM(N8:N30)</f>
-        <v/>
-      </c>
-      <c r="O31" s="44">
-        <f>IF(N31&gt;0,K31/N31,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="45" t="inlineStr">
+      <c r="B32" s="43">
+        <f>SUM(B9:B31)</f>
+        <v/>
+      </c>
+      <c r="C32" s="43">
+        <f>SUM(C9:C31)</f>
+        <v/>
+      </c>
+      <c r="D32" s="43">
+        <f>SUM(D9:D31)</f>
+        <v/>
+      </c>
+      <c r="E32" s="43">
+        <f>SUM(E9:E31)</f>
+        <v/>
+      </c>
+      <c r="F32" s="42" t="n"/>
+      <c r="G32" s="42" t="n"/>
+      <c r="H32" s="42" t="n"/>
+      <c r="I32" s="42" t="n"/>
+      <c r="J32" s="43">
+        <f>SUM(J9:J31)</f>
+        <v/>
+      </c>
+      <c r="K32" s="43">
+        <f>SUM(K9:K31)</f>
+        <v/>
+      </c>
+      <c r="L32" s="43">
+        <f>SUM(L9:L31)</f>
+        <v/>
+      </c>
+      <c r="M32" s="42" t="n"/>
+      <c r="N32" s="43">
+        <f>SUM(N9:N31)</f>
+        <v/>
+      </c>
+      <c r="O32" s="44">
+        <f>IF(N32&gt;0,K32/N32,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="45" t="inlineStr">
         <is>
           <t>Денежный поток по месяцам</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="38" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="38" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B35" s="38" t="inlineStr">
+      <c r="B36" s="38" t="inlineStr">
         <is>
           <t>Расходы (накрутка), ₽</t>
         </is>
       </c>
-      <c r="C35" s="38" t="inlineStr">
+      <c r="C36" s="38" t="inlineStr">
         <is>
           <t>Прибыль от продаж, ₽</t>
         </is>
       </c>
-      <c r="D35" s="38" t="inlineStr">
+      <c r="D36" s="38" t="inlineStr">
         <is>
           <t>Чистый поток, ₽</t>
         </is>
       </c>
-      <c r="E35" s="38" t="inlineStr">
+      <c r="E36" s="38" t="inlineStr">
         <is>
           <t>Накопительно, ₽</t>
         </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="B36" s="40">
-        <f>$K$31</f>
-        <v/>
-      </c>
-      <c r="C36" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="40">
-        <f>C36-B36</f>
-        <v/>
-      </c>
-      <c r="E36" s="40">
-        <f>D36</f>
-        <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="B37" s="40" t="n">
+        <v>1</v>
+      </c>
+      <c r="B37" s="40">
+        <f>$K$32</f>
+        <v/>
+      </c>
+      <c r="C37" s="40" t="n">
         <v>0</v>
-      </c>
-      <c r="C37" s="40">
-        <f>$N$31</f>
-        <v/>
       </c>
       <c r="D37" s="40">
         <f>C37-B37</f>
         <v/>
       </c>
       <c r="E37" s="40">
-        <f>E36+D37</f>
+        <f>D37</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B38" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D38" s="40">
@@ -8283,13 +8273,13 @@
     </row>
     <row r="39">
       <c r="A39" s="39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B39" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D39" s="40">
@@ -8303,13 +8293,13 @@
     </row>
     <row r="40">
       <c r="A40" s="39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C40" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D40" s="40">
@@ -8323,13 +8313,13 @@
     </row>
     <row r="41">
       <c r="A41" s="39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B41" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C41" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D41" s="40">
@@ -8343,13 +8333,13 @@
     </row>
     <row r="42">
       <c r="A42" s="39" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B42" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C42" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D42" s="40">
@@ -8363,13 +8353,13 @@
     </row>
     <row r="43">
       <c r="A43" s="39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B43" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C43" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D43" s="40">
@@ -8383,13 +8373,13 @@
     </row>
     <row r="44">
       <c r="A44" s="39" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B44" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C44" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D44" s="40">
@@ -8403,13 +8393,13 @@
     </row>
     <row r="45">
       <c r="A45" s="39" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B45" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C45" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D45" s="40">
@@ -8423,13 +8413,13 @@
     </row>
     <row r="46">
       <c r="A46" s="39" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C46" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D46" s="40">
@@ -8443,13 +8433,13 @@
     </row>
     <row r="47">
       <c r="A47" s="39" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47" s="40" t="n">
         <v>0</v>
       </c>
       <c r="C47" s="40">
-        <f>$N$31</f>
+        <f>$N$32</f>
         <v/>
       </c>
       <c r="D47" s="40">
@@ -8461,47 +8451,67 @@
         <v/>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="34" t="inlineStr">
-        <is>
-          <t>Разовые расходы на раскрутку (1-й мес), ₽</t>
-        </is>
-      </c>
-      <c r="B49" s="43">
-        <f>$K$31</f>
+    <row r="48">
+      <c r="A48" s="39" t="n">
+        <v>12</v>
+      </c>
+      <c r="B48" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="40">
+        <f>$N$32</f>
+        <v/>
+      </c>
+      <c r="D48" s="40">
+        <f>C48-B48</f>
+        <v/>
+      </c>
+      <c r="E48" s="40">
+        <f>E47+D48</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="34" t="inlineStr">
         <is>
-          <t>Прибыль в месяц (со 2-го мес), ₽</t>
+          <t>Разовые расходы на раскрутку (1-й мес), ₽</t>
         </is>
       </c>
       <c r="B50" s="43">
-        <f>$N$31</f>
+        <f>$K$32</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="34" t="inlineStr">
         <is>
-          <t>Окупаемость раскрутки, мес продаж</t>
-        </is>
-      </c>
-      <c r="B51" s="44">
-        <f>IF($N$31&gt;0,$K$31/$N$31,"—")</f>
+          <t>Прибыль в месяц (со 2-го мес), ₽</t>
+        </is>
+      </c>
+      <c r="B51" s="43">
+        <f>$N$32</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="34" t="inlineStr">
         <is>
+          <t>Окупаемость раскрутки, мес продаж</t>
+        </is>
+      </c>
+      <c r="B52" s="44">
+        <f>IF($N$32&gt;0,$K$32/$N$32,"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="34" t="inlineStr">
+        <is>
           <t>Выход в плюс с запуска, мес</t>
         </is>
       </c>
-      <c r="B52" s="44">
-        <f>IF($N$31&gt;0,1+$K$31/$N$31,"—")</f>
+      <c r="B53" s="44">
+        <f>IF($N$32&gt;0,1+$K$32/$N$32,"—")</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
+++ b/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
@@ -298,11 +298,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6572,7 +6572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O53"/>
+  <dimension ref="A1:M48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6586,10 +6586,8 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6622,176 +6620,114 @@
     <row r="4">
       <c r="A4" s="34" t="inlineStr">
         <is>
-          <t>Доля наших продаж от конкурента (со 2-го мес)</t>
-        </is>
-      </c>
-      <c r="B4" s="36" t="n">
-        <v>0.5</v>
+          <t>Прочие расходы на 1 самовыкуп, ₽ (забор с ПВЗ, оформление)</t>
+        </is>
+      </c>
+      <c r="B4" s="35" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="34" t="inlineStr">
         <is>
-          <t>Прочие расходы на 1 самовыкуп, ₽ (забор с ПВЗ, оформление)</t>
-        </is>
-      </c>
-      <c r="B5" s="35" t="n">
-        <v>50</v>
+          <t>Стартовая доля продаж от конкурента (1-й мес продаж)</t>
+        </is>
+      </c>
+      <c r="B5" s="36" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="37" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
+        <is>
+          <t>Ежемесячный рост доли продаж, +п.п.</t>
+        </is>
+      </c>
+      <c r="B6" s="36" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="37" t="inlineStr">
         <is>
           <t>Самовыкуп: платим цену с СПП (покупатель), получаем выплату Ozon с цены продавца (СПП финансирует Ozon), товар возвращается на склад → теряем только сборы Ozon сверх компенсации СПП + прочие расходы.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="48" customHeight="1">
-      <c r="A8" s="38" t="inlineStr">
+    <row r="9" ht="48" customHeight="1">
+      <c r="A9" s="38" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="B8" s="38" t="inlineStr">
+      <c r="B9" s="38" t="inlineStr">
         <is>
           <t>Отзывов, шт</t>
         </is>
       </c>
-      <c r="C8" s="38" t="inlineStr">
+      <c r="C9" s="38" t="inlineStr">
         <is>
           <t>Отзывы, ₽</t>
         </is>
       </c>
-      <c r="D8" s="38" t="inlineStr">
+      <c r="D9" s="38" t="inlineStr">
         <is>
           <t>Заказы конкур., шт</t>
         </is>
       </c>
-      <c r="E8" s="38" t="inlineStr">
+      <c r="E9" s="38" t="inlineStr">
         <is>
           <t>Самовыкупов, шт</t>
         </is>
       </c>
-      <c r="F8" s="38" t="inlineStr">
+      <c r="F9" s="38" t="inlineStr">
         <is>
           <t>Цена выкупа (с СПП), ₽</t>
         </is>
       </c>
-      <c r="G8" s="38" t="inlineStr">
+      <c r="G9" s="38" t="inlineStr">
         <is>
           <t>Сборы Ozon / выкуп, ₽</t>
         </is>
       </c>
-      <c r="H8" s="38" t="inlineStr">
+      <c r="H9" s="38" t="inlineStr">
         <is>
           <t>Компенсация СПП, ₽</t>
         </is>
       </c>
-      <c r="I8" s="38" t="inlineStr">
+      <c r="I9" s="38" t="inlineStr">
         <is>
           <t>Безвозврат / выкуп, ₽</t>
         </is>
       </c>
-      <c r="J8" s="38" t="inlineStr">
+      <c r="J9" s="38" t="inlineStr">
         <is>
           <t>Самовыкупы, ₽</t>
         </is>
       </c>
-      <c r="K8" s="38" t="inlineStr">
+      <c r="K9" s="38" t="inlineStr">
         <is>
           <t>Расходы 1-й мес, ₽</t>
         </is>
       </c>
-      <c r="L8" s="38" t="inlineStr">
-        <is>
-          <t>Продаж/мес (со 2-го), шт</t>
-        </is>
-      </c>
-      <c r="M8" s="38" t="inlineStr">
+      <c r="L9" s="38" t="inlineStr">
         <is>
           <t>Маржа/шт, ₽</t>
         </is>
       </c>
-      <c r="N8" s="38" t="inlineStr">
-        <is>
-          <t>Прибыль/мес (со 2-го), ₽</t>
-        </is>
-      </c>
-      <c r="O8" s="38" t="inlineStr">
-        <is>
-          <t>Окупаемость, мес</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="39">
-        <f>'Юнитка FBO'!A13</f>
-        <v/>
-      </c>
-      <c r="B9" s="40">
-        <f>'Юнитка FBO'!C13</f>
-        <v/>
-      </c>
-      <c r="C9" s="40">
-        <f>B9*$B$2</f>
-        <v/>
-      </c>
-      <c r="D9" s="40">
-        <f>'Юнитка FBO'!E13</f>
-        <v/>
-      </c>
-      <c r="E9" s="40">
-        <f>ROUND(D9*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F9" s="40">
-        <f>'Юнитка FBO'!I13</f>
-        <v/>
-      </c>
-      <c r="G9" s="40">
-        <f>'Юнитка FBO'!K13+'Юнитка FBO'!N13+'Юнитка FBO'!O13+'Юнитка FBO'!P13+'Юнитка FBO'!Q13+'Юнитка FBO'!R13+'Юнитка FBO'!S13+'Юнитка FBO'!V13+'Юнитка FBO'!X13+'Юнитка FBO'!Y13+'Юнитка FBO'!AK13</f>
-        <v/>
-      </c>
-      <c r="H9" s="40">
-        <f>'Юнитка FBO'!G13-'Юнитка FBO'!I13</f>
-        <v/>
-      </c>
-      <c r="I9" s="40">
-        <f>MAX(0,G9-H9)+$B$5</f>
-        <v/>
-      </c>
-      <c r="J9" s="40">
-        <f>E9*I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="40">
-        <f>C9+J9</f>
-        <v/>
-      </c>
-      <c r="L9" s="40">
-        <f>ROUND(D9*$B$4,0)</f>
-        <v/>
-      </c>
-      <c r="M9" s="40">
-        <f>'Юнитка FBO'!AG13</f>
-        <v/>
-      </c>
-      <c r="N9" s="40">
-        <f>L9*M9</f>
-        <v/>
-      </c>
-      <c r="O9" s="41">
-        <f>IF(N9&gt;0,K9/N9,"—")</f>
-        <v/>
+      <c r="M9" s="38" t="inlineStr">
+        <is>
+          <t>Прибыль/мес при 100% конкурента, ₽</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="39">
-        <f>'Юнитка FBO'!A14</f>
+        <f>'Юнитка FBO'!A13</f>
         <v/>
       </c>
       <c r="B10" s="40">
-        <f>'Юнитка FBO'!C14</f>
+        <f>'Юнитка FBO'!C13</f>
         <v/>
       </c>
       <c r="C10" s="40">
@@ -6799,7 +6735,7 @@
         <v/>
       </c>
       <c r="D10" s="40">
-        <f>'Юнитка FBO'!E14</f>
+        <f>'Юнитка FBO'!E13</f>
         <v/>
       </c>
       <c r="E10" s="40">
@@ -6807,19 +6743,19 @@
         <v/>
       </c>
       <c r="F10" s="40">
-        <f>'Юнитка FBO'!I14</f>
+        <f>'Юнитка FBO'!I13</f>
         <v/>
       </c>
       <c r="G10" s="40">
-        <f>'Юнитка FBO'!K14+'Юнитка FBO'!N14+'Юнитка FBO'!O14+'Юнитка FBO'!P14+'Юнитка FBO'!Q14+'Юнитка FBO'!R14+'Юнитка FBO'!S14+'Юнитка FBO'!V14+'Юнитка FBO'!X14+'Юнитка FBO'!Y14+'Юнитка FBO'!AK14</f>
+        <f>'Юнитка FBO'!K13+'Юнитка FBO'!N13+'Юнитка FBO'!O13+'Юнитка FBO'!P13+'Юнитка FBO'!Q13+'Юнитка FBO'!R13+'Юнитка FBO'!S13+'Юнитка FBO'!V13+'Юнитка FBO'!X13+'Юнитка FBO'!Y13+'Юнитка FBO'!AK13</f>
         <v/>
       </c>
       <c r="H10" s="40">
-        <f>'Юнитка FBO'!G14-'Юнитка FBO'!I14</f>
+        <f>'Юнитка FBO'!G13-'Юнитка FBO'!I13</f>
         <v/>
       </c>
       <c r="I10" s="40">
-        <f>MAX(0,G10-H10)+$B$5</f>
+        <f>MAX(0,G10-H10)+$B$4</f>
         <v/>
       </c>
       <c r="J10" s="40">
@@ -6831,29 +6767,21 @@
         <v/>
       </c>
       <c r="L10" s="40">
-        <f>ROUND(D10*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG13</f>
         <v/>
       </c>
       <c r="M10" s="40">
-        <f>'Юнитка FBO'!AG14</f>
-        <v/>
-      </c>
-      <c r="N10" s="40">
-        <f>L10*M10</f>
-        <v/>
-      </c>
-      <c r="O10" s="41">
-        <f>IF(N10&gt;0,K10/N10,"—")</f>
+        <f>D10*L10</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="39">
-        <f>'Юнитка FBO'!A15</f>
+        <f>'Юнитка FBO'!A14</f>
         <v/>
       </c>
       <c r="B11" s="40">
-        <f>'Юнитка FBO'!C15</f>
+        <f>'Юнитка FBO'!C14</f>
         <v/>
       </c>
       <c r="C11" s="40">
@@ -6861,7 +6789,7 @@
         <v/>
       </c>
       <c r="D11" s="40">
-        <f>'Юнитка FBO'!E15</f>
+        <f>'Юнитка FBO'!E14</f>
         <v/>
       </c>
       <c r="E11" s="40">
@@ -6869,19 +6797,19 @@
         <v/>
       </c>
       <c r="F11" s="40">
-        <f>'Юнитка FBO'!I15</f>
+        <f>'Юнитка FBO'!I14</f>
         <v/>
       </c>
       <c r="G11" s="40">
-        <f>'Юнитка FBO'!K15+'Юнитка FBO'!N15+'Юнитка FBO'!O15+'Юнитка FBO'!P15+'Юнитка FBO'!Q15+'Юнитка FBO'!R15+'Юнитка FBO'!S15+'Юнитка FBO'!V15+'Юнитка FBO'!X15+'Юнитка FBO'!Y15+'Юнитка FBO'!AK15</f>
+        <f>'Юнитка FBO'!K14+'Юнитка FBO'!N14+'Юнитка FBO'!O14+'Юнитка FBO'!P14+'Юнитка FBO'!Q14+'Юнитка FBO'!R14+'Юнитка FBO'!S14+'Юнитка FBO'!V14+'Юнитка FBO'!X14+'Юнитка FBO'!Y14+'Юнитка FBO'!AK14</f>
         <v/>
       </c>
       <c r="H11" s="40">
-        <f>'Юнитка FBO'!G15-'Юнитка FBO'!I15</f>
+        <f>'Юнитка FBO'!G14-'Юнитка FBO'!I14</f>
         <v/>
       </c>
       <c r="I11" s="40">
-        <f>MAX(0,G11-H11)+$B$5</f>
+        <f>MAX(0,G11-H11)+$B$4</f>
         <v/>
       </c>
       <c r="J11" s="40">
@@ -6893,29 +6821,21 @@
         <v/>
       </c>
       <c r="L11" s="40">
-        <f>ROUND(D11*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG14</f>
         <v/>
       </c>
       <c r="M11" s="40">
-        <f>'Юнитка FBO'!AG15</f>
-        <v/>
-      </c>
-      <c r="N11" s="40">
-        <f>L11*M11</f>
-        <v/>
-      </c>
-      <c r="O11" s="41">
-        <f>IF(N11&gt;0,K11/N11,"—")</f>
+        <f>D11*L11</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="39">
-        <f>'Юнитка FBO'!A16</f>
+        <f>'Юнитка FBO'!A15</f>
         <v/>
       </c>
       <c r="B12" s="40">
-        <f>'Юнитка FBO'!C16</f>
+        <f>'Юнитка FBO'!C15</f>
         <v/>
       </c>
       <c r="C12" s="40">
@@ -6923,7 +6843,7 @@
         <v/>
       </c>
       <c r="D12" s="40">
-        <f>'Юнитка FBO'!E16</f>
+        <f>'Юнитка FBO'!E15</f>
         <v/>
       </c>
       <c r="E12" s="40">
@@ -6931,19 +6851,19 @@
         <v/>
       </c>
       <c r="F12" s="40">
-        <f>'Юнитка FBO'!I16</f>
+        <f>'Юнитка FBO'!I15</f>
         <v/>
       </c>
       <c r="G12" s="40">
-        <f>'Юнитка FBO'!K16+'Юнитка FBO'!N16+'Юнитка FBO'!O16+'Юнитка FBO'!P16+'Юнитка FBO'!Q16+'Юнитка FBO'!R16+'Юнитка FBO'!S16+'Юнитка FBO'!V16+'Юнитка FBO'!X16+'Юнитка FBO'!Y16+'Юнитка FBO'!AK16</f>
+        <f>'Юнитка FBO'!K15+'Юнитка FBO'!N15+'Юнитка FBO'!O15+'Юнитка FBO'!P15+'Юнитка FBO'!Q15+'Юнитка FBO'!R15+'Юнитка FBO'!S15+'Юнитка FBO'!V15+'Юнитка FBO'!X15+'Юнитка FBO'!Y15+'Юнитка FBO'!AK15</f>
         <v/>
       </c>
       <c r="H12" s="40">
-        <f>'Юнитка FBO'!G16-'Юнитка FBO'!I16</f>
+        <f>'Юнитка FBO'!G15-'Юнитка FBO'!I15</f>
         <v/>
       </c>
       <c r="I12" s="40">
-        <f>MAX(0,G12-H12)+$B$5</f>
+        <f>MAX(0,G12-H12)+$B$4</f>
         <v/>
       </c>
       <c r="J12" s="40">
@@ -6955,29 +6875,21 @@
         <v/>
       </c>
       <c r="L12" s="40">
-        <f>ROUND(D12*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG15</f>
         <v/>
       </c>
       <c r="M12" s="40">
-        <f>'Юнитка FBO'!AG16</f>
-        <v/>
-      </c>
-      <c r="N12" s="40">
-        <f>L12*M12</f>
-        <v/>
-      </c>
-      <c r="O12" s="41">
-        <f>IF(N12&gt;0,K12/N12,"—")</f>
+        <f>D12*L12</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="39">
-        <f>'Юнитка FBO'!A17</f>
+        <f>'Юнитка FBO'!A16</f>
         <v/>
       </c>
       <c r="B13" s="40">
-        <f>'Юнитка FBO'!C17</f>
+        <f>'Юнитка FBO'!C16</f>
         <v/>
       </c>
       <c r="C13" s="40">
@@ -6985,7 +6897,7 @@
         <v/>
       </c>
       <c r="D13" s="40">
-        <f>'Юнитка FBO'!E17</f>
+        <f>'Юнитка FBO'!E16</f>
         <v/>
       </c>
       <c r="E13" s="40">
@@ -6993,19 +6905,19 @@
         <v/>
       </c>
       <c r="F13" s="40">
-        <f>'Юнитка FBO'!I17</f>
+        <f>'Юнитка FBO'!I16</f>
         <v/>
       </c>
       <c r="G13" s="40">
-        <f>'Юнитка FBO'!K17+'Юнитка FBO'!N17+'Юнитка FBO'!O17+'Юнитка FBO'!P17+'Юнитка FBO'!Q17+'Юнитка FBO'!R17+'Юнитка FBO'!S17+'Юнитка FBO'!V17+'Юнитка FBO'!X17+'Юнитка FBO'!Y17+'Юнитка FBO'!AK17</f>
+        <f>'Юнитка FBO'!K16+'Юнитка FBO'!N16+'Юнитка FBO'!O16+'Юнитка FBO'!P16+'Юнитка FBO'!Q16+'Юнитка FBO'!R16+'Юнитка FBO'!S16+'Юнитка FBO'!V16+'Юнитка FBO'!X16+'Юнитка FBO'!Y16+'Юнитка FBO'!AK16</f>
         <v/>
       </c>
       <c r="H13" s="40">
-        <f>'Юнитка FBO'!G17-'Юнитка FBO'!I17</f>
+        <f>'Юнитка FBO'!G16-'Юнитка FBO'!I16</f>
         <v/>
       </c>
       <c r="I13" s="40">
-        <f>MAX(0,G13-H13)+$B$5</f>
+        <f>MAX(0,G13-H13)+$B$4</f>
         <v/>
       </c>
       <c r="J13" s="40">
@@ -7017,29 +6929,21 @@
         <v/>
       </c>
       <c r="L13" s="40">
-        <f>ROUND(D13*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG16</f>
         <v/>
       </c>
       <c r="M13" s="40">
-        <f>'Юнитка FBO'!AG17</f>
-        <v/>
-      </c>
-      <c r="N13" s="40">
-        <f>L13*M13</f>
-        <v/>
-      </c>
-      <c r="O13" s="41">
-        <f>IF(N13&gt;0,K13/N13,"—")</f>
+        <f>D13*L13</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="39">
-        <f>'Юнитка FBO'!A18</f>
+        <f>'Юнитка FBO'!A17</f>
         <v/>
       </c>
       <c r="B14" s="40">
-        <f>'Юнитка FBO'!C18</f>
+        <f>'Юнитка FBO'!C17</f>
         <v/>
       </c>
       <c r="C14" s="40">
@@ -7047,7 +6951,7 @@
         <v/>
       </c>
       <c r="D14" s="40">
-        <f>'Юнитка FBO'!E18</f>
+        <f>'Юнитка FBO'!E17</f>
         <v/>
       </c>
       <c r="E14" s="40">
@@ -7055,19 +6959,19 @@
         <v/>
       </c>
       <c r="F14" s="40">
-        <f>'Юнитка FBO'!I18</f>
+        <f>'Юнитка FBO'!I17</f>
         <v/>
       </c>
       <c r="G14" s="40">
-        <f>'Юнитка FBO'!K18+'Юнитка FBO'!N18+'Юнитка FBO'!O18+'Юнитка FBO'!P18+'Юнитка FBO'!Q18+'Юнитка FBO'!R18+'Юнитка FBO'!S18+'Юнитка FBO'!V18+'Юнитка FBO'!X18+'Юнитка FBO'!Y18+'Юнитка FBO'!AK18</f>
+        <f>'Юнитка FBO'!K17+'Юнитка FBO'!N17+'Юнитка FBO'!O17+'Юнитка FBO'!P17+'Юнитка FBO'!Q17+'Юнитка FBO'!R17+'Юнитка FBO'!S17+'Юнитка FBO'!V17+'Юнитка FBO'!X17+'Юнитка FBO'!Y17+'Юнитка FBO'!AK17</f>
         <v/>
       </c>
       <c r="H14" s="40">
-        <f>'Юнитка FBO'!G18-'Юнитка FBO'!I18</f>
+        <f>'Юнитка FBO'!G17-'Юнитка FBO'!I17</f>
         <v/>
       </c>
       <c r="I14" s="40">
-        <f>MAX(0,G14-H14)+$B$5</f>
+        <f>MAX(0,G14-H14)+$B$4</f>
         <v/>
       </c>
       <c r="J14" s="40">
@@ -7079,29 +6983,21 @@
         <v/>
       </c>
       <c r="L14" s="40">
-        <f>ROUND(D14*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG17</f>
         <v/>
       </c>
       <c r="M14" s="40">
-        <f>'Юнитка FBO'!AG18</f>
-        <v/>
-      </c>
-      <c r="N14" s="40">
-        <f>L14*M14</f>
-        <v/>
-      </c>
-      <c r="O14" s="41">
-        <f>IF(N14&gt;0,K14/N14,"—")</f>
+        <f>D14*L14</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="39">
-        <f>'Юнитка FBO'!A19</f>
+        <f>'Юнитка FBO'!A18</f>
         <v/>
       </c>
       <c r="B15" s="40">
-        <f>'Юнитка FBO'!C19</f>
+        <f>'Юнитка FBO'!C18</f>
         <v/>
       </c>
       <c r="C15" s="40">
@@ -7109,7 +7005,7 @@
         <v/>
       </c>
       <c r="D15" s="40">
-        <f>'Юнитка FBO'!E19</f>
+        <f>'Юнитка FBO'!E18</f>
         <v/>
       </c>
       <c r="E15" s="40">
@@ -7117,19 +7013,19 @@
         <v/>
       </c>
       <c r="F15" s="40">
-        <f>'Юнитка FBO'!I19</f>
+        <f>'Юнитка FBO'!I18</f>
         <v/>
       </c>
       <c r="G15" s="40">
-        <f>'Юнитка FBO'!K19+'Юнитка FBO'!N19+'Юнитка FBO'!O19+'Юнитка FBO'!P19+'Юнитка FBO'!Q19+'Юнитка FBO'!R19+'Юнитка FBO'!S19+'Юнитка FBO'!V19+'Юнитка FBO'!X19+'Юнитка FBO'!Y19+'Юнитка FBO'!AK19</f>
+        <f>'Юнитка FBO'!K18+'Юнитка FBO'!N18+'Юнитка FBO'!O18+'Юнитка FBO'!P18+'Юнитка FBO'!Q18+'Юнитка FBO'!R18+'Юнитка FBO'!S18+'Юнитка FBO'!V18+'Юнитка FBO'!X18+'Юнитка FBO'!Y18+'Юнитка FBO'!AK18</f>
         <v/>
       </c>
       <c r="H15" s="40">
-        <f>'Юнитка FBO'!G19-'Юнитка FBO'!I19</f>
+        <f>'Юнитка FBO'!G18-'Юнитка FBO'!I18</f>
         <v/>
       </c>
       <c r="I15" s="40">
-        <f>MAX(0,G15-H15)+$B$5</f>
+        <f>MAX(0,G15-H15)+$B$4</f>
         <v/>
       </c>
       <c r="J15" s="40">
@@ -7141,29 +7037,21 @@
         <v/>
       </c>
       <c r="L15" s="40">
-        <f>ROUND(D15*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG18</f>
         <v/>
       </c>
       <c r="M15" s="40">
-        <f>'Юнитка FBO'!AG19</f>
-        <v/>
-      </c>
-      <c r="N15" s="40">
-        <f>L15*M15</f>
-        <v/>
-      </c>
-      <c r="O15" s="41">
-        <f>IF(N15&gt;0,K15/N15,"—")</f>
+        <f>D15*L15</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="39">
-        <f>'Юнитка FBO'!A20</f>
+        <f>'Юнитка FBO'!A19</f>
         <v/>
       </c>
       <c r="B16" s="40">
-        <f>'Юнитка FBO'!C20</f>
+        <f>'Юнитка FBO'!C19</f>
         <v/>
       </c>
       <c r="C16" s="40">
@@ -7171,7 +7059,7 @@
         <v/>
       </c>
       <c r="D16" s="40">
-        <f>'Юнитка FBO'!E20</f>
+        <f>'Юнитка FBO'!E19</f>
         <v/>
       </c>
       <c r="E16" s="40">
@@ -7179,19 +7067,19 @@
         <v/>
       </c>
       <c r="F16" s="40">
-        <f>'Юнитка FBO'!I20</f>
+        <f>'Юнитка FBO'!I19</f>
         <v/>
       </c>
       <c r="G16" s="40">
-        <f>'Юнитка FBO'!K20+'Юнитка FBO'!N20+'Юнитка FBO'!O20+'Юнитка FBO'!P20+'Юнитка FBO'!Q20+'Юнитка FBO'!R20+'Юнитка FBO'!S20+'Юнитка FBO'!V20+'Юнитка FBO'!X20+'Юнитка FBO'!Y20+'Юнитка FBO'!AK20</f>
+        <f>'Юнитка FBO'!K19+'Юнитка FBO'!N19+'Юнитка FBO'!O19+'Юнитка FBO'!P19+'Юнитка FBO'!Q19+'Юнитка FBO'!R19+'Юнитка FBO'!S19+'Юнитка FBO'!V19+'Юнитка FBO'!X19+'Юнитка FBO'!Y19+'Юнитка FBO'!AK19</f>
         <v/>
       </c>
       <c r="H16" s="40">
-        <f>'Юнитка FBO'!G20-'Юнитка FBO'!I20</f>
+        <f>'Юнитка FBO'!G19-'Юнитка FBO'!I19</f>
         <v/>
       </c>
       <c r="I16" s="40">
-        <f>MAX(0,G16-H16)+$B$5</f>
+        <f>MAX(0,G16-H16)+$B$4</f>
         <v/>
       </c>
       <c r="J16" s="40">
@@ -7203,29 +7091,21 @@
         <v/>
       </c>
       <c r="L16" s="40">
-        <f>ROUND(D16*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG19</f>
         <v/>
       </c>
       <c r="M16" s="40">
-        <f>'Юнитка FBO'!AG20</f>
-        <v/>
-      </c>
-      <c r="N16" s="40">
-        <f>L16*M16</f>
-        <v/>
-      </c>
-      <c r="O16" s="41">
-        <f>IF(N16&gt;0,K16/N16,"—")</f>
+        <f>D16*L16</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="39">
-        <f>'Юнитка FBO'!A21</f>
+        <f>'Юнитка FBO'!A20</f>
         <v/>
       </c>
       <c r="B17" s="40">
-        <f>'Юнитка FBO'!C21</f>
+        <f>'Юнитка FBO'!C20</f>
         <v/>
       </c>
       <c r="C17" s="40">
@@ -7233,7 +7113,7 @@
         <v/>
       </c>
       <c r="D17" s="40">
-        <f>'Юнитка FBO'!E21</f>
+        <f>'Юнитка FBO'!E20</f>
         <v/>
       </c>
       <c r="E17" s="40">
@@ -7241,19 +7121,19 @@
         <v/>
       </c>
       <c r="F17" s="40">
-        <f>'Юнитка FBO'!I21</f>
+        <f>'Юнитка FBO'!I20</f>
         <v/>
       </c>
       <c r="G17" s="40">
-        <f>'Юнитка FBO'!K21+'Юнитка FBO'!N21+'Юнитка FBO'!O21+'Юнитка FBO'!P21+'Юнитка FBO'!Q21+'Юнитка FBO'!R21+'Юнитка FBO'!S21+'Юнитка FBO'!V21+'Юнитка FBO'!X21+'Юнитка FBO'!Y21+'Юнитка FBO'!AK21</f>
+        <f>'Юнитка FBO'!K20+'Юнитка FBO'!N20+'Юнитка FBO'!O20+'Юнитка FBO'!P20+'Юнитка FBO'!Q20+'Юнитка FBO'!R20+'Юнитка FBO'!S20+'Юнитка FBO'!V20+'Юнитка FBO'!X20+'Юнитка FBO'!Y20+'Юнитка FBO'!AK20</f>
         <v/>
       </c>
       <c r="H17" s="40">
-        <f>'Юнитка FBO'!G21-'Юнитка FBO'!I21</f>
+        <f>'Юнитка FBO'!G20-'Юнитка FBO'!I20</f>
         <v/>
       </c>
       <c r="I17" s="40">
-        <f>MAX(0,G17-H17)+$B$5</f>
+        <f>MAX(0,G17-H17)+$B$4</f>
         <v/>
       </c>
       <c r="J17" s="40">
@@ -7265,29 +7145,21 @@
         <v/>
       </c>
       <c r="L17" s="40">
-        <f>ROUND(D17*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG20</f>
         <v/>
       </c>
       <c r="M17" s="40">
-        <f>'Юнитка FBO'!AG21</f>
-        <v/>
-      </c>
-      <c r="N17" s="40">
-        <f>L17*M17</f>
-        <v/>
-      </c>
-      <c r="O17" s="41">
-        <f>IF(N17&gt;0,K17/N17,"—")</f>
+        <f>D17*L17</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="39">
-        <f>'Юнитка FBO'!A22</f>
+        <f>'Юнитка FBO'!A21</f>
         <v/>
       </c>
       <c r="B18" s="40">
-        <f>'Юнитка FBO'!C22</f>
+        <f>'Юнитка FBO'!C21</f>
         <v/>
       </c>
       <c r="C18" s="40">
@@ -7295,7 +7167,7 @@
         <v/>
       </c>
       <c r="D18" s="40">
-        <f>'Юнитка FBO'!E22</f>
+        <f>'Юнитка FBO'!E21</f>
         <v/>
       </c>
       <c r="E18" s="40">
@@ -7303,19 +7175,19 @@
         <v/>
       </c>
       <c r="F18" s="40">
-        <f>'Юнитка FBO'!I22</f>
+        <f>'Юнитка FBO'!I21</f>
         <v/>
       </c>
       <c r="G18" s="40">
-        <f>'Юнитка FBO'!K22+'Юнитка FBO'!N22+'Юнитка FBO'!O22+'Юнитка FBO'!P22+'Юнитка FBO'!Q22+'Юнитка FBO'!R22+'Юнитка FBO'!S22+'Юнитка FBO'!V22+'Юнитка FBO'!X22+'Юнитка FBO'!Y22+'Юнитка FBO'!AK22</f>
+        <f>'Юнитка FBO'!K21+'Юнитка FBO'!N21+'Юнитка FBO'!O21+'Юнитка FBO'!P21+'Юнитка FBO'!Q21+'Юнитка FBO'!R21+'Юнитка FBO'!S21+'Юнитка FBO'!V21+'Юнитка FBO'!X21+'Юнитка FBO'!Y21+'Юнитка FBO'!AK21</f>
         <v/>
       </c>
       <c r="H18" s="40">
-        <f>'Юнитка FBO'!G22-'Юнитка FBO'!I22</f>
+        <f>'Юнитка FBO'!G21-'Юнитка FBO'!I21</f>
         <v/>
       </c>
       <c r="I18" s="40">
-        <f>MAX(0,G18-H18)+$B$5</f>
+        <f>MAX(0,G18-H18)+$B$4</f>
         <v/>
       </c>
       <c r="J18" s="40">
@@ -7327,29 +7199,21 @@
         <v/>
       </c>
       <c r="L18" s="40">
-        <f>ROUND(D18*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG21</f>
         <v/>
       </c>
       <c r="M18" s="40">
-        <f>'Юнитка FBO'!AG22</f>
-        <v/>
-      </c>
-      <c r="N18" s="40">
-        <f>L18*M18</f>
-        <v/>
-      </c>
-      <c r="O18" s="41">
-        <f>IF(N18&gt;0,K18/N18,"—")</f>
+        <f>D18*L18</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="39">
-        <f>'Юнитка FBO'!A23</f>
+        <f>'Юнитка FBO'!A22</f>
         <v/>
       </c>
       <c r="B19" s="40">
-        <f>'Юнитка FBO'!C23</f>
+        <f>'Юнитка FBO'!C22</f>
         <v/>
       </c>
       <c r="C19" s="40">
@@ -7357,7 +7221,7 @@
         <v/>
       </c>
       <c r="D19" s="40">
-        <f>'Юнитка FBO'!E23</f>
+        <f>'Юнитка FBO'!E22</f>
         <v/>
       </c>
       <c r="E19" s="40">
@@ -7365,19 +7229,19 @@
         <v/>
       </c>
       <c r="F19" s="40">
-        <f>'Юнитка FBO'!I23</f>
+        <f>'Юнитка FBO'!I22</f>
         <v/>
       </c>
       <c r="G19" s="40">
-        <f>'Юнитка FBO'!K23+'Юнитка FBO'!N23+'Юнитка FBO'!O23+'Юнитка FBO'!P23+'Юнитка FBO'!Q23+'Юнитка FBO'!R23+'Юнитка FBO'!S23+'Юнитка FBO'!V23+'Юнитка FBO'!X23+'Юнитка FBO'!Y23+'Юнитка FBO'!AK23</f>
+        <f>'Юнитка FBO'!K22+'Юнитка FBO'!N22+'Юнитка FBO'!O22+'Юнитка FBO'!P22+'Юнитка FBO'!Q22+'Юнитка FBO'!R22+'Юнитка FBO'!S22+'Юнитка FBO'!V22+'Юнитка FBO'!X22+'Юнитка FBO'!Y22+'Юнитка FBO'!AK22</f>
         <v/>
       </c>
       <c r="H19" s="40">
-        <f>'Юнитка FBO'!G23-'Юнитка FBO'!I23</f>
+        <f>'Юнитка FBO'!G22-'Юнитка FBO'!I22</f>
         <v/>
       </c>
       <c r="I19" s="40">
-        <f>MAX(0,G19-H19)+$B$5</f>
+        <f>MAX(0,G19-H19)+$B$4</f>
         <v/>
       </c>
       <c r="J19" s="40">
@@ -7389,29 +7253,21 @@
         <v/>
       </c>
       <c r="L19" s="40">
-        <f>ROUND(D19*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG22</f>
         <v/>
       </c>
       <c r="M19" s="40">
-        <f>'Юнитка FBO'!AG23</f>
-        <v/>
-      </c>
-      <c r="N19" s="40">
-        <f>L19*M19</f>
-        <v/>
-      </c>
-      <c r="O19" s="41">
-        <f>IF(N19&gt;0,K19/N19,"—")</f>
+        <f>D19*L19</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="39">
-        <f>'Юнитка FBO'!A24</f>
+        <f>'Юнитка FBO'!A23</f>
         <v/>
       </c>
       <c r="B20" s="40">
-        <f>'Юнитка FBO'!C24</f>
+        <f>'Юнитка FBO'!C23</f>
         <v/>
       </c>
       <c r="C20" s="40">
@@ -7419,7 +7275,7 @@
         <v/>
       </c>
       <c r="D20" s="40">
-        <f>'Юнитка FBO'!E24</f>
+        <f>'Юнитка FBO'!E23</f>
         <v/>
       </c>
       <c r="E20" s="40">
@@ -7427,19 +7283,19 @@
         <v/>
       </c>
       <c r="F20" s="40">
-        <f>'Юнитка FBO'!I24</f>
+        <f>'Юнитка FBO'!I23</f>
         <v/>
       </c>
       <c r="G20" s="40">
-        <f>'Юнитка FBO'!K24+'Юнитка FBO'!N24+'Юнитка FBO'!O24+'Юнитка FBO'!P24+'Юнитка FBO'!Q24+'Юнитка FBO'!R24+'Юнитка FBO'!S24+'Юнитка FBO'!V24+'Юнитка FBO'!X24+'Юнитка FBO'!Y24+'Юнитка FBO'!AK24</f>
+        <f>'Юнитка FBO'!K23+'Юнитка FBO'!N23+'Юнитка FBO'!O23+'Юнитка FBO'!P23+'Юнитка FBO'!Q23+'Юнитка FBO'!R23+'Юнитка FBO'!S23+'Юнитка FBO'!V23+'Юнитка FBO'!X23+'Юнитка FBO'!Y23+'Юнитка FBO'!AK23</f>
         <v/>
       </c>
       <c r="H20" s="40">
-        <f>'Юнитка FBO'!G24-'Юнитка FBO'!I24</f>
+        <f>'Юнитка FBO'!G23-'Юнитка FBO'!I23</f>
         <v/>
       </c>
       <c r="I20" s="40">
-        <f>MAX(0,G20-H20)+$B$5</f>
+        <f>MAX(0,G20-H20)+$B$4</f>
         <v/>
       </c>
       <c r="J20" s="40">
@@ -7451,29 +7307,21 @@
         <v/>
       </c>
       <c r="L20" s="40">
-        <f>ROUND(D20*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG23</f>
         <v/>
       </c>
       <c r="M20" s="40">
-        <f>'Юнитка FBO'!AG24</f>
-        <v/>
-      </c>
-      <c r="N20" s="40">
-        <f>L20*M20</f>
-        <v/>
-      </c>
-      <c r="O20" s="41">
-        <f>IF(N20&gt;0,K20/N20,"—")</f>
+        <f>D20*L20</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="39">
-        <f>'Юнитка FBO'!A25</f>
+        <f>'Юнитка FBO'!A24</f>
         <v/>
       </c>
       <c r="B21" s="40">
-        <f>'Юнитка FBO'!C25</f>
+        <f>'Юнитка FBO'!C24</f>
         <v/>
       </c>
       <c r="C21" s="40">
@@ -7481,7 +7329,7 @@
         <v/>
       </c>
       <c r="D21" s="40">
-        <f>'Юнитка FBO'!E25</f>
+        <f>'Юнитка FBO'!E24</f>
         <v/>
       </c>
       <c r="E21" s="40">
@@ -7489,19 +7337,19 @@
         <v/>
       </c>
       <c r="F21" s="40">
-        <f>'Юнитка FBO'!I25</f>
+        <f>'Юнитка FBO'!I24</f>
         <v/>
       </c>
       <c r="G21" s="40">
-        <f>'Юнитка FBO'!K25+'Юнитка FBO'!N25+'Юнитка FBO'!O25+'Юнитка FBO'!P25+'Юнитка FBO'!Q25+'Юнитка FBO'!R25+'Юнитка FBO'!S25+'Юнитка FBO'!V25+'Юнитка FBO'!X25+'Юнитка FBO'!Y25+'Юнитка FBO'!AK25</f>
+        <f>'Юнитка FBO'!K24+'Юнитка FBO'!N24+'Юнитка FBO'!O24+'Юнитка FBO'!P24+'Юнитка FBO'!Q24+'Юнитка FBO'!R24+'Юнитка FBO'!S24+'Юнитка FBO'!V24+'Юнитка FBO'!X24+'Юнитка FBO'!Y24+'Юнитка FBO'!AK24</f>
         <v/>
       </c>
       <c r="H21" s="40">
-        <f>'Юнитка FBO'!G25-'Юнитка FBO'!I25</f>
+        <f>'Юнитка FBO'!G24-'Юнитка FBO'!I24</f>
         <v/>
       </c>
       <c r="I21" s="40">
-        <f>MAX(0,G21-H21)+$B$5</f>
+        <f>MAX(0,G21-H21)+$B$4</f>
         <v/>
       </c>
       <c r="J21" s="40">
@@ -7513,29 +7361,21 @@
         <v/>
       </c>
       <c r="L21" s="40">
-        <f>ROUND(D21*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG24</f>
         <v/>
       </c>
       <c r="M21" s="40">
-        <f>'Юнитка FBO'!AG25</f>
-        <v/>
-      </c>
-      <c r="N21" s="40">
-        <f>L21*M21</f>
-        <v/>
-      </c>
-      <c r="O21" s="41">
-        <f>IF(N21&gt;0,K21/N21,"—")</f>
+        <f>D21*L21</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="39">
-        <f>'Юнитка FBO'!A26</f>
+        <f>'Юнитка FBO'!A25</f>
         <v/>
       </c>
       <c r="B22" s="40">
-        <f>'Юнитка FBO'!C26</f>
+        <f>'Юнитка FBO'!C25</f>
         <v/>
       </c>
       <c r="C22" s="40">
@@ -7543,7 +7383,7 @@
         <v/>
       </c>
       <c r="D22" s="40">
-        <f>'Юнитка FBO'!E26</f>
+        <f>'Юнитка FBO'!E25</f>
         <v/>
       </c>
       <c r="E22" s="40">
@@ -7551,19 +7391,19 @@
         <v/>
       </c>
       <c r="F22" s="40">
-        <f>'Юнитка FBO'!I26</f>
+        <f>'Юнитка FBO'!I25</f>
         <v/>
       </c>
       <c r="G22" s="40">
-        <f>'Юнитка FBO'!K26+'Юнитка FBO'!N26+'Юнитка FBO'!O26+'Юнитка FBO'!P26+'Юнитка FBO'!Q26+'Юнитка FBO'!R26+'Юнитка FBO'!S26+'Юнитка FBO'!V26+'Юнитка FBO'!X26+'Юнитка FBO'!Y26+'Юнитка FBO'!AK26</f>
+        <f>'Юнитка FBO'!K25+'Юнитка FBO'!N25+'Юнитка FBO'!O25+'Юнитка FBO'!P25+'Юнитка FBO'!Q25+'Юнитка FBO'!R25+'Юнитка FBO'!S25+'Юнитка FBO'!V25+'Юнитка FBO'!X25+'Юнитка FBO'!Y25+'Юнитка FBO'!AK25</f>
         <v/>
       </c>
       <c r="H22" s="40">
-        <f>'Юнитка FBO'!G26-'Юнитка FBO'!I26</f>
+        <f>'Юнитка FBO'!G25-'Юнитка FBO'!I25</f>
         <v/>
       </c>
       <c r="I22" s="40">
-        <f>MAX(0,G22-H22)+$B$5</f>
+        <f>MAX(0,G22-H22)+$B$4</f>
         <v/>
       </c>
       <c r="J22" s="40">
@@ -7575,29 +7415,21 @@
         <v/>
       </c>
       <c r="L22" s="40">
-        <f>ROUND(D22*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG25</f>
         <v/>
       </c>
       <c r="M22" s="40">
-        <f>'Юнитка FBO'!AG26</f>
-        <v/>
-      </c>
-      <c r="N22" s="40">
-        <f>L22*M22</f>
-        <v/>
-      </c>
-      <c r="O22" s="41">
-        <f>IF(N22&gt;0,K22/N22,"—")</f>
+        <f>D22*L22</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="39">
-        <f>'Юнитка FBO'!A27</f>
+        <f>'Юнитка FBO'!A26</f>
         <v/>
       </c>
       <c r="B23" s="40">
-        <f>'Юнитка FBO'!C27</f>
+        <f>'Юнитка FBO'!C26</f>
         <v/>
       </c>
       <c r="C23" s="40">
@@ -7605,7 +7437,7 @@
         <v/>
       </c>
       <c r="D23" s="40">
-        <f>'Юнитка FBO'!E27</f>
+        <f>'Юнитка FBO'!E26</f>
         <v/>
       </c>
       <c r="E23" s="40">
@@ -7613,19 +7445,19 @@
         <v/>
       </c>
       <c r="F23" s="40">
-        <f>'Юнитка FBO'!I27</f>
+        <f>'Юнитка FBO'!I26</f>
         <v/>
       </c>
       <c r="G23" s="40">
-        <f>'Юнитка FBO'!K27+'Юнитка FBO'!N27+'Юнитка FBO'!O27+'Юнитка FBO'!P27+'Юнитка FBO'!Q27+'Юнитка FBO'!R27+'Юнитка FBO'!S27+'Юнитка FBO'!V27+'Юнитка FBO'!X27+'Юнитка FBO'!Y27+'Юнитка FBO'!AK27</f>
+        <f>'Юнитка FBO'!K26+'Юнитка FBO'!N26+'Юнитка FBO'!O26+'Юнитка FBO'!P26+'Юнитка FBO'!Q26+'Юнитка FBO'!R26+'Юнитка FBO'!S26+'Юнитка FBO'!V26+'Юнитка FBO'!X26+'Юнитка FBO'!Y26+'Юнитка FBO'!AK26</f>
         <v/>
       </c>
       <c r="H23" s="40">
-        <f>'Юнитка FBO'!G27-'Юнитка FBO'!I27</f>
+        <f>'Юнитка FBO'!G26-'Юнитка FBO'!I26</f>
         <v/>
       </c>
       <c r="I23" s="40">
-        <f>MAX(0,G23-H23)+$B$5</f>
+        <f>MAX(0,G23-H23)+$B$4</f>
         <v/>
       </c>
       <c r="J23" s="40">
@@ -7637,29 +7469,21 @@
         <v/>
       </c>
       <c r="L23" s="40">
-        <f>ROUND(D23*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG26</f>
         <v/>
       </c>
       <c r="M23" s="40">
-        <f>'Юнитка FBO'!AG27</f>
-        <v/>
-      </c>
-      <c r="N23" s="40">
-        <f>L23*M23</f>
-        <v/>
-      </c>
-      <c r="O23" s="41">
-        <f>IF(N23&gt;0,K23/N23,"—")</f>
+        <f>D23*L23</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="39">
-        <f>'Юнитка FBO'!A28</f>
+        <f>'Юнитка FBO'!A27</f>
         <v/>
       </c>
       <c r="B24" s="40">
-        <f>'Юнитка FBO'!C28</f>
+        <f>'Юнитка FBO'!C27</f>
         <v/>
       </c>
       <c r="C24" s="40">
@@ -7667,7 +7491,7 @@
         <v/>
       </c>
       <c r="D24" s="40">
-        <f>'Юнитка FBO'!E28</f>
+        <f>'Юнитка FBO'!E27</f>
         <v/>
       </c>
       <c r="E24" s="40">
@@ -7675,19 +7499,19 @@
         <v/>
       </c>
       <c r="F24" s="40">
-        <f>'Юнитка FBO'!I28</f>
+        <f>'Юнитка FBO'!I27</f>
         <v/>
       </c>
       <c r="G24" s="40">
-        <f>'Юнитка FBO'!K28+'Юнитка FBO'!N28+'Юнитка FBO'!O28+'Юнитка FBO'!P28+'Юнитка FBO'!Q28+'Юнитка FBO'!R28+'Юнитка FBO'!S28+'Юнитка FBO'!V28+'Юнитка FBO'!X28+'Юнитка FBO'!Y28+'Юнитка FBO'!AK28</f>
+        <f>'Юнитка FBO'!K27+'Юнитка FBO'!N27+'Юнитка FBO'!O27+'Юнитка FBO'!P27+'Юнитка FBO'!Q27+'Юнитка FBO'!R27+'Юнитка FBO'!S27+'Юнитка FBO'!V27+'Юнитка FBO'!X27+'Юнитка FBO'!Y27+'Юнитка FBO'!AK27</f>
         <v/>
       </c>
       <c r="H24" s="40">
-        <f>'Юнитка FBO'!G28-'Юнитка FBO'!I28</f>
+        <f>'Юнитка FBO'!G27-'Юнитка FBO'!I27</f>
         <v/>
       </c>
       <c r="I24" s="40">
-        <f>MAX(0,G24-H24)+$B$5</f>
+        <f>MAX(0,G24-H24)+$B$4</f>
         <v/>
       </c>
       <c r="J24" s="40">
@@ -7699,29 +7523,21 @@
         <v/>
       </c>
       <c r="L24" s="40">
-        <f>ROUND(D24*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG27</f>
         <v/>
       </c>
       <c r="M24" s="40">
-        <f>'Юнитка FBO'!AG28</f>
-        <v/>
-      </c>
-      <c r="N24" s="40">
-        <f>L24*M24</f>
-        <v/>
-      </c>
-      <c r="O24" s="41">
-        <f>IF(N24&gt;0,K24/N24,"—")</f>
+        <f>D24*L24</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="39">
-        <f>'Юнитка FBO'!A29</f>
+        <f>'Юнитка FBO'!A28</f>
         <v/>
       </c>
       <c r="B25" s="40">
-        <f>'Юнитка FBO'!C29</f>
+        <f>'Юнитка FBO'!C28</f>
         <v/>
       </c>
       <c r="C25" s="40">
@@ -7729,7 +7545,7 @@
         <v/>
       </c>
       <c r="D25" s="40">
-        <f>'Юнитка FBO'!E29</f>
+        <f>'Юнитка FBO'!E28</f>
         <v/>
       </c>
       <c r="E25" s="40">
@@ -7737,19 +7553,19 @@
         <v/>
       </c>
       <c r="F25" s="40">
-        <f>'Юнитка FBO'!I29</f>
+        <f>'Юнитка FBO'!I28</f>
         <v/>
       </c>
       <c r="G25" s="40">
-        <f>'Юнитка FBO'!K29+'Юнитка FBO'!N29+'Юнитка FBO'!O29+'Юнитка FBO'!P29+'Юнитка FBO'!Q29+'Юнитка FBO'!R29+'Юнитка FBO'!S29+'Юнитка FBO'!V29+'Юнитка FBO'!X29+'Юнитка FBO'!Y29+'Юнитка FBO'!AK29</f>
+        <f>'Юнитка FBO'!K28+'Юнитка FBO'!N28+'Юнитка FBO'!O28+'Юнитка FBO'!P28+'Юнитка FBO'!Q28+'Юнитка FBO'!R28+'Юнитка FBO'!S28+'Юнитка FBO'!V28+'Юнитка FBO'!X28+'Юнитка FBO'!Y28+'Юнитка FBO'!AK28</f>
         <v/>
       </c>
       <c r="H25" s="40">
-        <f>'Юнитка FBO'!G29-'Юнитка FBO'!I29</f>
+        <f>'Юнитка FBO'!G28-'Юнитка FBO'!I28</f>
         <v/>
       </c>
       <c r="I25" s="40">
-        <f>MAX(0,G25-H25)+$B$5</f>
+        <f>MAX(0,G25-H25)+$B$4</f>
         <v/>
       </c>
       <c r="J25" s="40">
@@ -7761,29 +7577,21 @@
         <v/>
       </c>
       <c r="L25" s="40">
-        <f>ROUND(D25*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG28</f>
         <v/>
       </c>
       <c r="M25" s="40">
-        <f>'Юнитка FBO'!AG29</f>
-        <v/>
-      </c>
-      <c r="N25" s="40">
-        <f>L25*M25</f>
-        <v/>
-      </c>
-      <c r="O25" s="41">
-        <f>IF(N25&gt;0,K25/N25,"—")</f>
+        <f>D25*L25</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="39">
-        <f>'Юнитка FBO'!A30</f>
+        <f>'Юнитка FBO'!A29</f>
         <v/>
       </c>
       <c r="B26" s="40">
-        <f>'Юнитка FBO'!C30</f>
+        <f>'Юнитка FBO'!C29</f>
         <v/>
       </c>
       <c r="C26" s="40">
@@ -7791,7 +7599,7 @@
         <v/>
       </c>
       <c r="D26" s="40">
-        <f>'Юнитка FBO'!E30</f>
+        <f>'Юнитка FBO'!E29</f>
         <v/>
       </c>
       <c r="E26" s="40">
@@ -7799,19 +7607,19 @@
         <v/>
       </c>
       <c r="F26" s="40">
-        <f>'Юнитка FBO'!I30</f>
+        <f>'Юнитка FBO'!I29</f>
         <v/>
       </c>
       <c r="G26" s="40">
-        <f>'Юнитка FBO'!K30+'Юнитка FBO'!N30+'Юнитка FBO'!O30+'Юнитка FBO'!P30+'Юнитка FBO'!Q30+'Юнитка FBO'!R30+'Юнитка FBO'!S30+'Юнитка FBO'!V30+'Юнитка FBO'!X30+'Юнитка FBO'!Y30+'Юнитка FBO'!AK30</f>
+        <f>'Юнитка FBO'!K29+'Юнитка FBO'!N29+'Юнитка FBO'!O29+'Юнитка FBO'!P29+'Юнитка FBO'!Q29+'Юнитка FBO'!R29+'Юнитка FBO'!S29+'Юнитка FBO'!V29+'Юнитка FBO'!X29+'Юнитка FBO'!Y29+'Юнитка FBO'!AK29</f>
         <v/>
       </c>
       <c r="H26" s="40">
-        <f>'Юнитка FBO'!G30-'Юнитка FBO'!I30</f>
+        <f>'Юнитка FBO'!G29-'Юнитка FBO'!I29</f>
         <v/>
       </c>
       <c r="I26" s="40">
-        <f>MAX(0,G26-H26)+$B$5</f>
+        <f>MAX(0,G26-H26)+$B$4</f>
         <v/>
       </c>
       <c r="J26" s="40">
@@ -7823,29 +7631,21 @@
         <v/>
       </c>
       <c r="L26" s="40">
-        <f>ROUND(D26*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG29</f>
         <v/>
       </c>
       <c r="M26" s="40">
-        <f>'Юнитка FBO'!AG30</f>
-        <v/>
-      </c>
-      <c r="N26" s="40">
-        <f>L26*M26</f>
-        <v/>
-      </c>
-      <c r="O26" s="41">
-        <f>IF(N26&gt;0,K26/N26,"—")</f>
+        <f>D26*L26</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="39">
-        <f>'Юнитка FBO'!A31</f>
+        <f>'Юнитка FBO'!A30</f>
         <v/>
       </c>
       <c r="B27" s="40">
-        <f>'Юнитка FBO'!C31</f>
+        <f>'Юнитка FBO'!C30</f>
         <v/>
       </c>
       <c r="C27" s="40">
@@ -7853,7 +7653,7 @@
         <v/>
       </c>
       <c r="D27" s="40">
-        <f>'Юнитка FBO'!E31</f>
+        <f>'Юнитка FBO'!E30</f>
         <v/>
       </c>
       <c r="E27" s="40">
@@ -7861,19 +7661,19 @@
         <v/>
       </c>
       <c r="F27" s="40">
-        <f>'Юнитка FBO'!I31</f>
+        <f>'Юнитка FBO'!I30</f>
         <v/>
       </c>
       <c r="G27" s="40">
-        <f>'Юнитка FBO'!K31+'Юнитка FBO'!N31+'Юнитка FBO'!O31+'Юнитка FBO'!P31+'Юнитка FBO'!Q31+'Юнитка FBO'!R31+'Юнитка FBO'!S31+'Юнитка FBO'!V31+'Юнитка FBO'!X31+'Юнитка FBO'!Y31+'Юнитка FBO'!AK31</f>
+        <f>'Юнитка FBO'!K30+'Юнитка FBO'!N30+'Юнитка FBO'!O30+'Юнитка FBO'!P30+'Юнитка FBO'!Q30+'Юнитка FBO'!R30+'Юнитка FBO'!S30+'Юнитка FBO'!V30+'Юнитка FBO'!X30+'Юнитка FBO'!Y30+'Юнитка FBO'!AK30</f>
         <v/>
       </c>
       <c r="H27" s="40">
-        <f>'Юнитка FBO'!G31-'Юнитка FBO'!I31</f>
+        <f>'Юнитка FBO'!G30-'Юнитка FBO'!I30</f>
         <v/>
       </c>
       <c r="I27" s="40">
-        <f>MAX(0,G27-H27)+$B$5</f>
+        <f>MAX(0,G27-H27)+$B$4</f>
         <v/>
       </c>
       <c r="J27" s="40">
@@ -7885,29 +7685,21 @@
         <v/>
       </c>
       <c r="L27" s="40">
-        <f>ROUND(D27*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG30</f>
         <v/>
       </c>
       <c r="M27" s="40">
-        <f>'Юнитка FBO'!AG31</f>
-        <v/>
-      </c>
-      <c r="N27" s="40">
-        <f>L27*M27</f>
-        <v/>
-      </c>
-      <c r="O27" s="41">
-        <f>IF(N27&gt;0,K27/N27,"—")</f>
+        <f>D27*L27</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="39">
-        <f>'Юнитка FBO'!A32</f>
+        <f>'Юнитка FBO'!A31</f>
         <v/>
       </c>
       <c r="B28" s="40">
-        <f>'Юнитка FBO'!C32</f>
+        <f>'Юнитка FBO'!C31</f>
         <v/>
       </c>
       <c r="C28" s="40">
@@ -7915,7 +7707,7 @@
         <v/>
       </c>
       <c r="D28" s="40">
-        <f>'Юнитка FBO'!E32</f>
+        <f>'Юнитка FBO'!E31</f>
         <v/>
       </c>
       <c r="E28" s="40">
@@ -7923,19 +7715,19 @@
         <v/>
       </c>
       <c r="F28" s="40">
-        <f>'Юнитка FBO'!I32</f>
+        <f>'Юнитка FBO'!I31</f>
         <v/>
       </c>
       <c r="G28" s="40">
-        <f>'Юнитка FBO'!K32+'Юнитка FBO'!N32+'Юнитка FBO'!O32+'Юнитка FBO'!P32+'Юнитка FBO'!Q32+'Юнитка FBO'!R32+'Юнитка FBO'!S32+'Юнитка FBO'!V32+'Юнитка FBO'!X32+'Юнитка FBO'!Y32+'Юнитка FBO'!AK32</f>
+        <f>'Юнитка FBO'!K31+'Юнитка FBO'!N31+'Юнитка FBO'!O31+'Юнитка FBO'!P31+'Юнитка FBO'!Q31+'Юнитка FBO'!R31+'Юнитка FBO'!S31+'Юнитка FBO'!V31+'Юнитка FBO'!X31+'Юнитка FBO'!Y31+'Юнитка FBO'!AK31</f>
         <v/>
       </c>
       <c r="H28" s="40">
-        <f>'Юнитка FBO'!G32-'Юнитка FBO'!I32</f>
+        <f>'Юнитка FBO'!G31-'Юнитка FBO'!I31</f>
         <v/>
       </c>
       <c r="I28" s="40">
-        <f>MAX(0,G28-H28)+$B$5</f>
+        <f>MAX(0,G28-H28)+$B$4</f>
         <v/>
       </c>
       <c r="J28" s="40">
@@ -7947,29 +7739,21 @@
         <v/>
       </c>
       <c r="L28" s="40">
-        <f>ROUND(D28*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG31</f>
         <v/>
       </c>
       <c r="M28" s="40">
-        <f>'Юнитка FBO'!AG32</f>
-        <v/>
-      </c>
-      <c r="N28" s="40">
-        <f>L28*M28</f>
-        <v/>
-      </c>
-      <c r="O28" s="41">
-        <f>IF(N28&gt;0,K28/N28,"—")</f>
+        <f>D28*L28</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="39">
-        <f>'Юнитка FBO'!A33</f>
+        <f>'Юнитка FBO'!A32</f>
         <v/>
       </c>
       <c r="B29" s="40">
-        <f>'Юнитка FBO'!C33</f>
+        <f>'Юнитка FBO'!C32</f>
         <v/>
       </c>
       <c r="C29" s="40">
@@ -7977,7 +7761,7 @@
         <v/>
       </c>
       <c r="D29" s="40">
-        <f>'Юнитка FBO'!E33</f>
+        <f>'Юнитка FBO'!E32</f>
         <v/>
       </c>
       <c r="E29" s="40">
@@ -7985,19 +7769,19 @@
         <v/>
       </c>
       <c r="F29" s="40">
-        <f>'Юнитка FBO'!I33</f>
+        <f>'Юнитка FBO'!I32</f>
         <v/>
       </c>
       <c r="G29" s="40">
-        <f>'Юнитка FBO'!K33+'Юнитка FBO'!N33+'Юнитка FBO'!O33+'Юнитка FBO'!P33+'Юнитка FBO'!Q33+'Юнитка FBO'!R33+'Юнитка FBO'!S33+'Юнитка FBO'!V33+'Юнитка FBO'!X33+'Юнитка FBO'!Y33+'Юнитка FBO'!AK33</f>
+        <f>'Юнитка FBO'!K32+'Юнитка FBO'!N32+'Юнитка FBO'!O32+'Юнитка FBO'!P32+'Юнитка FBO'!Q32+'Юнитка FBO'!R32+'Юнитка FBO'!S32+'Юнитка FBO'!V32+'Юнитка FBO'!X32+'Юнитка FBO'!Y32+'Юнитка FBO'!AK32</f>
         <v/>
       </c>
       <c r="H29" s="40">
-        <f>'Юнитка FBO'!G33-'Юнитка FBO'!I33</f>
+        <f>'Юнитка FBO'!G32-'Юнитка FBO'!I32</f>
         <v/>
       </c>
       <c r="I29" s="40">
-        <f>MAX(0,G29-H29)+$B$5</f>
+        <f>MAX(0,G29-H29)+$B$4</f>
         <v/>
       </c>
       <c r="J29" s="40">
@@ -8009,29 +7793,21 @@
         <v/>
       </c>
       <c r="L29" s="40">
-        <f>ROUND(D29*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG32</f>
         <v/>
       </c>
       <c r="M29" s="40">
-        <f>'Юнитка FBO'!AG33</f>
-        <v/>
-      </c>
-      <c r="N29" s="40">
-        <f>L29*M29</f>
-        <v/>
-      </c>
-      <c r="O29" s="41">
-        <f>IF(N29&gt;0,K29/N29,"—")</f>
+        <f>D29*L29</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="39">
-        <f>'Юнитка FBO'!A34</f>
+        <f>'Юнитка FBO'!A33</f>
         <v/>
       </c>
       <c r="B30" s="40">
-        <f>'Юнитка FBO'!C34</f>
+        <f>'Юнитка FBO'!C33</f>
         <v/>
       </c>
       <c r="C30" s="40">
@@ -8039,7 +7815,7 @@
         <v/>
       </c>
       <c r="D30" s="40">
-        <f>'Юнитка FBO'!E34</f>
+        <f>'Юнитка FBO'!E33</f>
         <v/>
       </c>
       <c r="E30" s="40">
@@ -8047,19 +7823,19 @@
         <v/>
       </c>
       <c r="F30" s="40">
-        <f>'Юнитка FBO'!I34</f>
+        <f>'Юнитка FBO'!I33</f>
         <v/>
       </c>
       <c r="G30" s="40">
-        <f>'Юнитка FBO'!K34+'Юнитка FBO'!N34+'Юнитка FBO'!O34+'Юнитка FBO'!P34+'Юнитка FBO'!Q34+'Юнитка FBO'!R34+'Юнитка FBO'!S34+'Юнитка FBO'!V34+'Юнитка FBO'!X34+'Юнитка FBO'!Y34+'Юнитка FBO'!AK34</f>
+        <f>'Юнитка FBO'!K33+'Юнитка FBO'!N33+'Юнитка FBO'!O33+'Юнитка FBO'!P33+'Юнитка FBO'!Q33+'Юнитка FBO'!R33+'Юнитка FBO'!S33+'Юнитка FBO'!V33+'Юнитка FBO'!X33+'Юнитка FBO'!Y33+'Юнитка FBO'!AK33</f>
         <v/>
       </c>
       <c r="H30" s="40">
-        <f>'Юнитка FBO'!G34-'Юнитка FBO'!I34</f>
+        <f>'Юнитка FBO'!G33-'Юнитка FBO'!I33</f>
         <v/>
       </c>
       <c r="I30" s="40">
-        <f>MAX(0,G30-H30)+$B$5</f>
+        <f>MAX(0,G30-H30)+$B$4</f>
         <v/>
       </c>
       <c r="J30" s="40">
@@ -8071,29 +7847,21 @@
         <v/>
       </c>
       <c r="L30" s="40">
-        <f>ROUND(D30*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG33</f>
         <v/>
       </c>
       <c r="M30" s="40">
-        <f>'Юнитка FBO'!AG34</f>
-        <v/>
-      </c>
-      <c r="N30" s="40">
-        <f>L30*M30</f>
-        <v/>
-      </c>
-      <c r="O30" s="41">
-        <f>IF(N30&gt;0,K30/N30,"—")</f>
+        <f>D30*L30</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="39">
-        <f>'Юнитка FBO'!A35</f>
+        <f>'Юнитка FBO'!A34</f>
         <v/>
       </c>
       <c r="B31" s="40">
-        <f>'Юнитка FBO'!C35</f>
+        <f>'Юнитка FBO'!C34</f>
         <v/>
       </c>
       <c r="C31" s="40">
@@ -8101,7 +7869,7 @@
         <v/>
       </c>
       <c r="D31" s="40">
-        <f>'Юнитка FBO'!E35</f>
+        <f>'Юнитка FBO'!E34</f>
         <v/>
       </c>
       <c r="E31" s="40">
@@ -8109,19 +7877,19 @@
         <v/>
       </c>
       <c r="F31" s="40">
-        <f>'Юнитка FBO'!I35</f>
+        <f>'Юнитка FBO'!I34</f>
         <v/>
       </c>
       <c r="G31" s="40">
-        <f>'Юнитка FBO'!K35+'Юнитка FBO'!N35+'Юнитка FBO'!O35+'Юнитка FBO'!P35+'Юнитка FBO'!Q35+'Юнитка FBO'!R35+'Юнитка FBO'!S35+'Юнитка FBO'!V35+'Юнитка FBO'!X35+'Юнитка FBO'!Y35+'Юнитка FBO'!AK35</f>
+        <f>'Юнитка FBO'!K34+'Юнитка FBO'!N34+'Юнитка FBO'!O34+'Юнитка FBO'!P34+'Юнитка FBO'!Q34+'Юнитка FBO'!R34+'Юнитка FBO'!S34+'Юнитка FBO'!V34+'Юнитка FBO'!X34+'Юнитка FBO'!Y34+'Юнитка FBO'!AK34</f>
         <v/>
       </c>
       <c r="H31" s="40">
-        <f>'Юнитка FBO'!G35-'Юнитка FBO'!I35</f>
+        <f>'Юнитка FBO'!G34-'Юнитка FBO'!I34</f>
         <v/>
       </c>
       <c r="I31" s="40">
-        <f>MAX(0,G31-H31)+$B$5</f>
+        <f>MAX(0,G31-H31)+$B$4</f>
         <v/>
       </c>
       <c r="J31" s="40">
@@ -8133,385 +7901,341 @@
         <v/>
       </c>
       <c r="L31" s="40">
-        <f>ROUND(D31*$B$4,0)</f>
+        <f>'Юнитка FBO'!AG34</f>
         <v/>
       </c>
       <c r="M31" s="40">
+        <f>D31*L31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="39">
+        <f>'Юнитка FBO'!A35</f>
+        <v/>
+      </c>
+      <c r="B32" s="40">
+        <f>'Юнитка FBO'!C35</f>
+        <v/>
+      </c>
+      <c r="C32" s="40">
+        <f>B32*$B$2</f>
+        <v/>
+      </c>
+      <c r="D32" s="40">
+        <f>'Юнитка FBO'!E35</f>
+        <v/>
+      </c>
+      <c r="E32" s="40">
+        <f>ROUND(D32*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F32" s="40">
+        <f>'Юнитка FBO'!I35</f>
+        <v/>
+      </c>
+      <c r="G32" s="40">
+        <f>'Юнитка FBO'!K35+'Юнитка FBO'!N35+'Юнитка FBO'!O35+'Юнитка FBO'!P35+'Юнитка FBO'!Q35+'Юнитка FBO'!R35+'Юнитка FBO'!S35+'Юнитка FBO'!V35+'Юнитка FBO'!X35+'Юнитка FBO'!Y35+'Юнитка FBO'!AK35</f>
+        <v/>
+      </c>
+      <c r="H32" s="40">
+        <f>'Юнитка FBO'!G35-'Юнитка FBO'!I35</f>
+        <v/>
+      </c>
+      <c r="I32" s="40">
+        <f>MAX(0,G32-H32)+$B$4</f>
+        <v/>
+      </c>
+      <c r="J32" s="40">
+        <f>E32*I32</f>
+        <v/>
+      </c>
+      <c r="K32" s="40">
+        <f>C32+J32</f>
+        <v/>
+      </c>
+      <c r="L32" s="40">
         <f>'Юнитка FBO'!AG35</f>
         <v/>
       </c>
-      <c r="N31" s="40">
-        <f>L31*M31</f>
-        <v/>
-      </c>
-      <c r="O31" s="41">
-        <f>IF(N31&gt;0,K31/N31,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="42" t="inlineStr">
+      <c r="M32" s="40">
+        <f>D32*L32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B32" s="43">
-        <f>SUM(B9:B31)</f>
-        <v/>
-      </c>
-      <c r="C32" s="43">
-        <f>SUM(C9:C31)</f>
-        <v/>
-      </c>
-      <c r="D32" s="43">
-        <f>SUM(D9:D31)</f>
-        <v/>
-      </c>
-      <c r="E32" s="43">
-        <f>SUM(E9:E31)</f>
-        <v/>
-      </c>
-      <c r="F32" s="42" t="n"/>
-      <c r="G32" s="42" t="n"/>
-      <c r="H32" s="42" t="n"/>
-      <c r="I32" s="42" t="n"/>
-      <c r="J32" s="43">
-        <f>SUM(J9:J31)</f>
-        <v/>
-      </c>
-      <c r="K32" s="43">
-        <f>SUM(K9:K31)</f>
-        <v/>
-      </c>
-      <c r="L32" s="43">
-        <f>SUM(L9:L31)</f>
-        <v/>
-      </c>
-      <c r="M32" s="42" t="n"/>
-      <c r="N32" s="43">
-        <f>SUM(N9:N31)</f>
-        <v/>
-      </c>
-      <c r="O32" s="44">
-        <f>IF(N32&gt;0,K32/N32,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="45" t="inlineStr">
-        <is>
-          <t>Денежный поток по месяцам</t>
-        </is>
+      <c r="B33" s="42">
+        <f>SUM(B10:B32)</f>
+        <v/>
+      </c>
+      <c r="C33" s="42">
+        <f>SUM(C10:C32)</f>
+        <v/>
+      </c>
+      <c r="D33" s="42">
+        <f>SUM(D10:D32)</f>
+        <v/>
+      </c>
+      <c r="E33" s="42">
+        <f>SUM(E10:E32)</f>
+        <v/>
+      </c>
+      <c r="F33" s="41" t="n"/>
+      <c r="G33" s="41" t="n"/>
+      <c r="H33" s="41" t="n"/>
+      <c r="I33" s="41" t="n"/>
+      <c r="J33" s="42">
+        <f>SUM(J10:J32)</f>
+        <v/>
+      </c>
+      <c r="K33" s="42">
+        <f>SUM(K10:K32)</f>
+        <v/>
+      </c>
+      <c r="L33" s="41" t="n"/>
+      <c r="M33" s="42">
+        <f>SUM(M10:M32)</f>
+        <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="38" t="inlineStr">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>План по месяцам: раскрутка + выход на продажи (доля от конкурента растёт на +10 п.п./мес)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="38" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B36" s="38" t="inlineStr">
+      <c r="B37" s="38" t="inlineStr">
+        <is>
+          <t>Доля от продаж конкурента</t>
+        </is>
+      </c>
+      <c r="C37" s="38" t="inlineStr">
+        <is>
+          <t>Прибыль от продаж, ₽</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="inlineStr">
         <is>
           <t>Расходы (накрутка), ₽</t>
         </is>
       </c>
-      <c r="C36" s="38" t="inlineStr">
-        <is>
-          <t>Прибыль от продаж, ₽</t>
-        </is>
-      </c>
-      <c r="D36" s="38" t="inlineStr">
+      <c r="E37" s="38" t="inlineStr">
         <is>
           <t>Чистый поток, ₽</t>
         </is>
       </c>
-      <c r="E36" s="38" t="inlineStr">
+      <c r="F37" s="38" t="inlineStr">
         <is>
           <t>Накопительно, ₽</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="39" t="n">
-        <v>1</v>
-      </c>
-      <c r="B37" s="40">
-        <f>$K$32</f>
-        <v/>
-      </c>
-      <c r="C37" s="40" t="n">
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>Август (раскрутка)</t>
+        </is>
+      </c>
+      <c r="B38" s="44" t="n">
         <v>0</v>
       </c>
-      <c r="D37" s="40">
-        <f>C37-B37</f>
-        <v/>
-      </c>
-      <c r="E37" s="40">
-        <f>D37</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="39" t="n">
-        <v>2</v>
-      </c>
-      <c r="B38" s="40" t="n">
+      <c r="C38" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
       <c r="D38" s="40">
-        <f>C38-B38</f>
+        <f>$K$33</f>
         <v/>
       </c>
       <c r="E38" s="40">
-        <f>E37+D38</f>
+        <f>C38-D38</f>
+        <v/>
+      </c>
+      <c r="F38" s="40">
+        <f>E38</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="n">
-        <v>3</v>
-      </c>
-      <c r="B39" s="40" t="n">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>Сентябрь</t>
+        </is>
+      </c>
+      <c r="B39" s="44">
+        <f>$B$5+0*$B$6</f>
+        <v/>
+      </c>
+      <c r="C39" s="40">
+        <f>B39*$M$33</f>
+        <v/>
+      </c>
+      <c r="D39" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C39" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D39" s="40">
-        <f>C39-B39</f>
-        <v/>
-      </c>
       <c r="E39" s="40">
-        <f>E38+D39</f>
+        <f>C39-D39</f>
+        <v/>
+      </c>
+      <c r="F39" s="40">
+        <f>F38+E39</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="n">
-        <v>4</v>
-      </c>
-      <c r="B40" s="40" t="n">
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>Октябрь</t>
+        </is>
+      </c>
+      <c r="B40" s="44">
+        <f>$B$5+1*$B$6</f>
+        <v/>
+      </c>
+      <c r="C40" s="40">
+        <f>B40*$M$33</f>
+        <v/>
+      </c>
+      <c r="D40" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C40" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D40" s="40">
-        <f>C40-B40</f>
-        <v/>
-      </c>
       <c r="E40" s="40">
-        <f>E39+D40</f>
+        <f>C40-D40</f>
+        <v/>
+      </c>
+      <c r="F40" s="40">
+        <f>F39+E40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="n">
-        <v>5</v>
-      </c>
-      <c r="B41" s="40" t="n">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>Ноябрь</t>
+        </is>
+      </c>
+      <c r="B41" s="44">
+        <f>$B$5+2*$B$6</f>
+        <v/>
+      </c>
+      <c r="C41" s="40">
+        <f>B41*$M$33</f>
+        <v/>
+      </c>
+      <c r="D41" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C41" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D41" s="40">
-        <f>C41-B41</f>
-        <v/>
-      </c>
       <c r="E41" s="40">
-        <f>E40+D41</f>
+        <f>C41-D41</f>
+        <v/>
+      </c>
+      <c r="F41" s="40">
+        <f>F40+E41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="n">
-        <v>6</v>
-      </c>
-      <c r="B42" s="40" t="n">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>Декабрь</t>
+        </is>
+      </c>
+      <c r="B42" s="44">
+        <f>$B$5+3*$B$6</f>
+        <v/>
+      </c>
+      <c r="C42" s="40">
+        <f>B42*$M$33</f>
+        <v/>
+      </c>
+      <c r="D42" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="C42" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D42" s="40">
-        <f>C42-B42</f>
-        <v/>
-      </c>
       <c r="E42" s="40">
-        <f>E41+D42</f>
+        <f>C42-D42</f>
+        <v/>
+      </c>
+      <c r="F42" s="40">
+        <f>F41+E42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39" t="n">
-        <v>7</v>
-      </c>
-      <c r="B43" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C43" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D43" s="40">
-        <f>C43-B43</f>
-        <v/>
-      </c>
-      <c r="E43" s="40">
-        <f>E42+D43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="39" t="n">
-        <v>8</v>
-      </c>
-      <c r="B44" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C44" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D44" s="40">
-        <f>C44-B44</f>
-        <v/>
-      </c>
-      <c r="E44" s="40">
-        <f>E43+D44</f>
+      <c r="A43" s="41" t="inlineStr">
+        <is>
+          <t>Итого за период</t>
+        </is>
+      </c>
+      <c r="B43" s="41" t="n"/>
+      <c r="C43" s="42">
+        <f>SUM(C38:C42)</f>
+        <v/>
+      </c>
+      <c r="D43" s="42">
+        <f>SUM(D38:D42)</f>
+        <v/>
+      </c>
+      <c r="E43" s="42">
+        <f>SUM(E38:E42)</f>
+        <v/>
+      </c>
+      <c r="F43" s="42">
+        <f>F42</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="39" t="n">
-        <v>9</v>
-      </c>
-      <c r="B45" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C45" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D45" s="40">
-        <f>C45-B45</f>
-        <v/>
-      </c>
-      <c r="E45" s="40">
-        <f>E44+D45</f>
+      <c r="A45" s="34" t="inlineStr">
+        <is>
+          <t>Разовые расходы на раскрутку (август), ₽</t>
+        </is>
+      </c>
+      <c r="B45" s="42">
+        <f>$K$33</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="39" t="n">
-        <v>10</v>
-      </c>
-      <c r="B46" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C46" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D46" s="40">
-        <f>C46-B46</f>
-        <v/>
-      </c>
-      <c r="E46" s="40">
-        <f>E45+D46</f>
+      <c r="A46" s="34" t="inlineStr">
+        <is>
+          <t>Прибыль при 100% продаж конкурента, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B46" s="42">
+        <f>$M$33</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="39" t="n">
-        <v>11</v>
-      </c>
-      <c r="B47" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C47" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D47" s="40">
-        <f>C47-B47</f>
-        <v/>
-      </c>
-      <c r="E47" s="40">
-        <f>E46+D47</f>
+      <c r="A47" s="34" t="inlineStr">
+        <is>
+          <t>Накопительный поток к декабрю, ₽</t>
+        </is>
+      </c>
+      <c r="B47" s="42">
+        <f>F42</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="39" t="n">
-        <v>12</v>
-      </c>
-      <c r="B48" s="40" t="n">
-        <v>0</v>
-      </c>
-      <c r="C48" s="40">
-        <f>$N$32</f>
-        <v/>
-      </c>
-      <c r="D48" s="40">
-        <f>C48-B48</f>
-        <v/>
-      </c>
-      <c r="E48" s="40">
-        <f>E47+D48</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="34" t="inlineStr">
-        <is>
-          <t>Разовые расходы на раскрутку (1-й мес), ₽</t>
-        </is>
-      </c>
-      <c r="B50" s="43">
-        <f>$K$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="34" t="inlineStr">
-        <is>
-          <t>Прибыль в месяц (со 2-го мес), ₽</t>
-        </is>
-      </c>
-      <c r="B51" s="43">
-        <f>$N$32</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="34" t="inlineStr">
-        <is>
-          <t>Окупаемость раскрутки, мес продаж</t>
-        </is>
-      </c>
-      <c r="B52" s="44">
-        <f>IF($N$32&gt;0,$K$32/$N$32,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="34" t="inlineStr">
-        <is>
-          <t>Выход в плюс с запуска, мес</t>
-        </is>
-      </c>
-      <c r="B53" s="44">
-        <f>IF($N$32&gt;0,1+$K$32/$N$32,"—")</f>
+      <c r="A48" s="34" t="inlineStr">
+        <is>
+          <t>Окупаемость раскрутки, мес продаж (при 100%)</t>
+        </is>
+      </c>
+      <c r="B48" s="45">
+        <f>IF($M$33&gt;0,$K$33/$M$33,"—")</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
+++ b/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
@@ -8023,20 +8023,25 @@
       </c>
       <c r="C37" s="38" t="inlineStr">
         <is>
+          <t>Продаж, шт</t>
+        </is>
+      </c>
+      <c r="D37" s="38" t="inlineStr">
+        <is>
           <t>Прибыль от продаж, ₽</t>
         </is>
       </c>
-      <c r="D37" s="38" t="inlineStr">
+      <c r="E37" s="38" t="inlineStr">
         <is>
           <t>Расходы (накрутка), ₽</t>
         </is>
       </c>
-      <c r="E37" s="38" t="inlineStr">
+      <c r="F37" s="38" t="inlineStr">
         <is>
           <t>Чистый поток, ₽</t>
         </is>
       </c>
-      <c r="F37" s="38" t="inlineStr">
+      <c r="G37" s="38" t="inlineStr">
         <is>
           <t>Накопительно, ₽</t>
         </is>
@@ -8054,16 +8059,19 @@
       <c r="C38" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="40">
+      <c r="D38" s="40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="40">
         <f>$K$33</f>
         <v/>
       </c>
-      <c r="E38" s="40">
-        <f>C38-D38</f>
-        <v/>
-      </c>
       <c r="F38" s="40">
-        <f>E38</f>
+        <f>D38-E38</f>
+        <v/>
+      </c>
+      <c r="G38" s="40">
+        <f>F38</f>
         <v/>
       </c>
     </row>
@@ -8078,18 +8086,22 @@
         <v/>
       </c>
       <c r="C39" s="40">
+        <f>ROUND(B39*$D$33,0)</f>
+        <v/>
+      </c>
+      <c r="D39" s="40">
         <f>B39*$M$33</f>
         <v/>
       </c>
-      <c r="D39" s="40" t="n">
+      <c r="E39" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="40">
-        <f>C39-D39</f>
-        <v/>
-      </c>
       <c r="F39" s="40">
-        <f>F38+E39</f>
+        <f>D39-E39</f>
+        <v/>
+      </c>
+      <c r="G39" s="40">
+        <f>G38+F39</f>
         <v/>
       </c>
     </row>
@@ -8104,18 +8116,22 @@
         <v/>
       </c>
       <c r="C40" s="40">
+        <f>ROUND(B40*$D$33,0)</f>
+        <v/>
+      </c>
+      <c r="D40" s="40">
         <f>B40*$M$33</f>
         <v/>
       </c>
-      <c r="D40" s="40" t="n">
+      <c r="E40" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="40">
-        <f>C40-D40</f>
-        <v/>
-      </c>
       <c r="F40" s="40">
-        <f>F39+E40</f>
+        <f>D40-E40</f>
+        <v/>
+      </c>
+      <c r="G40" s="40">
+        <f>G39+F40</f>
         <v/>
       </c>
     </row>
@@ -8130,18 +8146,22 @@
         <v/>
       </c>
       <c r="C41" s="40">
+        <f>ROUND(B41*$D$33,0)</f>
+        <v/>
+      </c>
+      <c r="D41" s="40">
         <f>B41*$M$33</f>
         <v/>
       </c>
-      <c r="D41" s="40" t="n">
+      <c r="E41" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="40">
-        <f>C41-D41</f>
-        <v/>
-      </c>
       <c r="F41" s="40">
-        <f>F40+E41</f>
+        <f>D41-E41</f>
+        <v/>
+      </c>
+      <c r="G41" s="40">
+        <f>G40+F41</f>
         <v/>
       </c>
     </row>
@@ -8156,18 +8176,22 @@
         <v/>
       </c>
       <c r="C42" s="40">
+        <f>ROUND(B42*$D$33,0)</f>
+        <v/>
+      </c>
+      <c r="D42" s="40">
         <f>B42*$M$33</f>
         <v/>
       </c>
-      <c r="D42" s="40" t="n">
+      <c r="E42" s="40" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="40">
-        <f>C42-D42</f>
-        <v/>
-      </c>
       <c r="F42" s="40">
-        <f>F41+E42</f>
+        <f>D42-E42</f>
+        <v/>
+      </c>
+      <c r="G42" s="40">
+        <f>G41+F42</f>
         <v/>
       </c>
     </row>
@@ -8191,7 +8215,11 @@
         <v/>
       </c>
       <c r="F43" s="42">
-        <f>F42</f>
+        <f>SUM(F38:F42)</f>
+        <v/>
+      </c>
+      <c r="G43" s="42">
+        <f>G42</f>
         <v/>
       </c>
     </row>
@@ -8224,7 +8252,7 @@
         </is>
       </c>
       <c r="B47" s="42">
-        <f>F42</f>
+        <f>G42</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
+++ b/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
@@ -77,7 +77,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +116,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00548235"/>
       </patternFill>
     </fill>
     <fill>
@@ -234,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -296,13 +301,16 @@
     <xf numFmtId="0" fontId="9" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6572,7 +6580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M48"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6587,7 +6595,10 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6650,7 +6661,7 @@
     <row r="7">
       <c r="A7" s="37" t="inlineStr">
         <is>
-          <t>Самовыкуп: платим цену с СПП (покупатель), получаем выплату Ozon с цены продавца (СПП финансирует Ozon), товар возвращается на склад → теряем только сборы Ozon сверх компенсации СПП + прочие расходы.</t>
+          <t>Самовыкуп: платим цену с СПП (покупатель), получаем выплату Ozon с цены продавца (СПП финансирует Ozon), товар возвращается на склад → теряем только сборы Ozon сверх компенсации СПП + прочие расходы. Прибыль по месяцам = доля от конкурента (растёт +10 п.п./мес) × маржа/шт.</t>
         </is>
       </c>
     </row>
@@ -6715,1296 +6726,1599 @@
           <t>Маржа/шт, ₽</t>
         </is>
       </c>
-      <c r="M9" s="38" t="inlineStr">
-        <is>
-          <t>Прибыль/мес при 100% конкурента, ₽</t>
+      <c r="M9" s="39" t="inlineStr">
+        <is>
+          <t>Прибыль Сентябрь, ₽</t>
+        </is>
+      </c>
+      <c r="N9" s="39" t="inlineStr">
+        <is>
+          <t>Прибыль Октябрь, ₽</t>
+        </is>
+      </c>
+      <c r="O9" s="39" t="inlineStr">
+        <is>
+          <t>Прибыль Ноябрь, ₽</t>
+        </is>
+      </c>
+      <c r="P9" s="39" t="inlineStr">
+        <is>
+          <t>Прибыль Декабрь, ₽</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="39">
+      <c r="A10" s="40">
         <f>'Юнитка FBO'!A13</f>
         <v/>
       </c>
-      <c r="B10" s="40">
+      <c r="B10" s="41">
         <f>'Юнитка FBO'!C13</f>
         <v/>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="41">
         <f>B10*$B$2</f>
         <v/>
       </c>
-      <c r="D10" s="40">
+      <c r="D10" s="41">
         <f>'Юнитка FBO'!E13</f>
         <v/>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="41">
         <f>ROUND(D10*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F10" s="40">
+      <c r="F10" s="41">
         <f>'Юнитка FBO'!I13</f>
         <v/>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="41">
         <f>'Юнитка FBO'!K13+'Юнитка FBO'!N13+'Юнитка FBO'!O13+'Юнитка FBO'!P13+'Юнитка FBO'!Q13+'Юнитка FBO'!R13+'Юнитка FBO'!S13+'Юнитка FBO'!V13+'Юнитка FBO'!X13+'Юнитка FBO'!Y13+'Юнитка FBO'!AK13</f>
         <v/>
       </c>
-      <c r="H10" s="40">
+      <c r="H10" s="41">
         <f>'Юнитка FBO'!G13-'Юнитка FBO'!I13</f>
         <v/>
       </c>
-      <c r="I10" s="40">
+      <c r="I10" s="41">
         <f>MAX(0,G10-H10)+$B$4</f>
         <v/>
       </c>
-      <c r="J10" s="40">
+      <c r="J10" s="41">
         <f>E10*I10</f>
         <v/>
       </c>
-      <c r="K10" s="40">
+      <c r="K10" s="41">
         <f>C10+J10</f>
         <v/>
       </c>
-      <c r="L10" s="40">
+      <c r="L10" s="41">
         <f>'Юнитка FBO'!AG13</f>
         <v/>
       </c>
-      <c r="M10" s="40">
-        <f>D10*L10</f>
+      <c r="M10" s="41">
+        <f>D10*L10*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N10" s="41">
+        <f>D10*L10*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O10" s="41">
+        <f>D10*L10*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P10" s="41">
+        <f>D10*L10*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="39">
+      <c r="A11" s="40">
         <f>'Юнитка FBO'!A14</f>
         <v/>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="41">
         <f>'Юнитка FBO'!C14</f>
         <v/>
       </c>
-      <c r="C11" s="40">
+      <c r="C11" s="41">
         <f>B11*$B$2</f>
         <v/>
       </c>
-      <c r="D11" s="40">
+      <c r="D11" s="41">
         <f>'Юнитка FBO'!E14</f>
         <v/>
       </c>
-      <c r="E11" s="40">
+      <c r="E11" s="41">
         <f>ROUND(D11*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F11" s="40">
+      <c r="F11" s="41">
         <f>'Юнитка FBO'!I14</f>
         <v/>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="41">
         <f>'Юнитка FBO'!K14+'Юнитка FBO'!N14+'Юнитка FBO'!O14+'Юнитка FBO'!P14+'Юнитка FBO'!Q14+'Юнитка FBO'!R14+'Юнитка FBO'!S14+'Юнитка FBO'!V14+'Юнитка FBO'!X14+'Юнитка FBO'!Y14+'Юнитка FBO'!AK14</f>
         <v/>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="41">
         <f>'Юнитка FBO'!G14-'Юнитка FBO'!I14</f>
         <v/>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="41">
         <f>MAX(0,G11-H11)+$B$4</f>
         <v/>
       </c>
-      <c r="J11" s="40">
+      <c r="J11" s="41">
         <f>E11*I11</f>
         <v/>
       </c>
-      <c r="K11" s="40">
+      <c r="K11" s="41">
         <f>C11+J11</f>
         <v/>
       </c>
-      <c r="L11" s="40">
+      <c r="L11" s="41">
         <f>'Юнитка FBO'!AG14</f>
         <v/>
       </c>
-      <c r="M11" s="40">
-        <f>D11*L11</f>
+      <c r="M11" s="41">
+        <f>D11*L11*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N11" s="41">
+        <f>D11*L11*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O11" s="41">
+        <f>D11*L11*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P11" s="41">
+        <f>D11*L11*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="39">
+      <c r="A12" s="40">
         <f>'Юнитка FBO'!A15</f>
         <v/>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="41">
         <f>'Юнитка FBO'!C15</f>
         <v/>
       </c>
-      <c r="C12" s="40">
+      <c r="C12" s="41">
         <f>B12*$B$2</f>
         <v/>
       </c>
-      <c r="D12" s="40">
+      <c r="D12" s="41">
         <f>'Юнитка FBO'!E15</f>
         <v/>
       </c>
-      <c r="E12" s="40">
+      <c r="E12" s="41">
         <f>ROUND(D12*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F12" s="40">
+      <c r="F12" s="41">
         <f>'Юнитка FBO'!I15</f>
         <v/>
       </c>
-      <c r="G12" s="40">
+      <c r="G12" s="41">
         <f>'Юнитка FBO'!K15+'Юнитка FBO'!N15+'Юнитка FBO'!O15+'Юнитка FBO'!P15+'Юнитка FBO'!Q15+'Юнитка FBO'!R15+'Юнитка FBO'!S15+'Юнитка FBO'!V15+'Юнитка FBO'!X15+'Юнитка FBO'!Y15+'Юнитка FBO'!AK15</f>
         <v/>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="41">
         <f>'Юнитка FBO'!G15-'Юнитка FBO'!I15</f>
         <v/>
       </c>
-      <c r="I12" s="40">
+      <c r="I12" s="41">
         <f>MAX(0,G12-H12)+$B$4</f>
         <v/>
       </c>
-      <c r="J12" s="40">
+      <c r="J12" s="41">
         <f>E12*I12</f>
         <v/>
       </c>
-      <c r="K12" s="40">
+      <c r="K12" s="41">
         <f>C12+J12</f>
         <v/>
       </c>
-      <c r="L12" s="40">
+      <c r="L12" s="41">
         <f>'Юнитка FBO'!AG15</f>
         <v/>
       </c>
-      <c r="M12" s="40">
-        <f>D12*L12</f>
+      <c r="M12" s="41">
+        <f>D12*L12*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N12" s="41">
+        <f>D12*L12*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O12" s="41">
+        <f>D12*L12*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P12" s="41">
+        <f>D12*L12*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="39">
+      <c r="A13" s="40">
         <f>'Юнитка FBO'!A16</f>
         <v/>
       </c>
-      <c r="B13" s="40">
+      <c r="B13" s="41">
         <f>'Юнитка FBO'!C16</f>
         <v/>
       </c>
-      <c r="C13" s="40">
+      <c r="C13" s="41">
         <f>B13*$B$2</f>
         <v/>
       </c>
-      <c r="D13" s="40">
+      <c r="D13" s="41">
         <f>'Юнитка FBO'!E16</f>
         <v/>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="41">
         <f>ROUND(D13*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="41">
         <f>'Юнитка FBO'!I16</f>
         <v/>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="41">
         <f>'Юнитка FBO'!K16+'Юнитка FBO'!N16+'Юнитка FBO'!O16+'Юнитка FBO'!P16+'Юнитка FBO'!Q16+'Юнитка FBO'!R16+'Юнитка FBO'!S16+'Юнитка FBO'!V16+'Юнитка FBO'!X16+'Юнитка FBO'!Y16+'Юнитка FBO'!AK16</f>
         <v/>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="41">
         <f>'Юнитка FBO'!G16-'Юнитка FBO'!I16</f>
         <v/>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="41">
         <f>MAX(0,G13-H13)+$B$4</f>
         <v/>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="41">
         <f>E13*I13</f>
         <v/>
       </c>
-      <c r="K13" s="40">
+      <c r="K13" s="41">
         <f>C13+J13</f>
         <v/>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="41">
         <f>'Юнитка FBO'!AG16</f>
         <v/>
       </c>
-      <c r="M13" s="40">
-        <f>D13*L13</f>
+      <c r="M13" s="41">
+        <f>D13*L13*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N13" s="41">
+        <f>D13*L13*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O13" s="41">
+        <f>D13*L13*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P13" s="41">
+        <f>D13*L13*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="39">
+      <c r="A14" s="40">
         <f>'Юнитка FBO'!A17</f>
         <v/>
       </c>
-      <c r="B14" s="40">
+      <c r="B14" s="41">
         <f>'Юнитка FBO'!C17</f>
         <v/>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="41">
         <f>B14*$B$2</f>
         <v/>
       </c>
-      <c r="D14" s="40">
+      <c r="D14" s="41">
         <f>'Юнитка FBO'!E17</f>
         <v/>
       </c>
-      <c r="E14" s="40">
+      <c r="E14" s="41">
         <f>ROUND(D14*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F14" s="40">
+      <c r="F14" s="41">
         <f>'Юнитка FBO'!I17</f>
         <v/>
       </c>
-      <c r="G14" s="40">
+      <c r="G14" s="41">
         <f>'Юнитка FBO'!K17+'Юнитка FBO'!N17+'Юнитка FBO'!O17+'Юнитка FBO'!P17+'Юнитка FBO'!Q17+'Юнитка FBO'!R17+'Юнитка FBO'!S17+'Юнитка FBO'!V17+'Юнитка FBO'!X17+'Юнитка FBO'!Y17+'Юнитка FBO'!AK17</f>
         <v/>
       </c>
-      <c r="H14" s="40">
+      <c r="H14" s="41">
         <f>'Юнитка FBO'!G17-'Юнитка FBO'!I17</f>
         <v/>
       </c>
-      <c r="I14" s="40">
+      <c r="I14" s="41">
         <f>MAX(0,G14-H14)+$B$4</f>
         <v/>
       </c>
-      <c r="J14" s="40">
+      <c r="J14" s="41">
         <f>E14*I14</f>
         <v/>
       </c>
-      <c r="K14" s="40">
+      <c r="K14" s="41">
         <f>C14+J14</f>
         <v/>
       </c>
-      <c r="L14" s="40">
+      <c r="L14" s="41">
         <f>'Юнитка FBO'!AG17</f>
         <v/>
       </c>
-      <c r="M14" s="40">
-        <f>D14*L14</f>
+      <c r="M14" s="41">
+        <f>D14*L14*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N14" s="41">
+        <f>D14*L14*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O14" s="41">
+        <f>D14*L14*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P14" s="41">
+        <f>D14*L14*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="39">
+      <c r="A15" s="40">
         <f>'Юнитка FBO'!A18</f>
         <v/>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="41">
         <f>'Юнитка FBO'!C18</f>
         <v/>
       </c>
-      <c r="C15" s="40">
+      <c r="C15" s="41">
         <f>B15*$B$2</f>
         <v/>
       </c>
-      <c r="D15" s="40">
+      <c r="D15" s="41">
         <f>'Юнитка FBO'!E18</f>
         <v/>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="41">
         <f>ROUND(D15*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F15" s="40">
+      <c r="F15" s="41">
         <f>'Юнитка FBO'!I18</f>
         <v/>
       </c>
-      <c r="G15" s="40">
+      <c r="G15" s="41">
         <f>'Юнитка FBO'!K18+'Юнитка FBO'!N18+'Юнитка FBO'!O18+'Юнитка FBO'!P18+'Юнитка FBO'!Q18+'Юнитка FBO'!R18+'Юнитка FBO'!S18+'Юнитка FBO'!V18+'Юнитка FBO'!X18+'Юнитка FBO'!Y18+'Юнитка FBO'!AK18</f>
         <v/>
       </c>
-      <c r="H15" s="40">
+      <c r="H15" s="41">
         <f>'Юнитка FBO'!G18-'Юнитка FBO'!I18</f>
         <v/>
       </c>
-      <c r="I15" s="40">
+      <c r="I15" s="41">
         <f>MAX(0,G15-H15)+$B$4</f>
         <v/>
       </c>
-      <c r="J15" s="40">
+      <c r="J15" s="41">
         <f>E15*I15</f>
         <v/>
       </c>
-      <c r="K15" s="40">
+      <c r="K15" s="41">
         <f>C15+J15</f>
         <v/>
       </c>
-      <c r="L15" s="40">
+      <c r="L15" s="41">
         <f>'Юнитка FBO'!AG18</f>
         <v/>
       </c>
-      <c r="M15" s="40">
-        <f>D15*L15</f>
+      <c r="M15" s="41">
+        <f>D15*L15*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N15" s="41">
+        <f>D15*L15*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O15" s="41">
+        <f>D15*L15*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P15" s="41">
+        <f>D15*L15*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="39">
+      <c r="A16" s="40">
         <f>'Юнитка FBO'!A19</f>
         <v/>
       </c>
-      <c r="B16" s="40">
+      <c r="B16" s="41">
         <f>'Юнитка FBO'!C19</f>
         <v/>
       </c>
-      <c r="C16" s="40">
+      <c r="C16" s="41">
         <f>B16*$B$2</f>
         <v/>
       </c>
-      <c r="D16" s="40">
+      <c r="D16" s="41">
         <f>'Юнитка FBO'!E19</f>
         <v/>
       </c>
-      <c r="E16" s="40">
+      <c r="E16" s="41">
         <f>ROUND(D16*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F16" s="40">
+      <c r="F16" s="41">
         <f>'Юнитка FBO'!I19</f>
         <v/>
       </c>
-      <c r="G16" s="40">
+      <c r="G16" s="41">
         <f>'Юнитка FBO'!K19+'Юнитка FBO'!N19+'Юнитка FBO'!O19+'Юнитка FBO'!P19+'Юнитка FBO'!Q19+'Юнитка FBO'!R19+'Юнитка FBO'!S19+'Юнитка FBO'!V19+'Юнитка FBO'!X19+'Юнитка FBO'!Y19+'Юнитка FBO'!AK19</f>
         <v/>
       </c>
-      <c r="H16" s="40">
+      <c r="H16" s="41">
         <f>'Юнитка FBO'!G19-'Юнитка FBO'!I19</f>
         <v/>
       </c>
-      <c r="I16" s="40">
+      <c r="I16" s="41">
         <f>MAX(0,G16-H16)+$B$4</f>
         <v/>
       </c>
-      <c r="J16" s="40">
+      <c r="J16" s="41">
         <f>E16*I16</f>
         <v/>
       </c>
-      <c r="K16" s="40">
+      <c r="K16" s="41">
         <f>C16+J16</f>
         <v/>
       </c>
-      <c r="L16" s="40">
+      <c r="L16" s="41">
         <f>'Юнитка FBO'!AG19</f>
         <v/>
       </c>
-      <c r="M16" s="40">
-        <f>D16*L16</f>
+      <c r="M16" s="41">
+        <f>D16*L16*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N16" s="41">
+        <f>D16*L16*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O16" s="41">
+        <f>D16*L16*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P16" s="41">
+        <f>D16*L16*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="39">
+      <c r="A17" s="40">
         <f>'Юнитка FBO'!A20</f>
         <v/>
       </c>
-      <c r="B17" s="40">
+      <c r="B17" s="41">
         <f>'Юнитка FBO'!C20</f>
         <v/>
       </c>
-      <c r="C17" s="40">
+      <c r="C17" s="41">
         <f>B17*$B$2</f>
         <v/>
       </c>
-      <c r="D17" s="40">
+      <c r="D17" s="41">
         <f>'Юнитка FBO'!E20</f>
         <v/>
       </c>
-      <c r="E17" s="40">
+      <c r="E17" s="41">
         <f>ROUND(D17*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F17" s="40">
+      <c r="F17" s="41">
         <f>'Юнитка FBO'!I20</f>
         <v/>
       </c>
-      <c r="G17" s="40">
+      <c r="G17" s="41">
         <f>'Юнитка FBO'!K20+'Юнитка FBO'!N20+'Юнитка FBO'!O20+'Юнитка FBO'!P20+'Юнитка FBO'!Q20+'Юнитка FBO'!R20+'Юнитка FBO'!S20+'Юнитка FBO'!V20+'Юнитка FBO'!X20+'Юнитка FBO'!Y20+'Юнитка FBO'!AK20</f>
         <v/>
       </c>
-      <c r="H17" s="40">
+      <c r="H17" s="41">
         <f>'Юнитка FBO'!G20-'Юнитка FBO'!I20</f>
         <v/>
       </c>
-      <c r="I17" s="40">
+      <c r="I17" s="41">
         <f>MAX(0,G17-H17)+$B$4</f>
         <v/>
       </c>
-      <c r="J17" s="40">
+      <c r="J17" s="41">
         <f>E17*I17</f>
         <v/>
       </c>
-      <c r="K17" s="40">
+      <c r="K17" s="41">
         <f>C17+J17</f>
         <v/>
       </c>
-      <c r="L17" s="40">
+      <c r="L17" s="41">
         <f>'Юнитка FBO'!AG20</f>
         <v/>
       </c>
-      <c r="M17" s="40">
-        <f>D17*L17</f>
+      <c r="M17" s="41">
+        <f>D17*L17*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N17" s="41">
+        <f>D17*L17*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O17" s="41">
+        <f>D17*L17*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P17" s="41">
+        <f>D17*L17*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="39">
+      <c r="A18" s="40">
         <f>'Юнитка FBO'!A21</f>
         <v/>
       </c>
-      <c r="B18" s="40">
+      <c r="B18" s="41">
         <f>'Юнитка FBO'!C21</f>
         <v/>
       </c>
-      <c r="C18" s="40">
+      <c r="C18" s="41">
         <f>B18*$B$2</f>
         <v/>
       </c>
-      <c r="D18" s="40">
+      <c r="D18" s="41">
         <f>'Юнитка FBO'!E21</f>
         <v/>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="41">
         <f>ROUND(D18*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F18" s="40">
+      <c r="F18" s="41">
         <f>'Юнитка FBO'!I21</f>
         <v/>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="41">
         <f>'Юнитка FBO'!K21+'Юнитка FBO'!N21+'Юнитка FBO'!O21+'Юнитка FBO'!P21+'Юнитка FBO'!Q21+'Юнитка FBO'!R21+'Юнитка FBO'!S21+'Юнитка FBO'!V21+'Юнитка FBO'!X21+'Юнитка FBO'!Y21+'Юнитка FBO'!AK21</f>
         <v/>
       </c>
-      <c r="H18" s="40">
+      <c r="H18" s="41">
         <f>'Юнитка FBO'!G21-'Юнитка FBO'!I21</f>
         <v/>
       </c>
-      <c r="I18" s="40">
+      <c r="I18" s="41">
         <f>MAX(0,G18-H18)+$B$4</f>
         <v/>
       </c>
-      <c r="J18" s="40">
+      <c r="J18" s="41">
         <f>E18*I18</f>
         <v/>
       </c>
-      <c r="K18" s="40">
+      <c r="K18" s="41">
         <f>C18+J18</f>
         <v/>
       </c>
-      <c r="L18" s="40">
+      <c r="L18" s="41">
         <f>'Юнитка FBO'!AG21</f>
         <v/>
       </c>
-      <c r="M18" s="40">
-        <f>D18*L18</f>
+      <c r="M18" s="41">
+        <f>D18*L18*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N18" s="41">
+        <f>D18*L18*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O18" s="41">
+        <f>D18*L18*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P18" s="41">
+        <f>D18*L18*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="39">
+      <c r="A19" s="40">
         <f>'Юнитка FBO'!A22</f>
         <v/>
       </c>
-      <c r="B19" s="40">
+      <c r="B19" s="41">
         <f>'Юнитка FBO'!C22</f>
         <v/>
       </c>
-      <c r="C19" s="40">
+      <c r="C19" s="41">
         <f>B19*$B$2</f>
         <v/>
       </c>
-      <c r="D19" s="40">
+      <c r="D19" s="41">
         <f>'Юнитка FBO'!E22</f>
         <v/>
       </c>
-      <c r="E19" s="40">
+      <c r="E19" s="41">
         <f>ROUND(D19*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="41">
         <f>'Юнитка FBO'!I22</f>
         <v/>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="41">
         <f>'Юнитка FBO'!K22+'Юнитка FBO'!N22+'Юнитка FBO'!O22+'Юнитка FBO'!P22+'Юнитка FBO'!Q22+'Юнитка FBO'!R22+'Юнитка FBO'!S22+'Юнитка FBO'!V22+'Юнитка FBO'!X22+'Юнитка FBO'!Y22+'Юнитка FBO'!AK22</f>
         <v/>
       </c>
-      <c r="H19" s="40">
+      <c r="H19" s="41">
         <f>'Юнитка FBO'!G22-'Юнитка FBO'!I22</f>
         <v/>
       </c>
-      <c r="I19" s="40">
+      <c r="I19" s="41">
         <f>MAX(0,G19-H19)+$B$4</f>
         <v/>
       </c>
-      <c r="J19" s="40">
+      <c r="J19" s="41">
         <f>E19*I19</f>
         <v/>
       </c>
-      <c r="K19" s="40">
+      <c r="K19" s="41">
         <f>C19+J19</f>
         <v/>
       </c>
-      <c r="L19" s="40">
+      <c r="L19" s="41">
         <f>'Юнитка FBO'!AG22</f>
         <v/>
       </c>
-      <c r="M19" s="40">
-        <f>D19*L19</f>
+      <c r="M19" s="41">
+        <f>D19*L19*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N19" s="41">
+        <f>D19*L19*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O19" s="41">
+        <f>D19*L19*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P19" s="41">
+        <f>D19*L19*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="39">
+      <c r="A20" s="40">
         <f>'Юнитка FBO'!A23</f>
         <v/>
       </c>
-      <c r="B20" s="40">
+      <c r="B20" s="41">
         <f>'Юнитка FBO'!C23</f>
         <v/>
       </c>
-      <c r="C20" s="40">
+      <c r="C20" s="41">
         <f>B20*$B$2</f>
         <v/>
       </c>
-      <c r="D20" s="40">
+      <c r="D20" s="41">
         <f>'Юнитка FBO'!E23</f>
         <v/>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="41">
         <f>ROUND(D20*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="41">
         <f>'Юнитка FBO'!I23</f>
         <v/>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="41">
         <f>'Юнитка FBO'!K23+'Юнитка FBO'!N23+'Юнитка FBO'!O23+'Юнитка FBO'!P23+'Юнитка FBO'!Q23+'Юнитка FBO'!R23+'Юнитка FBO'!S23+'Юнитка FBO'!V23+'Юнитка FBO'!X23+'Юнитка FBO'!Y23+'Юнитка FBO'!AK23</f>
         <v/>
       </c>
-      <c r="H20" s="40">
+      <c r="H20" s="41">
         <f>'Юнитка FBO'!G23-'Юнитка FBO'!I23</f>
         <v/>
       </c>
-      <c r="I20" s="40">
+      <c r="I20" s="41">
         <f>MAX(0,G20-H20)+$B$4</f>
         <v/>
       </c>
-      <c r="J20" s="40">
+      <c r="J20" s="41">
         <f>E20*I20</f>
         <v/>
       </c>
-      <c r="K20" s="40">
+      <c r="K20" s="41">
         <f>C20+J20</f>
         <v/>
       </c>
-      <c r="L20" s="40">
+      <c r="L20" s="41">
         <f>'Юнитка FBO'!AG23</f>
         <v/>
       </c>
-      <c r="M20" s="40">
-        <f>D20*L20</f>
+      <c r="M20" s="41">
+        <f>D20*L20*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N20" s="41">
+        <f>D20*L20*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O20" s="41">
+        <f>D20*L20*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P20" s="41">
+        <f>D20*L20*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="39">
+      <c r="A21" s="40">
         <f>'Юнитка FBO'!A24</f>
         <v/>
       </c>
-      <c r="B21" s="40">
+      <c r="B21" s="41">
         <f>'Юнитка FBO'!C24</f>
         <v/>
       </c>
-      <c r="C21" s="40">
+      <c r="C21" s="41">
         <f>B21*$B$2</f>
         <v/>
       </c>
-      <c r="D21" s="40">
+      <c r="D21" s="41">
         <f>'Юнитка FBO'!E24</f>
         <v/>
       </c>
-      <c r="E21" s="40">
+      <c r="E21" s="41">
         <f>ROUND(D21*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="41">
         <f>'Юнитка FBO'!I24</f>
         <v/>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="41">
         <f>'Юнитка FBO'!K24+'Юнитка FBO'!N24+'Юнитка FBO'!O24+'Юнитка FBO'!P24+'Юнитка FBO'!Q24+'Юнитка FBO'!R24+'Юнитка FBO'!S24+'Юнитка FBO'!V24+'Юнитка FBO'!X24+'Юнитка FBO'!Y24+'Юнитка FBO'!AK24</f>
         <v/>
       </c>
-      <c r="H21" s="40">
+      <c r="H21" s="41">
         <f>'Юнитка FBO'!G24-'Юнитка FBO'!I24</f>
         <v/>
       </c>
-      <c r="I21" s="40">
+      <c r="I21" s="41">
         <f>MAX(0,G21-H21)+$B$4</f>
         <v/>
       </c>
-      <c r="J21" s="40">
+      <c r="J21" s="41">
         <f>E21*I21</f>
         <v/>
       </c>
-      <c r="K21" s="40">
+      <c r="K21" s="41">
         <f>C21+J21</f>
         <v/>
       </c>
-      <c r="L21" s="40">
+      <c r="L21" s="41">
         <f>'Юнитка FBO'!AG24</f>
         <v/>
       </c>
-      <c r="M21" s="40">
-        <f>D21*L21</f>
+      <c r="M21" s="41">
+        <f>D21*L21*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N21" s="41">
+        <f>D21*L21*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O21" s="41">
+        <f>D21*L21*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P21" s="41">
+        <f>D21*L21*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="39">
+      <c r="A22" s="40">
         <f>'Юнитка FBO'!A25</f>
         <v/>
       </c>
-      <c r="B22" s="40">
+      <c r="B22" s="41">
         <f>'Юнитка FBO'!C25</f>
         <v/>
       </c>
-      <c r="C22" s="40">
+      <c r="C22" s="41">
         <f>B22*$B$2</f>
         <v/>
       </c>
-      <c r="D22" s="40">
+      <c r="D22" s="41">
         <f>'Юнитка FBO'!E25</f>
         <v/>
       </c>
-      <c r="E22" s="40">
+      <c r="E22" s="41">
         <f>ROUND(D22*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F22" s="40">
+      <c r="F22" s="41">
         <f>'Юнитка FBO'!I25</f>
         <v/>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="41">
         <f>'Юнитка FBO'!K25+'Юнитка FBO'!N25+'Юнитка FBO'!O25+'Юнитка FBO'!P25+'Юнитка FBO'!Q25+'Юнитка FBO'!R25+'Юнитка FBO'!S25+'Юнитка FBO'!V25+'Юнитка FBO'!X25+'Юнитка FBO'!Y25+'Юнитка FBO'!AK25</f>
         <v/>
       </c>
-      <c r="H22" s="40">
+      <c r="H22" s="41">
         <f>'Юнитка FBO'!G25-'Юнитка FBO'!I25</f>
         <v/>
       </c>
-      <c r="I22" s="40">
+      <c r="I22" s="41">
         <f>MAX(0,G22-H22)+$B$4</f>
         <v/>
       </c>
-      <c r="J22" s="40">
+      <c r="J22" s="41">
         <f>E22*I22</f>
         <v/>
       </c>
-      <c r="K22" s="40">
+      <c r="K22" s="41">
         <f>C22+J22</f>
         <v/>
       </c>
-      <c r="L22" s="40">
+      <c r="L22" s="41">
         <f>'Юнитка FBO'!AG25</f>
         <v/>
       </c>
-      <c r="M22" s="40">
-        <f>D22*L22</f>
+      <c r="M22" s="41">
+        <f>D22*L22*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N22" s="41">
+        <f>D22*L22*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O22" s="41">
+        <f>D22*L22*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P22" s="41">
+        <f>D22*L22*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="39">
+      <c r="A23" s="40">
         <f>'Юнитка FBO'!A26</f>
         <v/>
       </c>
-      <c r="B23" s="40">
+      <c r="B23" s="41">
         <f>'Юнитка FBO'!C26</f>
         <v/>
       </c>
-      <c r="C23" s="40">
+      <c r="C23" s="41">
         <f>B23*$B$2</f>
         <v/>
       </c>
-      <c r="D23" s="40">
+      <c r="D23" s="41">
         <f>'Юнитка FBO'!E26</f>
         <v/>
       </c>
-      <c r="E23" s="40">
+      <c r="E23" s="41">
         <f>ROUND(D23*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F23" s="40">
+      <c r="F23" s="41">
         <f>'Юнитка FBO'!I26</f>
         <v/>
       </c>
-      <c r="G23" s="40">
+      <c r="G23" s="41">
         <f>'Юнитка FBO'!K26+'Юнитка FBO'!N26+'Юнитка FBO'!O26+'Юнитка FBO'!P26+'Юнитка FBO'!Q26+'Юнитка FBO'!R26+'Юнитка FBO'!S26+'Юнитка FBO'!V26+'Юнитка FBO'!X26+'Юнитка FBO'!Y26+'Юнитка FBO'!AK26</f>
         <v/>
       </c>
-      <c r="H23" s="40">
+      <c r="H23" s="41">
         <f>'Юнитка FBO'!G26-'Юнитка FBO'!I26</f>
         <v/>
       </c>
-      <c r="I23" s="40">
+      <c r="I23" s="41">
         <f>MAX(0,G23-H23)+$B$4</f>
         <v/>
       </c>
-      <c r="J23" s="40">
+      <c r="J23" s="41">
         <f>E23*I23</f>
         <v/>
       </c>
-      <c r="K23" s="40">
+      <c r="K23" s="41">
         <f>C23+J23</f>
         <v/>
       </c>
-      <c r="L23" s="40">
+      <c r="L23" s="41">
         <f>'Юнитка FBO'!AG26</f>
         <v/>
       </c>
-      <c r="M23" s="40">
-        <f>D23*L23</f>
+      <c r="M23" s="41">
+        <f>D23*L23*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N23" s="41">
+        <f>D23*L23*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O23" s="41">
+        <f>D23*L23*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P23" s="41">
+        <f>D23*L23*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="39">
+      <c r="A24" s="40">
         <f>'Юнитка FBO'!A27</f>
         <v/>
       </c>
-      <c r="B24" s="40">
+      <c r="B24" s="41">
         <f>'Юнитка FBO'!C27</f>
         <v/>
       </c>
-      <c r="C24" s="40">
+      <c r="C24" s="41">
         <f>B24*$B$2</f>
         <v/>
       </c>
-      <c r="D24" s="40">
+      <c r="D24" s="41">
         <f>'Юнитка FBO'!E27</f>
         <v/>
       </c>
-      <c r="E24" s="40">
+      <c r="E24" s="41">
         <f>ROUND(D24*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F24" s="40">
+      <c r="F24" s="41">
         <f>'Юнитка FBO'!I27</f>
         <v/>
       </c>
-      <c r="G24" s="40">
+      <c r="G24" s="41">
         <f>'Юнитка FBO'!K27+'Юнитка FBO'!N27+'Юнитка FBO'!O27+'Юнитка FBO'!P27+'Юнитка FBO'!Q27+'Юнитка FBO'!R27+'Юнитка FBO'!S27+'Юнитка FBO'!V27+'Юнитка FBO'!X27+'Юнитка FBO'!Y27+'Юнитка FBO'!AK27</f>
         <v/>
       </c>
-      <c r="H24" s="40">
+      <c r="H24" s="41">
         <f>'Юнитка FBO'!G27-'Юнитка FBO'!I27</f>
         <v/>
       </c>
-      <c r="I24" s="40">
+      <c r="I24" s="41">
         <f>MAX(0,G24-H24)+$B$4</f>
         <v/>
       </c>
-      <c r="J24" s="40">
+      <c r="J24" s="41">
         <f>E24*I24</f>
         <v/>
       </c>
-      <c r="K24" s="40">
+      <c r="K24" s="41">
         <f>C24+J24</f>
         <v/>
       </c>
-      <c r="L24" s="40">
+      <c r="L24" s="41">
         <f>'Юнитка FBO'!AG27</f>
         <v/>
       </c>
-      <c r="M24" s="40">
-        <f>D24*L24</f>
+      <c r="M24" s="41">
+        <f>D24*L24*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N24" s="41">
+        <f>D24*L24*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O24" s="41">
+        <f>D24*L24*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P24" s="41">
+        <f>D24*L24*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="39">
+      <c r="A25" s="40">
         <f>'Юнитка FBO'!A28</f>
         <v/>
       </c>
-      <c r="B25" s="40">
+      <c r="B25" s="41">
         <f>'Юнитка FBO'!C28</f>
         <v/>
       </c>
-      <c r="C25" s="40">
+      <c r="C25" s="41">
         <f>B25*$B$2</f>
         <v/>
       </c>
-      <c r="D25" s="40">
+      <c r="D25" s="41">
         <f>'Юнитка FBO'!E28</f>
         <v/>
       </c>
-      <c r="E25" s="40">
+      <c r="E25" s="41">
         <f>ROUND(D25*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F25" s="40">
+      <c r="F25" s="41">
         <f>'Юнитка FBO'!I28</f>
         <v/>
       </c>
-      <c r="G25" s="40">
+      <c r="G25" s="41">
         <f>'Юнитка FBO'!K28+'Юнитка FBO'!N28+'Юнитка FBO'!O28+'Юнитка FBO'!P28+'Юнитка FBO'!Q28+'Юнитка FBO'!R28+'Юнитка FBO'!S28+'Юнитка FBO'!V28+'Юнитка FBO'!X28+'Юнитка FBO'!Y28+'Юнитка FBO'!AK28</f>
         <v/>
       </c>
-      <c r="H25" s="40">
+      <c r="H25" s="41">
         <f>'Юнитка FBO'!G28-'Юнитка FBO'!I28</f>
         <v/>
       </c>
-      <c r="I25" s="40">
+      <c r="I25" s="41">
         <f>MAX(0,G25-H25)+$B$4</f>
         <v/>
       </c>
-      <c r="J25" s="40">
+      <c r="J25" s="41">
         <f>E25*I25</f>
         <v/>
       </c>
-      <c r="K25" s="40">
+      <c r="K25" s="41">
         <f>C25+J25</f>
         <v/>
       </c>
-      <c r="L25" s="40">
+      <c r="L25" s="41">
         <f>'Юнитка FBO'!AG28</f>
         <v/>
       </c>
-      <c r="M25" s="40">
-        <f>D25*L25</f>
+      <c r="M25" s="41">
+        <f>D25*L25*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N25" s="41">
+        <f>D25*L25*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O25" s="41">
+        <f>D25*L25*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P25" s="41">
+        <f>D25*L25*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="39">
+      <c r="A26" s="40">
         <f>'Юнитка FBO'!A29</f>
         <v/>
       </c>
-      <c r="B26" s="40">
+      <c r="B26" s="41">
         <f>'Юнитка FBO'!C29</f>
         <v/>
       </c>
-      <c r="C26" s="40">
+      <c r="C26" s="41">
         <f>B26*$B$2</f>
         <v/>
       </c>
-      <c r="D26" s="40">
+      <c r="D26" s="41">
         <f>'Юнитка FBO'!E29</f>
         <v/>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="41">
         <f>ROUND(D26*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="41">
         <f>'Юнитка FBO'!I29</f>
         <v/>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="41">
         <f>'Юнитка FBO'!K29+'Юнитка FBO'!N29+'Юнитка FBO'!O29+'Юнитка FBO'!P29+'Юнитка FBO'!Q29+'Юнитка FBO'!R29+'Юнитка FBO'!S29+'Юнитка FBO'!V29+'Юнитка FBO'!X29+'Юнитка FBO'!Y29+'Юнитка FBO'!AK29</f>
         <v/>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="41">
         <f>'Юнитка FBO'!G29-'Юнитка FBO'!I29</f>
         <v/>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="41">
         <f>MAX(0,G26-H26)+$B$4</f>
         <v/>
       </c>
-      <c r="J26" s="40">
+      <c r="J26" s="41">
         <f>E26*I26</f>
         <v/>
       </c>
-      <c r="K26" s="40">
+      <c r="K26" s="41">
         <f>C26+J26</f>
         <v/>
       </c>
-      <c r="L26" s="40">
+      <c r="L26" s="41">
         <f>'Юнитка FBO'!AG29</f>
         <v/>
       </c>
-      <c r="M26" s="40">
-        <f>D26*L26</f>
+      <c r="M26" s="41">
+        <f>D26*L26*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N26" s="41">
+        <f>D26*L26*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O26" s="41">
+        <f>D26*L26*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P26" s="41">
+        <f>D26*L26*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="39">
+      <c r="A27" s="40">
         <f>'Юнитка FBO'!A30</f>
         <v/>
       </c>
-      <c r="B27" s="40">
+      <c r="B27" s="41">
         <f>'Юнитка FBO'!C30</f>
         <v/>
       </c>
-      <c r="C27" s="40">
+      <c r="C27" s="41">
         <f>B27*$B$2</f>
         <v/>
       </c>
-      <c r="D27" s="40">
+      <c r="D27" s="41">
         <f>'Юнитка FBO'!E30</f>
         <v/>
       </c>
-      <c r="E27" s="40">
+      <c r="E27" s="41">
         <f>ROUND(D27*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F27" s="40">
+      <c r="F27" s="41">
         <f>'Юнитка FBO'!I30</f>
         <v/>
       </c>
-      <c r="G27" s="40">
+      <c r="G27" s="41">
         <f>'Юнитка FBO'!K30+'Юнитка FBO'!N30+'Юнитка FBO'!O30+'Юнитка FBO'!P30+'Юнитка FBO'!Q30+'Юнитка FBO'!R30+'Юнитка FBO'!S30+'Юнитка FBO'!V30+'Юнитка FBO'!X30+'Юнитка FBO'!Y30+'Юнитка FBO'!AK30</f>
         <v/>
       </c>
-      <c r="H27" s="40">
+      <c r="H27" s="41">
         <f>'Юнитка FBO'!G30-'Юнитка FBO'!I30</f>
         <v/>
       </c>
-      <c r="I27" s="40">
+      <c r="I27" s="41">
         <f>MAX(0,G27-H27)+$B$4</f>
         <v/>
       </c>
-      <c r="J27" s="40">
+      <c r="J27" s="41">
         <f>E27*I27</f>
         <v/>
       </c>
-      <c r="K27" s="40">
+      <c r="K27" s="41">
         <f>C27+J27</f>
         <v/>
       </c>
-      <c r="L27" s="40">
+      <c r="L27" s="41">
         <f>'Юнитка FBO'!AG30</f>
         <v/>
       </c>
-      <c r="M27" s="40">
-        <f>D27*L27</f>
+      <c r="M27" s="41">
+        <f>D27*L27*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N27" s="41">
+        <f>D27*L27*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O27" s="41">
+        <f>D27*L27*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P27" s="41">
+        <f>D27*L27*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="39">
+      <c r="A28" s="40">
         <f>'Юнитка FBO'!A31</f>
         <v/>
       </c>
-      <c r="B28" s="40">
+      <c r="B28" s="41">
         <f>'Юнитка FBO'!C31</f>
         <v/>
       </c>
-      <c r="C28" s="40">
+      <c r="C28" s="41">
         <f>B28*$B$2</f>
         <v/>
       </c>
-      <c r="D28" s="40">
+      <c r="D28" s="41">
         <f>'Юнитка FBO'!E31</f>
         <v/>
       </c>
-      <c r="E28" s="40">
+      <c r="E28" s="41">
         <f>ROUND(D28*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F28" s="40">
+      <c r="F28" s="41">
         <f>'Юнитка FBO'!I31</f>
         <v/>
       </c>
-      <c r="G28" s="40">
+      <c r="G28" s="41">
         <f>'Юнитка FBO'!K31+'Юнитка FBO'!N31+'Юнитка FBO'!O31+'Юнитка FBO'!P31+'Юнитка FBO'!Q31+'Юнитка FBO'!R31+'Юнитка FBO'!S31+'Юнитка FBO'!V31+'Юнитка FBO'!X31+'Юнитка FBO'!Y31+'Юнитка FBO'!AK31</f>
         <v/>
       </c>
-      <c r="H28" s="40">
+      <c r="H28" s="41">
         <f>'Юнитка FBO'!G31-'Юнитка FBO'!I31</f>
         <v/>
       </c>
-      <c r="I28" s="40">
+      <c r="I28" s="41">
         <f>MAX(0,G28-H28)+$B$4</f>
         <v/>
       </c>
-      <c r="J28" s="40">
+      <c r="J28" s="41">
         <f>E28*I28</f>
         <v/>
       </c>
-      <c r="K28" s="40">
+      <c r="K28" s="41">
         <f>C28+J28</f>
         <v/>
       </c>
-      <c r="L28" s="40">
+      <c r="L28" s="41">
         <f>'Юнитка FBO'!AG31</f>
         <v/>
       </c>
-      <c r="M28" s="40">
-        <f>D28*L28</f>
+      <c r="M28" s="41">
+        <f>D28*L28*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N28" s="41">
+        <f>D28*L28*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O28" s="41">
+        <f>D28*L28*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P28" s="41">
+        <f>D28*L28*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="39">
+      <c r="A29" s="40">
         <f>'Юнитка FBO'!A32</f>
         <v/>
       </c>
-      <c r="B29" s="40">
+      <c r="B29" s="41">
         <f>'Юнитка FBO'!C32</f>
         <v/>
       </c>
-      <c r="C29" s="40">
+      <c r="C29" s="41">
         <f>B29*$B$2</f>
         <v/>
       </c>
-      <c r="D29" s="40">
+      <c r="D29" s="41">
         <f>'Юнитка FBO'!E32</f>
         <v/>
       </c>
-      <c r="E29" s="40">
+      <c r="E29" s="41">
         <f>ROUND(D29*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F29" s="40">
+      <c r="F29" s="41">
         <f>'Юнитка FBO'!I32</f>
         <v/>
       </c>
-      <c r="G29" s="40">
+      <c r="G29" s="41">
         <f>'Юнитка FBO'!K32+'Юнитка FBO'!N32+'Юнитка FBO'!O32+'Юнитка FBO'!P32+'Юнитка FBO'!Q32+'Юнитка FBO'!R32+'Юнитка FBO'!S32+'Юнитка FBO'!V32+'Юнитка FBO'!X32+'Юнитка FBO'!Y32+'Юнитка FBO'!AK32</f>
         <v/>
       </c>
-      <c r="H29" s="40">
+      <c r="H29" s="41">
         <f>'Юнитка FBO'!G32-'Юнитка FBO'!I32</f>
         <v/>
       </c>
-      <c r="I29" s="40">
+      <c r="I29" s="41">
         <f>MAX(0,G29-H29)+$B$4</f>
         <v/>
       </c>
-      <c r="J29" s="40">
+      <c r="J29" s="41">
         <f>E29*I29</f>
         <v/>
       </c>
-      <c r="K29" s="40">
+      <c r="K29" s="41">
         <f>C29+J29</f>
         <v/>
       </c>
-      <c r="L29" s="40">
+      <c r="L29" s="41">
         <f>'Юнитка FBO'!AG32</f>
         <v/>
       </c>
-      <c r="M29" s="40">
-        <f>D29*L29</f>
+      <c r="M29" s="41">
+        <f>D29*L29*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N29" s="41">
+        <f>D29*L29*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O29" s="41">
+        <f>D29*L29*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P29" s="41">
+        <f>D29*L29*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="39">
+      <c r="A30" s="40">
         <f>'Юнитка FBO'!A33</f>
         <v/>
       </c>
-      <c r="B30" s="40">
+      <c r="B30" s="41">
         <f>'Юнитка FBO'!C33</f>
         <v/>
       </c>
-      <c r="C30" s="40">
+      <c r="C30" s="41">
         <f>B30*$B$2</f>
         <v/>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="41">
         <f>'Юнитка FBO'!E33</f>
         <v/>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="41">
         <f>ROUND(D30*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="41">
         <f>'Юнитка FBO'!I33</f>
         <v/>
       </c>
-      <c r="G30" s="40">
+      <c r="G30" s="41">
         <f>'Юнитка FBO'!K33+'Юнитка FBO'!N33+'Юнитка FBO'!O33+'Юнитка FBO'!P33+'Юнитка FBO'!Q33+'Юнитка FBO'!R33+'Юнитка FBO'!S33+'Юнитка FBO'!V33+'Юнитка FBO'!X33+'Юнитка FBO'!Y33+'Юнитка FBO'!AK33</f>
         <v/>
       </c>
-      <c r="H30" s="40">
+      <c r="H30" s="41">
         <f>'Юнитка FBO'!G33-'Юнитка FBO'!I33</f>
         <v/>
       </c>
-      <c r="I30" s="40">
+      <c r="I30" s="41">
         <f>MAX(0,G30-H30)+$B$4</f>
         <v/>
       </c>
-      <c r="J30" s="40">
+      <c r="J30" s="41">
         <f>E30*I30</f>
         <v/>
       </c>
-      <c r="K30" s="40">
+      <c r="K30" s="41">
         <f>C30+J30</f>
         <v/>
       </c>
-      <c r="L30" s="40">
+      <c r="L30" s="41">
         <f>'Юнитка FBO'!AG33</f>
         <v/>
       </c>
-      <c r="M30" s="40">
-        <f>D30*L30</f>
+      <c r="M30" s="41">
+        <f>D30*L30*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N30" s="41">
+        <f>D30*L30*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O30" s="41">
+        <f>D30*L30*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P30" s="41">
+        <f>D30*L30*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="39">
+      <c r="A31" s="40">
         <f>'Юнитка FBO'!A34</f>
         <v/>
       </c>
-      <c r="B31" s="40">
+      <c r="B31" s="41">
         <f>'Юнитка FBO'!C34</f>
         <v/>
       </c>
-      <c r="C31" s="40">
+      <c r="C31" s="41">
         <f>B31*$B$2</f>
         <v/>
       </c>
-      <c r="D31" s="40">
+      <c r="D31" s="41">
         <f>'Юнитка FBO'!E34</f>
         <v/>
       </c>
-      <c r="E31" s="40">
+      <c r="E31" s="41">
         <f>ROUND(D31*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F31" s="40">
+      <c r="F31" s="41">
         <f>'Юнитка FBO'!I34</f>
         <v/>
       </c>
-      <c r="G31" s="40">
+      <c r="G31" s="41">
         <f>'Юнитка FBO'!K34+'Юнитка FBO'!N34+'Юнитка FBO'!O34+'Юнитка FBO'!P34+'Юнитка FBO'!Q34+'Юнитка FBO'!R34+'Юнитка FBO'!S34+'Юнитка FBO'!V34+'Юнитка FBO'!X34+'Юнитка FBO'!Y34+'Юнитка FBO'!AK34</f>
         <v/>
       </c>
-      <c r="H31" s="40">
+      <c r="H31" s="41">
         <f>'Юнитка FBO'!G34-'Юнитка FBO'!I34</f>
         <v/>
       </c>
-      <c r="I31" s="40">
+      <c r="I31" s="41">
         <f>MAX(0,G31-H31)+$B$4</f>
         <v/>
       </c>
-      <c r="J31" s="40">
+      <c r="J31" s="41">
         <f>E31*I31</f>
         <v/>
       </c>
-      <c r="K31" s="40">
+      <c r="K31" s="41">
         <f>C31+J31</f>
         <v/>
       </c>
-      <c r="L31" s="40">
+      <c r="L31" s="41">
         <f>'Юнитка FBO'!AG34</f>
         <v/>
       </c>
-      <c r="M31" s="40">
-        <f>D31*L31</f>
+      <c r="M31" s="41">
+        <f>D31*L31*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N31" s="41">
+        <f>D31*L31*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O31" s="41">
+        <f>D31*L31*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P31" s="41">
+        <f>D31*L31*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="39">
+      <c r="A32" s="40">
         <f>'Юнитка FBO'!A35</f>
         <v/>
       </c>
-      <c r="B32" s="40">
+      <c r="B32" s="41">
         <f>'Юнитка FBO'!C35</f>
         <v/>
       </c>
-      <c r="C32" s="40">
+      <c r="C32" s="41">
         <f>B32*$B$2</f>
         <v/>
       </c>
-      <c r="D32" s="40">
+      <c r="D32" s="41">
         <f>'Юнитка FBO'!E35</f>
         <v/>
       </c>
-      <c r="E32" s="40">
+      <c r="E32" s="41">
         <f>ROUND(D32*$B$3,0)</f>
         <v/>
       </c>
-      <c r="F32" s="40">
+      <c r="F32" s="41">
         <f>'Юнитка FBO'!I35</f>
         <v/>
       </c>
-      <c r="G32" s="40">
+      <c r="G32" s="41">
         <f>'Юнитка FBO'!K35+'Юнитка FBO'!N35+'Юнитка FBO'!O35+'Юнитка FBO'!P35+'Юнитка FBO'!Q35+'Юнитка FBO'!R35+'Юнитка FBO'!S35+'Юнитка FBO'!V35+'Юнитка FBO'!X35+'Юнитка FBO'!Y35+'Юнитка FBO'!AK35</f>
         <v/>
       </c>
-      <c r="H32" s="40">
+      <c r="H32" s="41">
         <f>'Юнитка FBO'!G35-'Юнитка FBO'!I35</f>
         <v/>
       </c>
-      <c r="I32" s="40">
+      <c r="I32" s="41">
         <f>MAX(0,G32-H32)+$B$4</f>
         <v/>
       </c>
-      <c r="J32" s="40">
+      <c r="J32" s="41">
         <f>E32*I32</f>
         <v/>
       </c>
-      <c r="K32" s="40">
+      <c r="K32" s="41">
         <f>C32+J32</f>
         <v/>
       </c>
-      <c r="L32" s="40">
+      <c r="L32" s="41">
         <f>'Юнитка FBO'!AG35</f>
         <v/>
       </c>
-      <c r="M32" s="40">
-        <f>D32*L32</f>
+      <c r="M32" s="41">
+        <f>D32*L32*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N32" s="41">
+        <f>D32*L32*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O32" s="41">
+        <f>D32*L32*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P32" s="41">
+        <f>D32*L32*($B$5+3*$B$6)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="41" t="inlineStr">
+      <c r="A33" s="42" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B33" s="42">
+      <c r="B33" s="43">
         <f>SUM(B10:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="42">
+      <c r="C33" s="43">
         <f>SUM(C10:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="42">
+      <c r="D33" s="43">
         <f>SUM(D10:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="42">
+      <c r="E33" s="43">
         <f>SUM(E10:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="41" t="n"/>
-      <c r="G33" s="41" t="n"/>
-      <c r="H33" s="41" t="n"/>
-      <c r="I33" s="41" t="n"/>
-      <c r="J33" s="42">
+      <c r="F33" s="42" t="n"/>
+      <c r="G33" s="42" t="n"/>
+      <c r="H33" s="42" t="n"/>
+      <c r="I33" s="42" t="n"/>
+      <c r="J33" s="43">
         <f>SUM(J10:J32)</f>
         <v/>
       </c>
-      <c r="K33" s="42">
+      <c r="K33" s="43">
         <f>SUM(K10:K32)</f>
         <v/>
       </c>
-      <c r="L33" s="41" t="n"/>
-      <c r="M33" s="42">
+      <c r="L33" s="42" t="n"/>
+      <c r="M33" s="43">
         <f>SUM(M10:M32)</f>
         <v/>
       </c>
+      <c r="N33" s="43">
+        <f>SUM(N10:N32)</f>
+        <v/>
+      </c>
+      <c r="O33" s="43">
+        <f>SUM(O10:O32)</f>
+        <v/>
+      </c>
+      <c r="P33" s="43">
+        <f>SUM(P10:P32)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr">
+      <c r="A36" s="44" t="inlineStr">
         <is>
           <t>План по месяцам: раскрутка + выход на продажи (доля от конкурента растёт на +10 п.п./мес)</t>
         </is>
@@ -8048,177 +8362,177 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="39" t="inlineStr">
+      <c r="A38" s="40" t="inlineStr">
         <is>
           <t>Август (раскрутка)</t>
         </is>
       </c>
-      <c r="B38" s="44" t="n">
+      <c r="B38" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="C38" s="40" t="n">
+      <c r="C38" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="D38" s="40" t="n">
+      <c r="D38" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="E38" s="40">
+      <c r="E38" s="41">
         <f>$K$33</f>
         <v/>
       </c>
-      <c r="F38" s="40">
+      <c r="F38" s="41">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="40">
+      <c r="G38" s="41">
         <f>F38</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="39" t="inlineStr">
+      <c r="A39" s="40" t="inlineStr">
         <is>
           <t>Сентябрь</t>
         </is>
       </c>
-      <c r="B39" s="44">
+      <c r="B39" s="45">
         <f>$B$5+0*$B$6</f>
         <v/>
       </c>
-      <c r="C39" s="40">
+      <c r="C39" s="41">
         <f>ROUND(B39*$D$33,0)</f>
         <v/>
       </c>
-      <c r="D39" s="40">
-        <f>B39*$M$33</f>
-        <v/>
-      </c>
-      <c r="E39" s="40" t="n">
+      <c r="D39" s="41">
+        <f>M33</f>
+        <v/>
+      </c>
+      <c r="E39" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="40">
+      <c r="F39" s="41">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="40">
+      <c r="G39" s="41">
         <f>G38+F39</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>Октябрь</t>
         </is>
       </c>
-      <c r="B40" s="44">
+      <c r="B40" s="45">
         <f>$B$5+1*$B$6</f>
         <v/>
       </c>
-      <c r="C40" s="40">
+      <c r="C40" s="41">
         <f>ROUND(B40*$D$33,0)</f>
         <v/>
       </c>
-      <c r="D40" s="40">
-        <f>B40*$M$33</f>
-        <v/>
-      </c>
-      <c r="E40" s="40" t="n">
+      <c r="D40" s="41">
+        <f>N33</f>
+        <v/>
+      </c>
+      <c r="E40" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="40">
+      <c r="F40" s="41">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="40">
+      <c r="G40" s="41">
         <f>G39+F40</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>Ноябрь</t>
         </is>
       </c>
-      <c r="B41" s="44">
+      <c r="B41" s="45">
         <f>$B$5+2*$B$6</f>
         <v/>
       </c>
-      <c r="C41" s="40">
+      <c r="C41" s="41">
         <f>ROUND(B41*$D$33,0)</f>
         <v/>
       </c>
-      <c r="D41" s="40">
-        <f>B41*$M$33</f>
-        <v/>
-      </c>
-      <c r="E41" s="40" t="n">
+      <c r="D41" s="41">
+        <f>O33</f>
+        <v/>
+      </c>
+      <c r="E41" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="40">
+      <c r="F41" s="41">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="40">
+      <c r="G41" s="41">
         <f>G40+F41</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B42" s="44">
+      <c r="B42" s="45">
         <f>$B$5+3*$B$6</f>
         <v/>
       </c>
-      <c r="C42" s="40">
+      <c r="C42" s="41">
         <f>ROUND(B42*$D$33,0)</f>
         <v/>
       </c>
-      <c r="D42" s="40">
-        <f>B42*$M$33</f>
-        <v/>
-      </c>
-      <c r="E42" s="40" t="n">
+      <c r="D42" s="41">
+        <f>P33</f>
+        <v/>
+      </c>
+      <c r="E42" s="41" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="40">
+      <c r="F42" s="41">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="40">
+      <c r="G42" s="41">
         <f>G41+F42</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="41" t="inlineStr">
+      <c r="A43" s="42" t="inlineStr">
         <is>
           <t>Итого за период</t>
         </is>
       </c>
-      <c r="B43" s="41" t="n"/>
-      <c r="C43" s="42">
+      <c r="B43" s="42" t="n"/>
+      <c r="C43" s="43">
         <f>SUM(C38:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="42">
+      <c r="D43" s="43">
         <f>SUM(D38:D42)</f>
         <v/>
       </c>
-      <c r="E43" s="42">
+      <c r="E43" s="43">
         <f>SUM(E38:E42)</f>
         <v/>
       </c>
-      <c r="F43" s="42">
+      <c r="F43" s="43">
         <f>SUM(F38:F42)</f>
         <v/>
       </c>
-      <c r="G43" s="42">
+      <c r="G43" s="43">
         <f>G42</f>
         <v/>
       </c>
@@ -8229,7 +8543,7 @@
           <t>Разовые расходы на раскрутку (август), ₽</t>
         </is>
       </c>
-      <c r="B45" s="42">
+      <c r="B45" s="43">
         <f>$K$33</f>
         <v/>
       </c>
@@ -8240,8 +8554,8 @@
           <t>Прибыль при 100% продаж конкурента, ₽/мес</t>
         </is>
       </c>
-      <c r="B46" s="42">
-        <f>$M$33</f>
+      <c r="B46" s="43">
+        <f>SUMPRODUCT(D10:D32,L10:L32)</f>
         <v/>
       </c>
     </row>
@@ -8251,7 +8565,7 @@
           <t>Накопительный поток к декабрю, ₽</t>
         </is>
       </c>
-      <c r="B47" s="42">
+      <c r="B47" s="43">
         <f>G42</f>
         <v/>
       </c>
@@ -8262,8 +8576,8 @@
           <t>Окупаемость раскрутки, мес продаж (при 100%)</t>
         </is>
       </c>
-      <c r="B48" s="45">
-        <f>IF($M$33&gt;0,$K$33/$M$33,"—")</f>
+      <c r="B48" s="46">
+        <f>IF(SUMPRODUCT(D10:D32,L10:L32)&gt;0,$K$33/SUMPRODUCT(D10:D32,L10:L32),"—")</f>
         <v/>
       </c>
     </row>

--- a/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
+++ b/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
@@ -239,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -306,10 +306,11 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -6580,7 +6581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6599,6 +6600,7 @@
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="15" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6746,6 +6748,11 @@
           <t>Прибыль Декабрь, ₽</t>
         </is>
       </c>
+      <c r="Q9" s="38" t="inlineStr">
+        <is>
+          <t>ROI инвестиций (Сен–Дек)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="40">
@@ -6812,6 +6819,10 @@
         <f>D10*L10*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q10" s="42">
+        <f>IF(K10&gt;0,(M10+N10+O10+P10-K10)/K10,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="40">
@@ -6878,6 +6889,10 @@
         <f>D11*L11*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q11" s="42">
+        <f>IF(K11&gt;0,(M11+N11+O11+P11-K11)/K11,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="40">
@@ -6944,6 +6959,10 @@
         <f>D12*L12*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q12" s="42">
+        <f>IF(K12&gt;0,(M12+N12+O12+P12-K12)/K12,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="40">
@@ -7010,6 +7029,10 @@
         <f>D13*L13*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q13" s="42">
+        <f>IF(K13&gt;0,(M13+N13+O13+P13-K13)/K13,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="40">
@@ -7076,6 +7099,10 @@
         <f>D14*L14*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q14" s="42">
+        <f>IF(K14&gt;0,(M14+N14+O14+P14-K14)/K14,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="40">
@@ -7142,6 +7169,10 @@
         <f>D15*L15*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q15" s="42">
+        <f>IF(K15&gt;0,(M15+N15+O15+P15-K15)/K15,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="40">
@@ -7208,6 +7239,10 @@
         <f>D16*L16*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q16" s="42">
+        <f>IF(K16&gt;0,(M16+N16+O16+P16-K16)/K16,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="40">
@@ -7274,6 +7309,10 @@
         <f>D17*L17*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q17" s="42">
+        <f>IF(K17&gt;0,(M17+N17+O17+P17-K17)/K17,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="40">
@@ -7340,6 +7379,10 @@
         <f>D18*L18*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q18" s="42">
+        <f>IF(K18&gt;0,(M18+N18+O18+P18-K18)/K18,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="40">
@@ -7406,6 +7449,10 @@
         <f>D19*L19*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q19" s="42">
+        <f>IF(K19&gt;0,(M19+N19+O19+P19-K19)/K19,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="40">
@@ -7472,6 +7519,10 @@
         <f>D20*L20*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q20" s="42">
+        <f>IF(K20&gt;0,(M20+N20+O20+P20-K20)/K20,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="40">
@@ -7538,6 +7589,10 @@
         <f>D21*L21*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q21" s="42">
+        <f>IF(K21&gt;0,(M21+N21+O21+P21-K21)/K21,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="40">
@@ -7604,6 +7659,10 @@
         <f>D22*L22*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q22" s="42">
+        <f>IF(K22&gt;0,(M22+N22+O22+P22-K22)/K22,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="40">
@@ -7670,6 +7729,10 @@
         <f>D23*L23*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q23" s="42">
+        <f>IF(K23&gt;0,(M23+N23+O23+P23-K23)/K23,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="40">
@@ -7736,6 +7799,10 @@
         <f>D24*L24*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q24" s="42">
+        <f>IF(K24&gt;0,(M24+N24+O24+P24-K24)/K24,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="40">
@@ -7802,6 +7869,10 @@
         <f>D25*L25*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q25" s="42">
+        <f>IF(K25&gt;0,(M25+N25+O25+P25-K25)/K25,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="40">
@@ -7868,6 +7939,10 @@
         <f>D26*L26*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q26" s="42">
+        <f>IF(K26&gt;0,(M26+N26+O26+P26-K26)/K26,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="40">
@@ -7934,6 +8009,10 @@
         <f>D27*L27*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q27" s="42">
+        <f>IF(K27&gt;0,(M27+N27+O27+P27-K27)/K27,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="40">
@@ -8000,6 +8079,10 @@
         <f>D28*L28*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q28" s="42">
+        <f>IF(K28&gt;0,(M28+N28+O28+P28-K28)/K28,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="40">
@@ -8066,6 +8149,10 @@
         <f>D29*L29*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q29" s="42">
+        <f>IF(K29&gt;0,(M29+N29+O29+P29-K29)/K29,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="40">
@@ -8132,6 +8219,10 @@
         <f>D30*L30*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q30" s="42">
+        <f>IF(K30&gt;0,(M30+N30+O30+P30-K30)/K30,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="40">
@@ -8198,6 +8289,10 @@
         <f>D31*L31*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q31" s="42">
+        <f>IF(K31&gt;0,(M31+N31+O31+P31-K31)/K31,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="40">
@@ -8264,61 +8359,69 @@
         <f>D32*L32*($B$5+3*$B$6)</f>
         <v/>
       </c>
+      <c r="Q32" s="42">
+        <f>IF(K32&gt;0,(M32+N32+O32+P32-K32)/K32,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="42" t="inlineStr">
+      <c r="A33" s="43" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B33" s="43">
+      <c r="B33" s="44">
         <f>SUM(B10:B32)</f>
         <v/>
       </c>
-      <c r="C33" s="43">
+      <c r="C33" s="44">
         <f>SUM(C10:C32)</f>
         <v/>
       </c>
-      <c r="D33" s="43">
+      <c r="D33" s="44">
         <f>SUM(D10:D32)</f>
         <v/>
       </c>
-      <c r="E33" s="43">
+      <c r="E33" s="44">
         <f>SUM(E10:E32)</f>
         <v/>
       </c>
-      <c r="F33" s="42" t="n"/>
-      <c r="G33" s="42" t="n"/>
-      <c r="H33" s="42" t="n"/>
-      <c r="I33" s="42" t="n"/>
-      <c r="J33" s="43">
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="43" t="n"/>
+      <c r="H33" s="43" t="n"/>
+      <c r="I33" s="43" t="n"/>
+      <c r="J33" s="44">
         <f>SUM(J10:J32)</f>
         <v/>
       </c>
-      <c r="K33" s="43">
+      <c r="K33" s="44">
         <f>SUM(K10:K32)</f>
         <v/>
       </c>
-      <c r="L33" s="42" t="n"/>
-      <c r="M33" s="43">
+      <c r="L33" s="43" t="n"/>
+      <c r="M33" s="44">
         <f>SUM(M10:M32)</f>
         <v/>
       </c>
-      <c r="N33" s="43">
+      <c r="N33" s="44">
         <f>SUM(N10:N32)</f>
         <v/>
       </c>
-      <c r="O33" s="43">
+      <c r="O33" s="44">
         <f>SUM(O10:O32)</f>
         <v/>
       </c>
-      <c r="P33" s="43">
+      <c r="P33" s="44">
         <f>SUM(P10:P32)</f>
         <v/>
       </c>
+      <c r="Q33" s="45">
+        <f>IF(K33&gt;0,(M33+N33+O33+P33-K33)/K33,"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="44" t="inlineStr">
+      <c r="A36" s="46" t="inlineStr">
         <is>
           <t>План по месяцам: раскрутка + выход на продажи (доля от конкурента растёт на +10 п.п./мес)</t>
         </is>
@@ -8367,7 +8470,7 @@
           <t>Август (раскрутка)</t>
         </is>
       </c>
-      <c r="B38" s="45" t="n">
+      <c r="B38" s="42" t="n">
         <v>0</v>
       </c>
       <c r="C38" s="41" t="n">
@@ -8395,7 +8498,7 @@
           <t>Сентябрь</t>
         </is>
       </c>
-      <c r="B39" s="45">
+      <c r="B39" s="42">
         <f>$B$5+0*$B$6</f>
         <v/>
       </c>
@@ -8425,7 +8528,7 @@
           <t>Октябрь</t>
         </is>
       </c>
-      <c r="B40" s="45">
+      <c r="B40" s="42">
         <f>$B$5+1*$B$6</f>
         <v/>
       </c>
@@ -8455,7 +8558,7 @@
           <t>Ноябрь</t>
         </is>
       </c>
-      <c r="B41" s="45">
+      <c r="B41" s="42">
         <f>$B$5+2*$B$6</f>
         <v/>
       </c>
@@ -8485,7 +8588,7 @@
           <t>Декабрь</t>
         </is>
       </c>
-      <c r="B42" s="45">
+      <c r="B42" s="42">
         <f>$B$5+3*$B$6</f>
         <v/>
       </c>
@@ -8510,29 +8613,29 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="42" t="inlineStr">
+      <c r="A43" s="43" t="inlineStr">
         <is>
           <t>Итого за период</t>
         </is>
       </c>
-      <c r="B43" s="42" t="n"/>
-      <c r="C43" s="43">
+      <c r="B43" s="43" t="n"/>
+      <c r="C43" s="44">
         <f>SUM(C38:C42)</f>
         <v/>
       </c>
-      <c r="D43" s="43">
+      <c r="D43" s="44">
         <f>SUM(D38:D42)</f>
         <v/>
       </c>
-      <c r="E43" s="43">
+      <c r="E43" s="44">
         <f>SUM(E38:E42)</f>
         <v/>
       </c>
-      <c r="F43" s="43">
+      <c r="F43" s="44">
         <f>SUM(F38:F42)</f>
         <v/>
       </c>
-      <c r="G43" s="43">
+      <c r="G43" s="44">
         <f>G42</f>
         <v/>
       </c>
@@ -8543,7 +8646,7 @@
           <t>Разовые расходы на раскрутку (август), ₽</t>
         </is>
       </c>
-      <c r="B45" s="43">
+      <c r="B45" s="44">
         <f>$K$33</f>
         <v/>
       </c>
@@ -8554,7 +8657,7 @@
           <t>Прибыль при 100% продаж конкурента, ₽/мес</t>
         </is>
       </c>
-      <c r="B46" s="43">
+      <c r="B46" s="44">
         <f>SUMPRODUCT(D10:D32,L10:L32)</f>
         <v/>
       </c>
@@ -8565,7 +8668,7 @@
           <t>Накопительный поток к декабрю, ₽</t>
         </is>
       </c>
-      <c r="B47" s="43">
+      <c r="B47" s="44">
         <f>G42</f>
         <v/>
       </c>
@@ -8576,7 +8679,7 @@
           <t>Окупаемость раскрутки, мес продаж (при 100%)</t>
         </is>
       </c>
-      <c r="B48" s="46">
+      <c r="B48" s="47">
         <f>IF(SUMPRODUCT(D10:D32,L10:L32)&gt;0,$K$33/SUMPRODUCT(D10:D32,L10:L32),"—")</f>
         <v/>
       </c>

--- a/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
+++ b/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
@@ -316,6 +316,28 @@
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -8685,6 +8707,14 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="Q10:Q33">
+    <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
+      <formula>0</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="greaterThanOrEqual" dxfId="1">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
+++ b/outputs/ozon/ozon_raskrutka_samovykup_2026-08-14.xlsx
@@ -239,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -307,11 +307,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="9" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -6603,7 +6604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q48"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -6623,6 +6624,8 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6683,176 +6686,126 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="37" t="inlineStr">
-        <is>
-          <t>Самовыкуп: платим цену с СПП (покупатель), получаем выплату Ozon с цены продавца (СПП финансирует Ozon), товар возвращается на склад → теряем только сборы Ozon сверх компенсации СПП + прочие расходы. Прибыль по месяцам = доля от конкурента (растёт +10 п.п./мес) × маржа/шт.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A7" s="34" t="inlineStr">
+        <is>
+          <t>Доля продаж для оценки срока распродажи остатка</t>
+        </is>
+      </c>
+      <c r="B7" s="36" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="37" t="inlineStr">
+        <is>
+          <t>Самовыкуп: платим цену с СПП (покупатель), получаем выплату Ozon с цены продавца (СПП финансирует Ozon), товар возвращается на склад → теряем только сборы Ozon сверх компенсации СПП + прочие расходы. Прибыль по месяцам = доля от конкурента (растёт +10 п.п./мес) × маржа/шт. Срок распродажи остатка = остаток / (продажи в мес при оценочной доле).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="48" customHeight="1">
+      <c r="A10" s="38" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B10" s="38" t="inlineStr">
         <is>
           <t>Отзывов, шт</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C10" s="38" t="inlineStr">
         <is>
           <t>Отзывы, ₽</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
+      <c r="D10" s="38" t="inlineStr">
         <is>
           <t>Заказы конкур., шт</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E10" s="38" t="inlineStr">
         <is>
           <t>Самовыкупов, шт</t>
         </is>
       </c>
-      <c r="F9" s="38" t="inlineStr">
+      <c r="F10" s="38" t="inlineStr">
         <is>
           <t>Цена выкупа (с СПП), ₽</t>
         </is>
       </c>
-      <c r="G9" s="38" t="inlineStr">
+      <c r="G10" s="38" t="inlineStr">
         <is>
           <t>Сборы Ozon / выкуп, ₽</t>
         </is>
       </c>
-      <c r="H9" s="38" t="inlineStr">
+      <c r="H10" s="38" t="inlineStr">
         <is>
           <t>Компенсация СПП, ₽</t>
         </is>
       </c>
-      <c r="I9" s="38" t="inlineStr">
+      <c r="I10" s="38" t="inlineStr">
         <is>
           <t>Безвозврат / выкуп, ₽</t>
         </is>
       </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="J10" s="38" t="inlineStr">
         <is>
           <t>Самовыкупы, ₽</t>
         </is>
       </c>
-      <c r="K9" s="38" t="inlineStr">
+      <c r="K10" s="38" t="inlineStr">
         <is>
           <t>Расходы 1-й мес, ₽</t>
         </is>
       </c>
-      <c r="L9" s="38" t="inlineStr">
+      <c r="L10" s="38" t="inlineStr">
         <is>
           <t>Маржа/шт, ₽</t>
         </is>
       </c>
-      <c r="M9" s="39" t="inlineStr">
+      <c r="M10" s="39" t="inlineStr">
         <is>
           <t>Прибыль Сентябрь, ₽</t>
         </is>
       </c>
-      <c r="N9" s="39" t="inlineStr">
+      <c r="N10" s="39" t="inlineStr">
         <is>
           <t>Прибыль Октябрь, ₽</t>
         </is>
       </c>
-      <c r="O9" s="39" t="inlineStr">
+      <c r="O10" s="39" t="inlineStr">
         <is>
           <t>Прибыль Ноябрь, ₽</t>
         </is>
       </c>
-      <c r="P9" s="39" t="inlineStr">
+      <c r="P10" s="39" t="inlineStr">
         <is>
           <t>Прибыль Декабрь, ₽</t>
         </is>
       </c>
-      <c r="Q9" s="38" t="inlineStr">
+      <c r="Q10" s="38" t="inlineStr">
         <is>
           <t>ROI инвестиций (Сен–Дек)</t>
         </is>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="40">
-        <f>'Юнитка FBO'!A13</f>
-        <v/>
-      </c>
-      <c r="B10" s="41">
-        <f>'Юнитка FBO'!C13</f>
-        <v/>
-      </c>
-      <c r="C10" s="41">
-        <f>B10*$B$2</f>
-        <v/>
-      </c>
-      <c r="D10" s="41">
-        <f>'Юнитка FBO'!E13</f>
-        <v/>
-      </c>
-      <c r="E10" s="41">
-        <f>ROUND(D10*$B$3,0)</f>
-        <v/>
-      </c>
-      <c r="F10" s="41">
-        <f>'Юнитка FBO'!I13</f>
-        <v/>
-      </c>
-      <c r="G10" s="41">
-        <f>'Юнитка FBO'!K13+'Юнитка FBO'!N13+'Юнитка FBO'!O13+'Юнитка FBO'!P13+'Юнитка FBO'!Q13+'Юнитка FBO'!R13+'Юнитка FBO'!S13+'Юнитка FBO'!V13+'Юнитка FBO'!X13+'Юнитка FBO'!Y13+'Юнитка FBO'!AK13</f>
-        <v/>
-      </c>
-      <c r="H10" s="41">
-        <f>'Юнитка FBO'!G13-'Юнитка FBO'!I13</f>
-        <v/>
-      </c>
-      <c r="I10" s="41">
-        <f>MAX(0,G10-H10)+$B$4</f>
-        <v/>
-      </c>
-      <c r="J10" s="41">
-        <f>E10*I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="41">
-        <f>C10+J10</f>
-        <v/>
-      </c>
-      <c r="L10" s="41">
-        <f>'Юнитка FBO'!AG13</f>
-        <v/>
-      </c>
-      <c r="M10" s="41">
-        <f>D10*L10*($B$5+0*$B$6)</f>
-        <v/>
-      </c>
-      <c r="N10" s="41">
-        <f>D10*L10*($B$5+1*$B$6)</f>
-        <v/>
-      </c>
-      <c r="O10" s="41">
-        <f>D10*L10*($B$5+2*$B$6)</f>
-        <v/>
-      </c>
-      <c r="P10" s="41">
-        <f>D10*L10*($B$5+3*$B$6)</f>
-        <v/>
-      </c>
-      <c r="Q10" s="42">
-        <f>IF(K10&gt;0,(M10+N10+O10+P10-K10)/K10,"—")</f>
-        <v/>
+      <c r="R10" s="38" t="inlineStr">
+        <is>
+          <t>Остаток, шт</t>
+        </is>
+      </c>
+      <c r="S10" s="38" t="inlineStr">
+        <is>
+          <t>Распродажа остатка, мес</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="40">
-        <f>'Юнитка FBO'!A14</f>
+        <f>'Юнитка FBO'!A13</f>
         <v/>
       </c>
       <c r="B11" s="41">
-        <f>'Юнитка FBO'!C14</f>
+        <f>'Юнитка FBO'!C13</f>
         <v/>
       </c>
       <c r="C11" s="41">
@@ -6860,7 +6813,7 @@
         <v/>
       </c>
       <c r="D11" s="41">
-        <f>'Юнитка FBO'!E14</f>
+        <f>'Юнитка FBO'!E13</f>
         <v/>
       </c>
       <c r="E11" s="41">
@@ -6868,15 +6821,15 @@
         <v/>
       </c>
       <c r="F11" s="41">
-        <f>'Юнитка FBO'!I14</f>
+        <f>'Юнитка FBO'!I13</f>
         <v/>
       </c>
       <c r="G11" s="41">
-        <f>'Юнитка FBO'!K14+'Юнитка FBO'!N14+'Юнитка FBO'!O14+'Юнитка FBO'!P14+'Юнитка FBO'!Q14+'Юнитка FBO'!R14+'Юнитка FBO'!S14+'Юнитка FBO'!V14+'Юнитка FBO'!X14+'Юнитка FBO'!Y14+'Юнитка FBO'!AK14</f>
+        <f>'Юнитка FBO'!K13+'Юнитка FBO'!N13+'Юнитка FBO'!O13+'Юнитка FBO'!P13+'Юнитка FBO'!Q13+'Юнитка FBO'!R13+'Юнитка FBO'!S13+'Юнитка FBO'!V13+'Юнитка FBO'!X13+'Юнитка FBO'!Y13+'Юнитка FBO'!AK13</f>
         <v/>
       </c>
       <c r="H11" s="41">
-        <f>'Юнитка FBO'!G14-'Юнитка FBO'!I14</f>
+        <f>'Юнитка FBO'!G13-'Юнитка FBO'!I13</f>
         <v/>
       </c>
       <c r="I11" s="41">
@@ -6892,7 +6845,7 @@
         <v/>
       </c>
       <c r="L11" s="41">
-        <f>'Юнитка FBO'!AG14</f>
+        <f>'Юнитка FBO'!AG13</f>
         <v/>
       </c>
       <c r="M11" s="41">
@@ -6915,14 +6868,22 @@
         <f>IF(K11&gt;0,(M11+N11+O11+P11-K11)/K11,"—")</f>
         <v/>
       </c>
+      <c r="R11" s="41">
+        <f>'Юнитка FBO'!B13</f>
+        <v/>
+      </c>
+      <c r="S11" s="43">
+        <f>IF(D11*$B$7&gt;0,R11/(D11*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="40">
-        <f>'Юнитка FBO'!A15</f>
+        <f>'Юнитка FBO'!A14</f>
         <v/>
       </c>
       <c r="B12" s="41">
-        <f>'Юнитка FBO'!C15</f>
+        <f>'Юнитка FBO'!C14</f>
         <v/>
       </c>
       <c r="C12" s="41">
@@ -6930,7 +6891,7 @@
         <v/>
       </c>
       <c r="D12" s="41">
-        <f>'Юнитка FBO'!E15</f>
+        <f>'Юнитка FBO'!E14</f>
         <v/>
       </c>
       <c r="E12" s="41">
@@ -6938,15 +6899,15 @@
         <v/>
       </c>
       <c r="F12" s="41">
-        <f>'Юнитка FBO'!I15</f>
+        <f>'Юнитка FBO'!I14</f>
         <v/>
       </c>
       <c r="G12" s="41">
-        <f>'Юнитка FBO'!K15+'Юнитка FBO'!N15+'Юнитка FBO'!O15+'Юнитка FBO'!P15+'Юнитка FBO'!Q15+'Юнитка FBO'!R15+'Юнитка FBO'!S15+'Юнитка FBO'!V15+'Юнитка FBO'!X15+'Юнитка FBO'!Y15+'Юнитка FBO'!AK15</f>
+        <f>'Юнитка FBO'!K14+'Юнитка FBO'!N14+'Юнитка FBO'!O14+'Юнитка FBO'!P14+'Юнитка FBO'!Q14+'Юнитка FBO'!R14+'Юнитка FBO'!S14+'Юнитка FBO'!V14+'Юнитка FBO'!X14+'Юнитка FBO'!Y14+'Юнитка FBO'!AK14</f>
         <v/>
       </c>
       <c r="H12" s="41">
-        <f>'Юнитка FBO'!G15-'Юнитка FBO'!I15</f>
+        <f>'Юнитка FBO'!G14-'Юнитка FBO'!I14</f>
         <v/>
       </c>
       <c r="I12" s="41">
@@ -6962,7 +6923,7 @@
         <v/>
       </c>
       <c r="L12" s="41">
-        <f>'Юнитка FBO'!AG15</f>
+        <f>'Юнитка FBO'!AG14</f>
         <v/>
       </c>
       <c r="M12" s="41">
@@ -6985,14 +6946,22 @@
         <f>IF(K12&gt;0,(M12+N12+O12+P12-K12)/K12,"—")</f>
         <v/>
       </c>
+      <c r="R12" s="41">
+        <f>'Юнитка FBO'!B14</f>
+        <v/>
+      </c>
+      <c r="S12" s="43">
+        <f>IF(D12*$B$7&gt;0,R12/(D12*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="40">
-        <f>'Юнитка FBO'!A16</f>
+        <f>'Юнитка FBO'!A15</f>
         <v/>
       </c>
       <c r="B13" s="41">
-        <f>'Юнитка FBO'!C16</f>
+        <f>'Юнитка FBO'!C15</f>
         <v/>
       </c>
       <c r="C13" s="41">
@@ -7000,7 +6969,7 @@
         <v/>
       </c>
       <c r="D13" s="41">
-        <f>'Юнитка FBO'!E16</f>
+        <f>'Юнитка FBO'!E15</f>
         <v/>
       </c>
       <c r="E13" s="41">
@@ -7008,15 +6977,15 @@
         <v/>
       </c>
       <c r="F13" s="41">
-        <f>'Юнитка FBO'!I16</f>
+        <f>'Юнитка FBO'!I15</f>
         <v/>
       </c>
       <c r="G13" s="41">
-        <f>'Юнитка FBO'!K16+'Юнитка FBO'!N16+'Юнитка FBO'!O16+'Юнитка FBO'!P16+'Юнитка FBO'!Q16+'Юнитка FBO'!R16+'Юнитка FBO'!S16+'Юнитка FBO'!V16+'Юнитка FBO'!X16+'Юнитка FBO'!Y16+'Юнитка FBO'!AK16</f>
+        <f>'Юнитка FBO'!K15+'Юнитка FBO'!N15+'Юнитка FBO'!O15+'Юнитка FBO'!P15+'Юнитка FBO'!Q15+'Юнитка FBO'!R15+'Юнитка FBO'!S15+'Юнитка FBO'!V15+'Юнитка FBO'!X15+'Юнитка FBO'!Y15+'Юнитка FBO'!AK15</f>
         <v/>
       </c>
       <c r="H13" s="41">
-        <f>'Юнитка FBO'!G16-'Юнитка FBO'!I16</f>
+        <f>'Юнитка FBO'!G15-'Юнитка FBO'!I15</f>
         <v/>
       </c>
       <c r="I13" s="41">
@@ -7032,7 +7001,7 @@
         <v/>
       </c>
       <c r="L13" s="41">
-        <f>'Юнитка FBO'!AG16</f>
+        <f>'Юнитка FBO'!AG15</f>
         <v/>
       </c>
       <c r="M13" s="41">
@@ -7055,14 +7024,22 @@
         <f>IF(K13&gt;0,(M13+N13+O13+P13-K13)/K13,"—")</f>
         <v/>
       </c>
+      <c r="R13" s="41">
+        <f>'Юнитка FBO'!B15</f>
+        <v/>
+      </c>
+      <c r="S13" s="43">
+        <f>IF(D13*$B$7&gt;0,R13/(D13*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="40">
-        <f>'Юнитка FBO'!A17</f>
+        <f>'Юнитка FBO'!A16</f>
         <v/>
       </c>
       <c r="B14" s="41">
-        <f>'Юнитка FBO'!C17</f>
+        <f>'Юнитка FBO'!C16</f>
         <v/>
       </c>
       <c r="C14" s="41">
@@ -7070,7 +7047,7 @@
         <v/>
       </c>
       <c r="D14" s="41">
-        <f>'Юнитка FBO'!E17</f>
+        <f>'Юнитка FBO'!E16</f>
         <v/>
       </c>
       <c r="E14" s="41">
@@ -7078,15 +7055,15 @@
         <v/>
       </c>
       <c r="F14" s="41">
-        <f>'Юнитка FBO'!I17</f>
+        <f>'Юнитка FBO'!I16</f>
         <v/>
       </c>
       <c r="G14" s="41">
-        <f>'Юнитка FBO'!K17+'Юнитка FBO'!N17+'Юнитка FBO'!O17+'Юнитка FBO'!P17+'Юнитка FBO'!Q17+'Юнитка FBO'!R17+'Юнитка FBO'!S17+'Юнитка FBO'!V17+'Юнитка FBO'!X17+'Юнитка FBO'!Y17+'Юнитка FBO'!AK17</f>
+        <f>'Юнитка FBO'!K16+'Юнитка FBO'!N16+'Юнитка FBO'!O16+'Юнитка FBO'!P16+'Юнитка FBO'!Q16+'Юнитка FBO'!R16+'Юнитка FBO'!S16+'Юнитка FBO'!V16+'Юнитка FBO'!X16+'Юнитка FBO'!Y16+'Юнитка FBO'!AK16</f>
         <v/>
       </c>
       <c r="H14" s="41">
-        <f>'Юнитка FBO'!G17-'Юнитка FBO'!I17</f>
+        <f>'Юнитка FBO'!G16-'Юнитка FBO'!I16</f>
         <v/>
       </c>
       <c r="I14" s="41">
@@ -7102,7 +7079,7 @@
         <v/>
       </c>
       <c r="L14" s="41">
-        <f>'Юнитка FBO'!AG17</f>
+        <f>'Юнитка FBO'!AG16</f>
         <v/>
       </c>
       <c r="M14" s="41">
@@ -7125,14 +7102,22 @@
         <f>IF(K14&gt;0,(M14+N14+O14+P14-K14)/K14,"—")</f>
         <v/>
       </c>
+      <c r="R14" s="41">
+        <f>'Юнитка FBO'!B16</f>
+        <v/>
+      </c>
+      <c r="S14" s="43">
+        <f>IF(D14*$B$7&gt;0,R14/(D14*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="40">
-        <f>'Юнитка FBO'!A18</f>
+        <f>'Юнитка FBO'!A17</f>
         <v/>
       </c>
       <c r="B15" s="41">
-        <f>'Юнитка FBO'!C18</f>
+        <f>'Юнитка FBO'!C17</f>
         <v/>
       </c>
       <c r="C15" s="41">
@@ -7140,7 +7125,7 @@
         <v/>
       </c>
       <c r="D15" s="41">
-        <f>'Юнитка FBO'!E18</f>
+        <f>'Юнитка FBO'!E17</f>
         <v/>
       </c>
       <c r="E15" s="41">
@@ -7148,15 +7133,15 @@
         <v/>
       </c>
       <c r="F15" s="41">
-        <f>'Юнитка FBO'!I18</f>
+        <f>'Юнитка FBO'!I17</f>
         <v/>
       </c>
       <c r="G15" s="41">
-        <f>'Юнитка FBO'!K18+'Юнитка FBO'!N18+'Юнитка FBO'!O18+'Юнитка FBO'!P18+'Юнитка FBO'!Q18+'Юнитка FBO'!R18+'Юнитка FBO'!S18+'Юнитка FBO'!V18+'Юнитка FBO'!X18+'Юнитка FBO'!Y18+'Юнитка FBO'!AK18</f>
+        <f>'Юнитка FBO'!K17+'Юнитка FBO'!N17+'Юнитка FBO'!O17+'Юнитка FBO'!P17+'Юнитка FBO'!Q17+'Юнитка FBO'!R17+'Юнитка FBO'!S17+'Юнитка FBO'!V17+'Юнитка FBO'!X17+'Юнитка FBO'!Y17+'Юнитка FBO'!AK17</f>
         <v/>
       </c>
       <c r="H15" s="41">
-        <f>'Юнитка FBO'!G18-'Юнитка FBO'!I18</f>
+        <f>'Юнитка FBO'!G17-'Юнитка FBO'!I17</f>
         <v/>
       </c>
       <c r="I15" s="41">
@@ -7172,7 +7157,7 @@
         <v/>
       </c>
       <c r="L15" s="41">
-        <f>'Юнитка FBO'!AG18</f>
+        <f>'Юнитка FBO'!AG17</f>
         <v/>
       </c>
       <c r="M15" s="41">
@@ -7195,14 +7180,22 @@
         <f>IF(K15&gt;0,(M15+N15+O15+P15-K15)/K15,"—")</f>
         <v/>
       </c>
+      <c r="R15" s="41">
+        <f>'Юнитка FBO'!B17</f>
+        <v/>
+      </c>
+      <c r="S15" s="43">
+        <f>IF(D15*$B$7&gt;0,R15/(D15*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="40">
-        <f>'Юнитка FBO'!A19</f>
+        <f>'Юнитка FBO'!A18</f>
         <v/>
       </c>
       <c r="B16" s="41">
-        <f>'Юнитка FBO'!C19</f>
+        <f>'Юнитка FBO'!C18</f>
         <v/>
       </c>
       <c r="C16" s="41">
@@ -7210,7 +7203,7 @@
         <v/>
       </c>
       <c r="D16" s="41">
-        <f>'Юнитка FBO'!E19</f>
+        <f>'Юнитка FBO'!E18</f>
         <v/>
       </c>
       <c r="E16" s="41">
@@ -7218,15 +7211,15 @@
         <v/>
       </c>
       <c r="F16" s="41">
-        <f>'Юнитка FBO'!I19</f>
+        <f>'Юнитка FBO'!I18</f>
         <v/>
       </c>
       <c r="G16" s="41">
-        <f>'Юнитка FBO'!K19+'Юнитка FBO'!N19+'Юнитка FBO'!O19+'Юнитка FBO'!P19+'Юнитка FBO'!Q19+'Юнитка FBO'!R19+'Юнитка FBO'!S19+'Юнитка FBO'!V19+'Юнитка FBO'!X19+'Юнитка FBO'!Y19+'Юнитка FBO'!AK19</f>
+        <f>'Юнитка FBO'!K18+'Юнитка FBO'!N18+'Юнитка FBO'!O18+'Юнитка FBO'!P18+'Юнитка FBO'!Q18+'Юнитка FBO'!R18+'Юнитка FBO'!S18+'Юнитка FBO'!V18+'Юнитка FBO'!X18+'Юнитка FBO'!Y18+'Юнитка FBO'!AK18</f>
         <v/>
       </c>
       <c r="H16" s="41">
-        <f>'Юнитка FBO'!G19-'Юнитка FBO'!I19</f>
+        <f>'Юнитка FBO'!G18-'Юнитка FBO'!I18</f>
         <v/>
       </c>
       <c r="I16" s="41">
@@ -7242,7 +7235,7 @@
         <v/>
       </c>
       <c r="L16" s="41">
-        <f>'Юнитка FBO'!AG19</f>
+        <f>'Юнитка FBO'!AG18</f>
         <v/>
       </c>
       <c r="M16" s="41">
@@ -7265,14 +7258,22 @@
         <f>IF(K16&gt;0,(M16+N16+O16+P16-K16)/K16,"—")</f>
         <v/>
       </c>
+      <c r="R16" s="41">
+        <f>'Юнитка FBO'!B18</f>
+        <v/>
+      </c>
+      <c r="S16" s="43">
+        <f>IF(D16*$B$7&gt;0,R16/(D16*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="40">
-        <f>'Юнитка FBO'!A20</f>
+        <f>'Юнитка FBO'!A19</f>
         <v/>
       </c>
       <c r="B17" s="41">
-        <f>'Юнитка FBO'!C20</f>
+        <f>'Юнитка FBO'!C19</f>
         <v/>
       </c>
       <c r="C17" s="41">
@@ -7280,7 +7281,7 @@
         <v/>
       </c>
       <c r="D17" s="41">
-        <f>'Юнитка FBO'!E20</f>
+        <f>'Юнитка FBO'!E19</f>
         <v/>
       </c>
       <c r="E17" s="41">
@@ -7288,15 +7289,15 @@
         <v/>
       </c>
       <c r="F17" s="41">
-        <f>'Юнитка FBO'!I20</f>
+        <f>'Юнитка FBO'!I19</f>
         <v/>
       </c>
       <c r="G17" s="41">
-        <f>'Юнитка FBO'!K20+'Юнитка FBO'!N20+'Юнитка FBO'!O20+'Юнитка FBO'!P20+'Юнитка FBO'!Q20+'Юнитка FBO'!R20+'Юнитка FBO'!S20+'Юнитка FBO'!V20+'Юнитка FBO'!X20+'Юнитка FBO'!Y20+'Юнитка FBO'!AK20</f>
+        <f>'Юнитка FBO'!K19+'Юнитка FBO'!N19+'Юнитка FBO'!O19+'Юнитка FBO'!P19+'Юнитка FBO'!Q19+'Юнитка FBO'!R19+'Юнитка FBO'!S19+'Юнитка FBO'!V19+'Юнитка FBO'!X19+'Юнитка FBO'!Y19+'Юнитка FBO'!AK19</f>
         <v/>
       </c>
       <c r="H17" s="41">
-        <f>'Юнитка FBO'!G20-'Юнитка FBO'!I20</f>
+        <f>'Юнитка FBO'!G19-'Юнитка FBO'!I19</f>
         <v/>
       </c>
       <c r="I17" s="41">
@@ -7312,7 +7313,7 @@
         <v/>
       </c>
       <c r="L17" s="41">
-        <f>'Юнитка FBO'!AG20</f>
+        <f>'Юнитка FBO'!AG19</f>
         <v/>
       </c>
       <c r="M17" s="41">
@@ -7335,14 +7336,22 @@
         <f>IF(K17&gt;0,(M17+N17+O17+P17-K17)/K17,"—")</f>
         <v/>
       </c>
+      <c r="R17" s="41">
+        <f>'Юнитка FBO'!B19</f>
+        <v/>
+      </c>
+      <c r="S17" s="43">
+        <f>IF(D17*$B$7&gt;0,R17/(D17*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="40">
-        <f>'Юнитка FBO'!A21</f>
+        <f>'Юнитка FBO'!A20</f>
         <v/>
       </c>
       <c r="B18" s="41">
-        <f>'Юнитка FBO'!C21</f>
+        <f>'Юнитка FBO'!C20</f>
         <v/>
       </c>
       <c r="C18" s="41">
@@ -7350,7 +7359,7 @@
         <v/>
       </c>
       <c r="D18" s="41">
-        <f>'Юнитка FBO'!E21</f>
+        <f>'Юнитка FBO'!E20</f>
         <v/>
       </c>
       <c r="E18" s="41">
@@ -7358,15 +7367,15 @@
         <v/>
       </c>
       <c r="F18" s="41">
-        <f>'Юнитка FBO'!I21</f>
+        <f>'Юнитка FBO'!I20</f>
         <v/>
       </c>
       <c r="G18" s="41">
-        <f>'Юнитка FBO'!K21+'Юнитка FBO'!N21+'Юнитка FBO'!O21+'Юнитка FBO'!P21+'Юнитка FBO'!Q21+'Юнитка FBO'!R21+'Юнитка FBO'!S21+'Юнитка FBO'!V21+'Юнитка FBO'!X21+'Юнитка FBO'!Y21+'Юнитка FBO'!AK21</f>
+        <f>'Юнитка FBO'!K20+'Юнитка FBO'!N20+'Юнитка FBO'!O20+'Юнитка FBO'!P20+'Юнитка FBO'!Q20+'Юнитка FBO'!R20+'Юнитка FBO'!S20+'Юнитка FBO'!V20+'Юнитка FBO'!X20+'Юнитка FBO'!Y20+'Юнитка FBO'!AK20</f>
         <v/>
       </c>
       <c r="H18" s="41">
-        <f>'Юнитка FBO'!G21-'Юнитка FBO'!I21</f>
+        <f>'Юнитка FBO'!G20-'Юнитка FBO'!I20</f>
         <v/>
       </c>
       <c r="I18" s="41">
@@ -7382,7 +7391,7 @@
         <v/>
       </c>
       <c r="L18" s="41">
-        <f>'Юнитка FBO'!AG21</f>
+        <f>'Юнитка FBO'!AG20</f>
         <v/>
       </c>
       <c r="M18" s="41">
@@ -7405,14 +7414,22 @@
         <f>IF(K18&gt;0,(M18+N18+O18+P18-K18)/K18,"—")</f>
         <v/>
       </c>
+      <c r="R18" s="41">
+        <f>'Юнитка FBO'!B20</f>
+        <v/>
+      </c>
+      <c r="S18" s="43">
+        <f>IF(D18*$B$7&gt;0,R18/(D18*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="40">
-        <f>'Юнитка FBO'!A22</f>
+        <f>'Юнитка FBO'!A21</f>
         <v/>
       </c>
       <c r="B19" s="41">
-        <f>'Юнитка FBO'!C22</f>
+        <f>'Юнитка FBO'!C21</f>
         <v/>
       </c>
       <c r="C19" s="41">
@@ -7420,7 +7437,7 @@
         <v/>
       </c>
       <c r="D19" s="41">
-        <f>'Юнитка FBO'!E22</f>
+        <f>'Юнитка FBO'!E21</f>
         <v/>
       </c>
       <c r="E19" s="41">
@@ -7428,15 +7445,15 @@
         <v/>
       </c>
       <c r="F19" s="41">
-        <f>'Юнитка FBO'!I22</f>
+        <f>'Юнитка FBO'!I21</f>
         <v/>
       </c>
       <c r="G19" s="41">
-        <f>'Юнитка FBO'!K22+'Юнитка FBO'!N22+'Юнитка FBO'!O22+'Юнитка FBO'!P22+'Юнитка FBO'!Q22+'Юнитка FBO'!R22+'Юнитка FBO'!S22+'Юнитка FBO'!V22+'Юнитка FBO'!X22+'Юнитка FBO'!Y22+'Юнитка FBO'!AK22</f>
+        <f>'Юнитка FBO'!K21+'Юнитка FBO'!N21+'Юнитка FBO'!O21+'Юнитка FBO'!P21+'Юнитка FBO'!Q21+'Юнитка FBO'!R21+'Юнитка FBO'!S21+'Юнитка FBO'!V21+'Юнитка FBO'!X21+'Юнитка FBO'!Y21+'Юнитка FBO'!AK21</f>
         <v/>
       </c>
       <c r="H19" s="41">
-        <f>'Юнитка FBO'!G22-'Юнитка FBO'!I22</f>
+        <f>'Юнитка FBO'!G21-'Юнитка FBO'!I21</f>
         <v/>
       </c>
       <c r="I19" s="41">
@@ -7452,7 +7469,7 @@
         <v/>
       </c>
       <c r="L19" s="41">
-        <f>'Юнитка FBO'!AG22</f>
+        <f>'Юнитка FBO'!AG21</f>
         <v/>
       </c>
       <c r="M19" s="41">
@@ -7475,14 +7492,22 @@
         <f>IF(K19&gt;0,(M19+N19+O19+P19-K19)/K19,"—")</f>
         <v/>
       </c>
+      <c r="R19" s="41">
+        <f>'Юнитка FBO'!B21</f>
+        <v/>
+      </c>
+      <c r="S19" s="43">
+        <f>IF(D19*$B$7&gt;0,R19/(D19*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="40">
-        <f>'Юнитка FBO'!A23</f>
+        <f>'Юнитка FBO'!A22</f>
         <v/>
       </c>
       <c r="B20" s="41">
-        <f>'Юнитка FBO'!C23</f>
+        <f>'Юнитка FBO'!C22</f>
         <v/>
       </c>
       <c r="C20" s="41">
@@ -7490,7 +7515,7 @@
         <v/>
       </c>
       <c r="D20" s="41">
-        <f>'Юнитка FBO'!E23</f>
+        <f>'Юнитка FBO'!E22</f>
         <v/>
       </c>
       <c r="E20" s="41">
@@ -7498,15 +7523,15 @@
         <v/>
       </c>
       <c r="F20" s="41">
-        <f>'Юнитка FBO'!I23</f>
+        <f>'Юнитка FBO'!I22</f>
         <v/>
       </c>
       <c r="G20" s="41">
-        <f>'Юнитка FBO'!K23+'Юнитка FBO'!N23+'Юнитка FBO'!O23+'Юнитка FBO'!P23+'Юнитка FBO'!Q23+'Юнитка FBO'!R23+'Юнитка FBO'!S23+'Юнитка FBO'!V23+'Юнитка FBO'!X23+'Юнитка FBO'!Y23+'Юнитка FBO'!AK23</f>
+        <f>'Юнитка FBO'!K22+'Юнитка FBO'!N22+'Юнитка FBO'!O22+'Юнитка FBO'!P22+'Юнитка FBO'!Q22+'Юнитка FBO'!R22+'Юнитка FBO'!S22+'Юнитка FBO'!V22+'Юнитка FBO'!X22+'Юнитка FBO'!Y22+'Юнитка FBO'!AK22</f>
         <v/>
       </c>
       <c r="H20" s="41">
-        <f>'Юнитка FBO'!G23-'Юнитка FBO'!I23</f>
+        <f>'Юнитка FBO'!G22-'Юнитка FBO'!I22</f>
         <v/>
       </c>
       <c r="I20" s="41">
@@ -7522,7 +7547,7 @@
         <v/>
       </c>
       <c r="L20" s="41">
-        <f>'Юнитка FBO'!AG23</f>
+        <f>'Юнитка FBO'!AG22</f>
         <v/>
       </c>
       <c r="M20" s="41">
@@ -7545,14 +7570,22 @@
         <f>IF(K20&gt;0,(M20+N20+O20+P20-K20)/K20,"—")</f>
         <v/>
       </c>
+      <c r="R20" s="41">
+        <f>'Юнитка FBO'!B22</f>
+        <v/>
+      </c>
+      <c r="S20" s="43">
+        <f>IF(D20*$B$7&gt;0,R20/(D20*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="40">
-        <f>'Юнитка FBO'!A24</f>
+        <f>'Юнитка FBO'!A23</f>
         <v/>
       </c>
       <c r="B21" s="41">
-        <f>'Юнитка FBO'!C24</f>
+        <f>'Юнитка FBO'!C23</f>
         <v/>
       </c>
       <c r="C21" s="41">
@@ -7560,7 +7593,7 @@
         <v/>
       </c>
       <c r="D21" s="41">
-        <f>'Юнитка FBO'!E24</f>
+        <f>'Юнитка FBO'!E23</f>
         <v/>
       </c>
       <c r="E21" s="41">
@@ -7568,15 +7601,15 @@
         <v/>
       </c>
       <c r="F21" s="41">
-        <f>'Юнитка FBO'!I24</f>
+        <f>'Юнитка FBO'!I23</f>
         <v/>
       </c>
       <c r="G21" s="41">
-        <f>'Юнитка FBO'!K24+'Юнитка FBO'!N24+'Юнитка FBO'!O24+'Юнитка FBO'!P24+'Юнитка FBO'!Q24+'Юнитка FBO'!R24+'Юнитка FBO'!S24+'Юнитка FBO'!V24+'Юнитка FBO'!X24+'Юнитка FBO'!Y24+'Юнитка FBO'!AK24</f>
+        <f>'Юнитка FBO'!K23+'Юнитка FBO'!N23+'Юнитка FBO'!O23+'Юнитка FBO'!P23+'Юнитка FBO'!Q23+'Юнитка FBO'!R23+'Юнитка FBO'!S23+'Юнитка FBO'!V23+'Юнитка FBO'!X23+'Юнитка FBO'!Y23+'Юнитка FBO'!AK23</f>
         <v/>
       </c>
       <c r="H21" s="41">
-        <f>'Юнитка FBO'!G24-'Юнитка FBO'!I24</f>
+        <f>'Юнитка FBO'!G23-'Юнитка FBO'!I23</f>
         <v/>
       </c>
       <c r="I21" s="41">
@@ -7592,7 +7625,7 @@
         <v/>
       </c>
       <c r="L21" s="41">
-        <f>'Юнитка FBO'!AG24</f>
+        <f>'Юнитка FBO'!AG23</f>
         <v/>
       </c>
       <c r="M21" s="41">
@@ -7615,14 +7648,22 @@
         <f>IF(K21&gt;0,(M21+N21+O21+P21-K21)/K21,"—")</f>
         <v/>
       </c>
+      <c r="R21" s="41">
+        <f>'Юнитка FBO'!B23</f>
+        <v/>
+      </c>
+      <c r="S21" s="43">
+        <f>IF(D21*$B$7&gt;0,R21/(D21*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="40">
-        <f>'Юнитка FBO'!A25</f>
+        <f>'Юнитка FBO'!A24</f>
         <v/>
       </c>
       <c r="B22" s="41">
-        <f>'Юнитка FBO'!C25</f>
+        <f>'Юнитка FBO'!C24</f>
         <v/>
       </c>
       <c r="C22" s="41">
@@ -7630,7 +7671,7 @@
         <v/>
       </c>
       <c r="D22" s="41">
-        <f>'Юнитка FBO'!E25</f>
+        <f>'Юнитка FBO'!E24</f>
         <v/>
       </c>
       <c r="E22" s="41">
@@ -7638,15 +7679,15 @@
         <v/>
       </c>
       <c r="F22" s="41">
-        <f>'Юнитка FBO'!I25</f>
+        <f>'Юнитка FBO'!I24</f>
         <v/>
       </c>
       <c r="G22" s="41">
-        <f>'Юнитка FBO'!K25+'Юнитка FBO'!N25+'Юнитка FBO'!O25+'Юнитка FBO'!P25+'Юнитка FBO'!Q25+'Юнитка FBO'!R25+'Юнитка FBO'!S25+'Юнитка FBO'!V25+'Юнитка FBO'!X25+'Юнитка FBO'!Y25+'Юнитка FBO'!AK25</f>
+        <f>'Юнитка FBO'!K24+'Юнитка FBO'!N24+'Юнитка FBO'!O24+'Юнитка FBO'!P24+'Юнитка FBO'!Q24+'Юнитка FBO'!R24+'Юнитка FBO'!S24+'Юнитка FBO'!V24+'Юнитка FBO'!X24+'Юнитка FBO'!Y24+'Юнитка FBO'!AK24</f>
         <v/>
       </c>
       <c r="H22" s="41">
-        <f>'Юнитка FBO'!G25-'Юнитка FBO'!I25</f>
+        <f>'Юнитка FBO'!G24-'Юнитка FBO'!I24</f>
         <v/>
       </c>
       <c r="I22" s="41">
@@ -7662,7 +7703,7 @@
         <v/>
       </c>
       <c r="L22" s="41">
-        <f>'Юнитка FBO'!AG25</f>
+        <f>'Юнитка FBO'!AG24</f>
         <v/>
       </c>
       <c r="M22" s="41">
@@ -7685,14 +7726,22 @@
         <f>IF(K22&gt;0,(M22+N22+O22+P22-K22)/K22,"—")</f>
         <v/>
       </c>
+      <c r="R22" s="41">
+        <f>'Юнитка FBO'!B24</f>
+        <v/>
+      </c>
+      <c r="S22" s="43">
+        <f>IF(D22*$B$7&gt;0,R22/(D22*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="40">
-        <f>'Юнитка FBO'!A26</f>
+        <f>'Юнитка FBO'!A25</f>
         <v/>
       </c>
       <c r="B23" s="41">
-        <f>'Юнитка FBO'!C26</f>
+        <f>'Юнитка FBO'!C25</f>
         <v/>
       </c>
       <c r="C23" s="41">
@@ -7700,7 +7749,7 @@
         <v/>
       </c>
       <c r="D23" s="41">
-        <f>'Юнитка FBO'!E26</f>
+        <f>'Юнитка FBO'!E25</f>
         <v/>
       </c>
       <c r="E23" s="41">
@@ -7708,15 +7757,15 @@
         <v/>
       </c>
       <c r="F23" s="41">
-        <f>'Юнитка FBO'!I26</f>
+        <f>'Юнитка FBO'!I25</f>
         <v/>
       </c>
       <c r="G23" s="41">
-        <f>'Юнитка FBO'!K26+'Юнитка FBO'!N26+'Юнитка FBO'!O26+'Юнитка FBO'!P26+'Юнитка FBO'!Q26+'Юнитка FBO'!R26+'Юнитка FBO'!S26+'Юнитка FBO'!V26+'Юнитка FBO'!X26+'Юнитка FBO'!Y26+'Юнитка FBO'!AK26</f>
+        <f>'Юнитка FBO'!K25+'Юнитка FBO'!N25+'Юнитка FBO'!O25+'Юнитка FBO'!P25+'Юнитка FBO'!Q25+'Юнитка FBO'!R25+'Юнитка FBO'!S25+'Юнитка FBO'!V25+'Юнитка FBO'!X25+'Юнитка FBO'!Y25+'Юнитка FBO'!AK25</f>
         <v/>
       </c>
       <c r="H23" s="41">
-        <f>'Юнитка FBO'!G26-'Юнитка FBO'!I26</f>
+        <f>'Юнитка FBO'!G25-'Юнитка FBO'!I25</f>
         <v/>
       </c>
       <c r="I23" s="41">
@@ -7732,7 +7781,7 @@
         <v/>
       </c>
       <c r="L23" s="41">
-        <f>'Юнитка FBO'!AG26</f>
+        <f>'Юнитка FBO'!AG25</f>
         <v/>
       </c>
       <c r="M23" s="41">
@@ -7755,14 +7804,22 @@
         <f>IF(K23&gt;0,(M23+N23+O23+P23-K23)/K23,"—")</f>
         <v/>
       </c>
+      <c r="R23" s="41">
+        <f>'Юнитка FBO'!B25</f>
+        <v/>
+      </c>
+      <c r="S23" s="43">
+        <f>IF(D23*$B$7&gt;0,R23/(D23*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="40">
-        <f>'Юнитка FBO'!A27</f>
+        <f>'Юнитка FBO'!A26</f>
         <v/>
       </c>
       <c r="B24" s="41">
-        <f>'Юнитка FBO'!C27</f>
+        <f>'Юнитка FBO'!C26</f>
         <v/>
       </c>
       <c r="C24" s="41">
@@ -7770,7 +7827,7 @@
         <v/>
       </c>
       <c r="D24" s="41">
-        <f>'Юнитка FBO'!E27</f>
+        <f>'Юнитка FBO'!E26</f>
         <v/>
       </c>
       <c r="E24" s="41">
@@ -7778,15 +7835,15 @@
         <v/>
       </c>
       <c r="F24" s="41">
-        <f>'Юнитка FBO'!I27</f>
+        <f>'Юнитка FBO'!I26</f>
         <v/>
       </c>
       <c r="G24" s="41">
-        <f>'Юнитка FBO'!K27+'Юнитка FBO'!N27+'Юнитка FBO'!O27+'Юнитка FBO'!P27+'Юнитка FBO'!Q27+'Юнитка FBO'!R27+'Юнитка FBO'!S27+'Юнитка FBO'!V27+'Юнитка FBO'!X27+'Юнитка FBO'!Y27+'Юнитка FBO'!AK27</f>
+        <f>'Юнитка FBO'!K26+'Юнитка FBO'!N26+'Юнитка FBO'!O26+'Юнитка FBO'!P26+'Юнитка FBO'!Q26+'Юнитка FBO'!R26+'Юнитка FBO'!S26+'Юнитка FBO'!V26+'Юнитка FBO'!X26+'Юнитка FBO'!Y26+'Юнитка FBO'!AK26</f>
         <v/>
       </c>
       <c r="H24" s="41">
-        <f>'Юнитка FBO'!G27-'Юнитка FBO'!I27</f>
+        <f>'Юнитка FBO'!G26-'Юнитка FBO'!I26</f>
         <v/>
       </c>
       <c r="I24" s="41">
@@ -7802,7 +7859,7 @@
         <v/>
       </c>
       <c r="L24" s="41">
-        <f>'Юнитка FBO'!AG27</f>
+        <f>'Юнитка FBO'!AG26</f>
         <v/>
       </c>
       <c r="M24" s="41">
@@ -7825,14 +7882,22 @@
         <f>IF(K24&gt;0,(M24+N24+O24+P24-K24)/K24,"—")</f>
         <v/>
       </c>
+      <c r="R24" s="41">
+        <f>'Юнитка FBO'!B26</f>
+        <v/>
+      </c>
+      <c r="S24" s="43">
+        <f>IF(D24*$B$7&gt;0,R24/(D24*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="40">
-        <f>'Юнитка FBO'!A28</f>
+        <f>'Юнитка FBO'!A27</f>
         <v/>
       </c>
       <c r="B25" s="41">
-        <f>'Юнитка FBO'!C28</f>
+        <f>'Юнитка FBO'!C27</f>
         <v/>
       </c>
       <c r="C25" s="41">
@@ -7840,7 +7905,7 @@
         <v/>
       </c>
       <c r="D25" s="41">
-        <f>'Юнитка FBO'!E28</f>
+        <f>'Юнитка FBO'!E27</f>
         <v/>
       </c>
       <c r="E25" s="41">
@@ -7848,15 +7913,15 @@
         <v/>
       </c>
       <c r="F25" s="41">
-        <f>'Юнитка FBO'!I28</f>
+        <f>'Юнитка FBO'!I27</f>
         <v/>
       </c>
       <c r="G25" s="41">
-        <f>'Юнитка FBO'!K28+'Юнитка FBO'!N28+'Юнитка FBO'!O28+'Юнитка FBO'!P28+'Юнитка FBO'!Q28+'Юнитка FBO'!R28+'Юнитка FBO'!S28+'Юнитка FBO'!V28+'Юнитка FBO'!X28+'Юнитка FBO'!Y28+'Юнитка FBO'!AK28</f>
+        <f>'Юнитка FBO'!K27+'Юнитка FBO'!N27+'Юнитка FBO'!O27+'Юнитка FBO'!P27+'Юнитка FBO'!Q27+'Юнитка FBO'!R27+'Юнитка FBO'!S27+'Юнитка FBO'!V27+'Юнитка FBO'!X27+'Юнитка FBO'!Y27+'Юнитка FBO'!AK27</f>
         <v/>
       </c>
       <c r="H25" s="41">
-        <f>'Юнитка FBO'!G28-'Юнитка FBO'!I28</f>
+        <f>'Юнитка FBO'!G27-'Юнитка FBO'!I27</f>
         <v/>
       </c>
       <c r="I25" s="41">
@@ -7872,7 +7937,7 @@
         <v/>
       </c>
       <c r="L25" s="41">
-        <f>'Юнитка FBO'!AG28</f>
+        <f>'Юнитка FBO'!AG27</f>
         <v/>
       </c>
       <c r="M25" s="41">
@@ -7895,14 +7960,22 @@
         <f>IF(K25&gt;0,(M25+N25+O25+P25-K25)/K25,"—")</f>
         <v/>
       </c>
+      <c r="R25" s="41">
+        <f>'Юнитка FBO'!B27</f>
+        <v/>
+      </c>
+      <c r="S25" s="43">
+        <f>IF(D25*$B$7&gt;0,R25/(D25*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="40">
-        <f>'Юнитка FBO'!A29</f>
+        <f>'Юнитка FBO'!A28</f>
         <v/>
       </c>
       <c r="B26" s="41">
-        <f>'Юнитка FBO'!C29</f>
+        <f>'Юнитка FBO'!C28</f>
         <v/>
       </c>
       <c r="C26" s="41">
@@ -7910,7 +7983,7 @@
         <v/>
       </c>
       <c r="D26" s="41">
-        <f>'Юнитка FBO'!E29</f>
+        <f>'Юнитка FBO'!E28</f>
         <v/>
       </c>
       <c r="E26" s="41">
@@ -7918,15 +7991,15 @@
         <v/>
       </c>
       <c r="F26" s="41">
-        <f>'Юнитка FBO'!I29</f>
+        <f>'Юнитка FBO'!I28</f>
         <v/>
       </c>
       <c r="G26" s="41">
-        <f>'Юнитка FBO'!K29+'Юнитка FBO'!N29+'Юнитка FBO'!O29+'Юнитка FBO'!P29+'Юнитка FBO'!Q29+'Юнитка FBO'!R29+'Юнитка FBO'!S29+'Юнитка FBO'!V29+'Юнитка FBO'!X29+'Юнитка FBO'!Y29+'Юнитка FBO'!AK29</f>
+        <f>'Юнитка FBO'!K28+'Юнитка FBO'!N28+'Юнитка FBO'!O28+'Юнитка FBO'!P28+'Юнитка FBO'!Q28+'Юнитка FBO'!R28+'Юнитка FBO'!S28+'Юнитка FBO'!V28+'Юнитка FBO'!X28+'Юнитка FBO'!Y28+'Юнитка FBO'!AK28</f>
         <v/>
       </c>
       <c r="H26" s="41">
-        <f>'Юнитка FBO'!G29-'Юнитка FBO'!I29</f>
+        <f>'Юнитка FBO'!G28-'Юнитка FBO'!I28</f>
         <v/>
       </c>
       <c r="I26" s="41">
@@ -7942,7 +8015,7 @@
         <v/>
       </c>
       <c r="L26" s="41">
-        <f>'Юнитка FBO'!AG29</f>
+        <f>'Юнитка FBO'!AG28</f>
         <v/>
       </c>
       <c r="M26" s="41">
@@ -7965,14 +8038,22 @@
         <f>IF(K26&gt;0,(M26+N26+O26+P26-K26)/K26,"—")</f>
         <v/>
       </c>
+      <c r="R26" s="41">
+        <f>'Юнитка FBO'!B28</f>
+        <v/>
+      </c>
+      <c r="S26" s="43">
+        <f>IF(D26*$B$7&gt;0,R26/(D26*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="40">
-        <f>'Юнитка FBO'!A30</f>
+        <f>'Юнитка FBO'!A29</f>
         <v/>
       </c>
       <c r="B27" s="41">
-        <f>'Юнитка FBO'!C30</f>
+        <f>'Юнитка FBO'!C29</f>
         <v/>
       </c>
       <c r="C27" s="41">
@@ -7980,7 +8061,7 @@
         <v/>
       </c>
       <c r="D27" s="41">
-        <f>'Юнитка FBO'!E30</f>
+        <f>'Юнитка FBO'!E29</f>
         <v/>
       </c>
       <c r="E27" s="41">
@@ -7988,15 +8069,15 @@
         <v/>
       </c>
       <c r="F27" s="41">
-        <f>'Юнитка FBO'!I30</f>
+        <f>'Юнитка FBO'!I29</f>
         <v/>
       </c>
       <c r="G27" s="41">
-        <f>'Юнитка FBO'!K30+'Юнитка FBO'!N30+'Юнитка FBO'!O30+'Юнитка FBO'!P30+'Юнитка FBO'!Q30+'Юнитка FBO'!R30+'Юнитка FBO'!S30+'Юнитка FBO'!V30+'Юнитка FBO'!X30+'Юнитка FBO'!Y30+'Юнитка FBO'!AK30</f>
+        <f>'Юнитка FBO'!K29+'Юнитка FBO'!N29+'Юнитка FBO'!O29+'Юнитка FBO'!P29+'Юнитка FBO'!Q29+'Юнитка FBO'!R29+'Юнитка FBO'!S29+'Юнитка FBO'!V29+'Юнитка FBO'!X29+'Юнитка FBO'!Y29+'Юнитка FBO'!AK29</f>
         <v/>
       </c>
       <c r="H27" s="41">
-        <f>'Юнитка FBO'!G30-'Юнитка FBO'!I30</f>
+        <f>'Юнитка FBO'!G29-'Юнитка FBO'!I29</f>
         <v/>
       </c>
       <c r="I27" s="41">
@@ -8012,7 +8093,7 @@
         <v/>
       </c>
       <c r="L27" s="41">
-        <f>'Юнитка FBO'!AG30</f>
+        <f>'Юнитка FBO'!AG29</f>
         <v/>
       </c>
       <c r="M27" s="41">
@@ -8035,14 +8116,22 @@
         <f>IF(K27&gt;0,(M27+N27+O27+P27-K27)/K27,"—")</f>
         <v/>
       </c>
+      <c r="R27" s="41">
+        <f>'Юнитка FBO'!B29</f>
+        <v/>
+      </c>
+      <c r="S27" s="43">
+        <f>IF(D27*$B$7&gt;0,R27/(D27*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="40">
-        <f>'Юнитка FBO'!A31</f>
+        <f>'Юнитка FBO'!A30</f>
         <v/>
       </c>
       <c r="B28" s="41">
-        <f>'Юнитка FBO'!C31</f>
+        <f>'Юнитка FBO'!C30</f>
         <v/>
       </c>
       <c r="C28" s="41">
@@ -8050,7 +8139,7 @@
         <v/>
       </c>
       <c r="D28" s="41">
-        <f>'Юнитка FBO'!E31</f>
+        <f>'Юнитка FBO'!E30</f>
         <v/>
       </c>
       <c r="E28" s="41">
@@ -8058,15 +8147,15 @@
         <v/>
       </c>
       <c r="F28" s="41">
-        <f>'Юнитка FBO'!I31</f>
+        <f>'Юнитка FBO'!I30</f>
         <v/>
       </c>
       <c r="G28" s="41">
-        <f>'Юнитка FBO'!K31+'Юнитка FBO'!N31+'Юнитка FBO'!O31+'Юнитка FBO'!P31+'Юнитка FBO'!Q31+'Юнитка FBO'!R31+'Юнитка FBO'!S31+'Юнитка FBO'!V31+'Юнитка FBO'!X31+'Юнитка FBO'!Y31+'Юнитка FBO'!AK31</f>
+        <f>'Юнитка FBO'!K30+'Юнитка FBO'!N30+'Юнитка FBO'!O30+'Юнитка FBO'!P30+'Юнитка FBO'!Q30+'Юнитка FBO'!R30+'Юнитка FBO'!S30+'Юнитка FBO'!V30+'Юнитка FBO'!X30+'Юнитка FBO'!Y30+'Юнитка FBO'!AK30</f>
         <v/>
       </c>
       <c r="H28" s="41">
-        <f>'Юнитка FBO'!G31-'Юнитка FBO'!I31</f>
+        <f>'Юнитка FBO'!G30-'Юнитка FBO'!I30</f>
         <v/>
       </c>
       <c r="I28" s="41">
@@ -8082,7 +8171,7 @@
         <v/>
       </c>
       <c r="L28" s="41">
-        <f>'Юнитка FBO'!AG31</f>
+        <f>'Юнитка FBO'!AG30</f>
         <v/>
       </c>
       <c r="M28" s="41">
@@ -8105,14 +8194,22 @@
         <f>IF(K28&gt;0,(M28+N28+O28+P28-K28)/K28,"—")</f>
         <v/>
       </c>
+      <c r="R28" s="41">
+        <f>'Юнитка FBO'!B30</f>
+        <v/>
+      </c>
+      <c r="S28" s="43">
+        <f>IF(D28*$B$7&gt;0,R28/(D28*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="40">
-        <f>'Юнитка FBO'!A32</f>
+        <f>'Юнитка FBO'!A31</f>
         <v/>
       </c>
       <c r="B29" s="41">
-        <f>'Юнитка FBO'!C32</f>
+        <f>'Юнитка FBO'!C31</f>
         <v/>
       </c>
       <c r="C29" s="41">
@@ -8120,7 +8217,7 @@
         <v/>
       </c>
       <c r="D29" s="41">
-        <f>'Юнитка FBO'!E32</f>
+        <f>'Юнитка FBO'!E31</f>
         <v/>
       </c>
       <c r="E29" s="41">
@@ -8128,15 +8225,15 @@
         <v/>
       </c>
       <c r="F29" s="41">
-        <f>'Юнитка FBO'!I32</f>
+        <f>'Юнитка FBO'!I31</f>
         <v/>
       </c>
       <c r="G29" s="41">
-        <f>'Юнитка FBO'!K32+'Юнитка FBO'!N32+'Юнитка FBO'!O32+'Юнитка FBO'!P32+'Юнитка FBO'!Q32+'Юнитка FBO'!R32+'Юнитка FBO'!S32+'Юнитка FBO'!V32+'Юнитка FBO'!X32+'Юнитка FBO'!Y32+'Юнитка FBO'!AK32</f>
+        <f>'Юнитка FBO'!K31+'Юнитка FBO'!N31+'Юнитка FBO'!O31+'Юнитка FBO'!P31+'Юнитка FBO'!Q31+'Юнитка FBO'!R31+'Юнитка FBO'!S31+'Юнитка FBO'!V31+'Юнитка FBO'!X31+'Юнитка FBO'!Y31+'Юнитка FBO'!AK31</f>
         <v/>
       </c>
       <c r="H29" s="41">
-        <f>'Юнитка FBO'!G32-'Юнитка FBO'!I32</f>
+        <f>'Юнитка FBO'!G31-'Юнитка FBO'!I31</f>
         <v/>
       </c>
       <c r="I29" s="41">
@@ -8152,7 +8249,7 @@
         <v/>
       </c>
       <c r="L29" s="41">
-        <f>'Юнитка FBO'!AG32</f>
+        <f>'Юнитка FBO'!AG31</f>
         <v/>
       </c>
       <c r="M29" s="41">
@@ -8175,14 +8272,22 @@
         <f>IF(K29&gt;0,(M29+N29+O29+P29-K29)/K29,"—")</f>
         <v/>
       </c>
+      <c r="R29" s="41">
+        <f>'Юнитка FBO'!B31</f>
+        <v/>
+      </c>
+      <c r="S29" s="43">
+        <f>IF(D29*$B$7&gt;0,R29/(D29*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="40">
-        <f>'Юнитка FBO'!A33</f>
+        <f>'Юнитка FBO'!A32</f>
         <v/>
       </c>
       <c r="B30" s="41">
-        <f>'Юнитка FBO'!C33</f>
+        <f>'Юнитка FBO'!C32</f>
         <v/>
       </c>
       <c r="C30" s="41">
@@ -8190,7 +8295,7 @@
         <v/>
       </c>
       <c r="D30" s="41">
-        <f>'Юнитка FBO'!E33</f>
+        <f>'Юнитка FBO'!E32</f>
         <v/>
       </c>
       <c r="E30" s="41">
@@ -8198,15 +8303,15 @@
         <v/>
       </c>
       <c r="F30" s="41">
-        <f>'Юнитка FBO'!I33</f>
+        <f>'Юнитка FBO'!I32</f>
         <v/>
       </c>
       <c r="G30" s="41">
-        <f>'Юнитка FBO'!K33+'Юнитка FBO'!N33+'Юнитка FBO'!O33+'Юнитка FBO'!P33+'Юнитка FBO'!Q33+'Юнитка FBO'!R33+'Юнитка FBO'!S33+'Юнитка FBO'!V33+'Юнитка FBO'!X33+'Юнитка FBO'!Y33+'Юнитка FBO'!AK33</f>
+        <f>'Юнитка FBO'!K32+'Юнитка FBO'!N32+'Юнитка FBO'!O32+'Юнитка FBO'!P32+'Юнитка FBO'!Q32+'Юнитка FBO'!R32+'Юнитка FBO'!S32+'Юнитка FBO'!V32+'Юнитка FBO'!X32+'Юнитка FBO'!Y32+'Юнитка FBO'!AK32</f>
         <v/>
       </c>
       <c r="H30" s="41">
-        <f>'Юнитка FBO'!G33-'Юнитка FBO'!I33</f>
+        <f>'Юнитка FBO'!G32-'Юнитка FBO'!I32</f>
         <v/>
       </c>
       <c r="I30" s="41">
@@ -8222,7 +8327,7 @@
         <v/>
       </c>
       <c r="L30" s="41">
-        <f>'Юнитка FBO'!AG33</f>
+        <f>'Юнитка FBO'!AG32</f>
         <v/>
       </c>
       <c r="M30" s="41">
@@ -8245,14 +8350,22 @@
         <f>IF(K30&gt;0,(M30+N30+O30+P30-K30)/K30,"—")</f>
         <v/>
       </c>
+      <c r="R30" s="41">
+        <f>'Юнитка FBO'!B32</f>
+        <v/>
+      </c>
+      <c r="S30" s="43">
+        <f>IF(D30*$B$7&gt;0,R30/(D30*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="40">
-        <f>'Юнитка FBO'!A34</f>
+        <f>'Юнитка FBO'!A33</f>
         <v/>
       </c>
       <c r="B31" s="41">
-        <f>'Юнитка FBO'!C34</f>
+        <f>'Юнитка FBO'!C33</f>
         <v/>
       </c>
       <c r="C31" s="41">
@@ -8260,7 +8373,7 @@
         <v/>
       </c>
       <c r="D31" s="41">
-        <f>'Юнитка FBO'!E34</f>
+        <f>'Юнитка FBO'!E33</f>
         <v/>
       </c>
       <c r="E31" s="41">
@@ -8268,15 +8381,15 @@
         <v/>
       </c>
       <c r="F31" s="41">
-        <f>'Юнитка FBO'!I34</f>
+        <f>'Юнитка FBO'!I33</f>
         <v/>
       </c>
       <c r="G31" s="41">
-        <f>'Юнитка FBO'!K34+'Юнитка FBO'!N34+'Юнитка FBO'!O34+'Юнитка FBO'!P34+'Юнитка FBO'!Q34+'Юнитка FBO'!R34+'Юнитка FBO'!S34+'Юнитка FBO'!V34+'Юнитка FBO'!X34+'Юнитка FBO'!Y34+'Юнитка FBO'!AK34</f>
+        <f>'Юнитка FBO'!K33+'Юнитка FBO'!N33+'Юнитка FBO'!O33+'Юнитка FBO'!P33+'Юнитка FBO'!Q33+'Юнитка FBO'!R33+'Юнитка FBO'!S33+'Юнитка FBO'!V33+'Юнитка FBO'!X33+'Юнитка FBO'!Y33+'Юнитка FBO'!AK33</f>
         <v/>
       </c>
       <c r="H31" s="41">
-        <f>'Юнитка FBO'!G34-'Юнитка FBO'!I34</f>
+        <f>'Юнитка FBO'!G33-'Юнитка FBO'!I33</f>
         <v/>
       </c>
       <c r="I31" s="41">
@@ -8292,7 +8405,7 @@
         <v/>
       </c>
       <c r="L31" s="41">
-        <f>'Юнитка FBO'!AG34</f>
+        <f>'Юнитка FBO'!AG33</f>
         <v/>
       </c>
       <c r="M31" s="41">
@@ -8315,14 +8428,22 @@
         <f>IF(K31&gt;0,(M31+N31+O31+P31-K31)/K31,"—")</f>
         <v/>
       </c>
+      <c r="R31" s="41">
+        <f>'Юнитка FBO'!B33</f>
+        <v/>
+      </c>
+      <c r="S31" s="43">
+        <f>IF(D31*$B$7&gt;0,R31/(D31*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="40">
-        <f>'Юнитка FBO'!A35</f>
+        <f>'Юнитка FBO'!A34</f>
         <v/>
       </c>
       <c r="B32" s="41">
-        <f>'Юнитка FBO'!C35</f>
+        <f>'Юнитка FBO'!C34</f>
         <v/>
       </c>
       <c r="C32" s="41">
@@ -8330,7 +8451,7 @@
         <v/>
       </c>
       <c r="D32" s="41">
-        <f>'Юнитка FBO'!E35</f>
+        <f>'Юнитка FBO'!E34</f>
         <v/>
       </c>
       <c r="E32" s="41">
@@ -8338,15 +8459,15 @@
         <v/>
       </c>
       <c r="F32" s="41">
-        <f>'Юнитка FBO'!I35</f>
+        <f>'Юнитка FBO'!I34</f>
         <v/>
       </c>
       <c r="G32" s="41">
-        <f>'Юнитка FBO'!K35+'Юнитка FBO'!N35+'Юнитка FBO'!O35+'Юнитка FBO'!P35+'Юнитка FBO'!Q35+'Юнитка FBO'!R35+'Юнитка FBO'!S35+'Юнитка FBO'!V35+'Юнитка FBO'!X35+'Юнитка FBO'!Y35+'Юнитка FBO'!AK35</f>
+        <f>'Юнитка FBO'!K34+'Юнитка FBO'!N34+'Юнитка FBO'!O34+'Юнитка FBO'!P34+'Юнитка FBO'!Q34+'Юнитка FBO'!R34+'Юнитка FBO'!S34+'Юнитка FBO'!V34+'Юнитка FBO'!X34+'Юнитка FBO'!Y34+'Юнитка FBO'!AK34</f>
         <v/>
       </c>
       <c r="H32" s="41">
-        <f>'Юнитка FBO'!G35-'Юнитка FBO'!I35</f>
+        <f>'Юнитка FBO'!G34-'Юнитка FBO'!I34</f>
         <v/>
       </c>
       <c r="I32" s="41">
@@ -8362,7 +8483,7 @@
         <v/>
       </c>
       <c r="L32" s="41">
-        <f>'Юнитка FBO'!AG35</f>
+        <f>'Юнитка FBO'!AG34</f>
         <v/>
       </c>
       <c r="M32" s="41">
@@ -8385,181 +8506,245 @@
         <f>IF(K32&gt;0,(M32+N32+O32+P32-K32)/K32,"—")</f>
         <v/>
       </c>
+      <c r="R32" s="41">
+        <f>'Юнитка FBO'!B34</f>
+        <v/>
+      </c>
+      <c r="S32" s="43">
+        <f>IF(D32*$B$7&gt;0,R32/(D32*$B$7),"—")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
+      <c r="A33" s="40">
+        <f>'Юнитка FBO'!A35</f>
+        <v/>
+      </c>
+      <c r="B33" s="41">
+        <f>'Юнитка FBO'!C35</f>
+        <v/>
+      </c>
+      <c r="C33" s="41">
+        <f>B33*$B$2</f>
+        <v/>
+      </c>
+      <c r="D33" s="41">
+        <f>'Юнитка FBO'!E35</f>
+        <v/>
+      </c>
+      <c r="E33" s="41">
+        <f>ROUND(D33*$B$3,0)</f>
+        <v/>
+      </c>
+      <c r="F33" s="41">
+        <f>'Юнитка FBO'!I35</f>
+        <v/>
+      </c>
+      <c r="G33" s="41">
+        <f>'Юнитка FBO'!K35+'Юнитка FBO'!N35+'Юнитка FBO'!O35+'Юнитка FBO'!P35+'Юнитка FBO'!Q35+'Юнитка FBO'!R35+'Юнитка FBO'!S35+'Юнитка FBO'!V35+'Юнитка FBO'!X35+'Юнитка FBO'!Y35+'Юнитка FBO'!AK35</f>
+        <v/>
+      </c>
+      <c r="H33" s="41">
+        <f>'Юнитка FBO'!G35-'Юнитка FBO'!I35</f>
+        <v/>
+      </c>
+      <c r="I33" s="41">
+        <f>MAX(0,G33-H33)+$B$4</f>
+        <v/>
+      </c>
+      <c r="J33" s="41">
+        <f>E33*I33</f>
+        <v/>
+      </c>
+      <c r="K33" s="41">
+        <f>C33+J33</f>
+        <v/>
+      </c>
+      <c r="L33" s="41">
+        <f>'Юнитка FBO'!AG35</f>
+        <v/>
+      </c>
+      <c r="M33" s="41">
+        <f>D33*L33*($B$5+0*$B$6)</f>
+        <v/>
+      </c>
+      <c r="N33" s="41">
+        <f>D33*L33*($B$5+1*$B$6)</f>
+        <v/>
+      </c>
+      <c r="O33" s="41">
+        <f>D33*L33*($B$5+2*$B$6)</f>
+        <v/>
+      </c>
+      <c r="P33" s="41">
+        <f>D33*L33*($B$5+3*$B$6)</f>
+        <v/>
+      </c>
+      <c r="Q33" s="42">
+        <f>IF(K33&gt;0,(M33+N33+O33+P33-K33)/K33,"—")</f>
+        <v/>
+      </c>
+      <c r="R33" s="41">
+        <f>'Юнитка FBO'!B35</f>
+        <v/>
+      </c>
+      <c r="S33" s="43">
+        <f>IF(D33*$B$7&gt;0,R33/(D33*$B$7),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="44" t="inlineStr">
         <is>
           <t>ИТОГО</t>
         </is>
       </c>
-      <c r="B33" s="44">
-        <f>SUM(B10:B32)</f>
-        <v/>
-      </c>
-      <c r="C33" s="44">
-        <f>SUM(C10:C32)</f>
-        <v/>
-      </c>
-      <c r="D33" s="44">
-        <f>SUM(D10:D32)</f>
-        <v/>
-      </c>
-      <c r="E33" s="44">
-        <f>SUM(E10:E32)</f>
-        <v/>
-      </c>
-      <c r="F33" s="43" t="n"/>
-      <c r="G33" s="43" t="n"/>
-      <c r="H33" s="43" t="n"/>
-      <c r="I33" s="43" t="n"/>
-      <c r="J33" s="44">
-        <f>SUM(J10:J32)</f>
-        <v/>
-      </c>
-      <c r="K33" s="44">
-        <f>SUM(K10:K32)</f>
-        <v/>
-      </c>
-      <c r="L33" s="43" t="n"/>
-      <c r="M33" s="44">
-        <f>SUM(M10:M32)</f>
-        <v/>
-      </c>
-      <c r="N33" s="44">
-        <f>SUM(N10:N32)</f>
-        <v/>
-      </c>
-      <c r="O33" s="44">
-        <f>SUM(O10:O32)</f>
-        <v/>
-      </c>
-      <c r="P33" s="44">
-        <f>SUM(P10:P32)</f>
-        <v/>
-      </c>
-      <c r="Q33" s="45">
-        <f>IF(K33&gt;0,(M33+N33+O33+P33-K33)/K33,"—")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="46" t="inlineStr">
+      <c r="B34" s="45">
+        <f>SUM(B11:B33)</f>
+        <v/>
+      </c>
+      <c r="C34" s="45">
+        <f>SUM(C11:C33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="45">
+        <f>SUM(D11:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="45">
+        <f>SUM(E11:E33)</f>
+        <v/>
+      </c>
+      <c r="F34" s="44" t="n"/>
+      <c r="G34" s="44" t="n"/>
+      <c r="H34" s="44" t="n"/>
+      <c r="I34" s="44" t="n"/>
+      <c r="J34" s="45">
+        <f>SUM(J11:J33)</f>
+        <v/>
+      </c>
+      <c r="K34" s="45">
+        <f>SUM(K11:K33)</f>
+        <v/>
+      </c>
+      <c r="L34" s="44" t="n"/>
+      <c r="M34" s="45">
+        <f>SUM(M11:M33)</f>
+        <v/>
+      </c>
+      <c r="N34" s="45">
+        <f>SUM(N11:N33)</f>
+        <v/>
+      </c>
+      <c r="O34" s="45">
+        <f>SUM(O11:O33)</f>
+        <v/>
+      </c>
+      <c r="P34" s="45">
+        <f>SUM(P11:P33)</f>
+        <v/>
+      </c>
+      <c r="Q34" s="46">
+        <f>IF(K34&gt;0,(M34+N34+O34+P34-K34)/K34,"—")</f>
+        <v/>
+      </c>
+      <c r="R34" s="45">
+        <f>SUM(R11:R33)</f>
+        <v/>
+      </c>
+      <c r="S34" s="47">
+        <f>IF(D34*$B$7&gt;0,R34/(D34*$B$7),"—")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
         <is>
           <t>План по месяцам: раскрутка + выход на продажи (доля от конкурента растёт на +10 п.п./мес)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="32" customHeight="1">
-      <c r="A37" s="38" t="inlineStr">
+    <row r="38" ht="32" customHeight="1">
+      <c r="A38" s="38" t="inlineStr">
         <is>
           <t>Месяц</t>
         </is>
       </c>
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B38" s="38" t="inlineStr">
         <is>
           <t>Доля от продаж конкурента</t>
         </is>
       </c>
-      <c r="C37" s="38" t="inlineStr">
+      <c r="C38" s="38" t="inlineStr">
         <is>
           <t>Продаж, шт</t>
         </is>
       </c>
-      <c r="D37" s="38" t="inlineStr">
+      <c r="D38" s="38" t="inlineStr">
         <is>
           <t>Прибыль от продаж, ₽</t>
         </is>
       </c>
-      <c r="E37" s="38" t="inlineStr">
+      <c r="E38" s="38" t="inlineStr">
         <is>
           <t>Расходы (накрутка), ₽</t>
         </is>
       </c>
-      <c r="F37" s="38" t="inlineStr">
+      <c r="F38" s="38" t="inlineStr">
         <is>
           <t>Чистый поток, ₽</t>
         </is>
       </c>
-      <c r="G37" s="38" t="inlineStr">
+      <c r="G38" s="38" t="inlineStr">
         <is>
           <t>Накопительно, ₽</t>
         </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="40" t="inlineStr">
-        <is>
-          <t>Август (раскрутка)</t>
-        </is>
-      </c>
-      <c r="B38" s="42" t="n">
-        <v>0</v>
-      </c>
-      <c r="C38" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="41">
-        <f>$K$33</f>
-        <v/>
-      </c>
-      <c r="F38" s="41">
-        <f>D38-E38</f>
-        <v/>
-      </c>
-      <c r="G38" s="41">
-        <f>F38</f>
-        <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="40" t="inlineStr">
         <is>
-          <t>Сентябрь</t>
-        </is>
-      </c>
-      <c r="B39" s="42">
-        <f>$B$5+0*$B$6</f>
-        <v/>
-      </c>
-      <c r="C39" s="41">
-        <f>ROUND(B39*$D$33,0)</f>
-        <v/>
-      </c>
-      <c r="D39" s="41">
-        <f>M33</f>
-        <v/>
-      </c>
-      <c r="E39" s="41" t="n">
+          <t>Август (раскрутка)</t>
+        </is>
+      </c>
+      <c r="B39" s="42" t="n">
         <v>0</v>
+      </c>
+      <c r="C39" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="41">
+        <f>$K$34</f>
+        <v/>
       </c>
       <c r="F39" s="41">
         <f>D39-E39</f>
         <v/>
       </c>
       <c r="G39" s="41">
-        <f>G38+F39</f>
+        <f>F39</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="40" t="inlineStr">
         <is>
-          <t>Октябрь</t>
+          <t>Сентябрь</t>
         </is>
       </c>
       <c r="B40" s="42">
-        <f>$B$5+1*$B$6</f>
+        <f>$B$5+0*$B$6</f>
         <v/>
       </c>
       <c r="C40" s="41">
-        <f>ROUND(B40*$D$33,0)</f>
+        <f>ROUND(B40*$D$34,0)</f>
         <v/>
       </c>
       <c r="D40" s="41">
-        <f>N33</f>
+        <f>M34</f>
         <v/>
       </c>
       <c r="E40" s="41" t="n">
@@ -8577,19 +8762,19 @@
     <row r="41">
       <c r="A41" s="40" t="inlineStr">
         <is>
-          <t>Ноябрь</t>
+          <t>Октябрь</t>
         </is>
       </c>
       <c r="B41" s="42">
-        <f>$B$5+2*$B$6</f>
+        <f>$B$5+1*$B$6</f>
         <v/>
       </c>
       <c r="C41" s="41">
-        <f>ROUND(B41*$D$33,0)</f>
+        <f>ROUND(B41*$D$34,0)</f>
         <v/>
       </c>
       <c r="D41" s="41">
-        <f>O33</f>
+        <f>N34</f>
         <v/>
       </c>
       <c r="E41" s="41" t="n">
@@ -8607,19 +8792,19 @@
     <row r="42">
       <c r="A42" s="40" t="inlineStr">
         <is>
-          <t>Декабрь</t>
+          <t>Ноябрь</t>
         </is>
       </c>
       <c r="B42" s="42">
-        <f>$B$5+3*$B$6</f>
+        <f>$B$5+2*$B$6</f>
         <v/>
       </c>
       <c r="C42" s="41">
-        <f>ROUND(B42*$D$33,0)</f>
+        <f>ROUND(B42*$D$34,0)</f>
         <v/>
       </c>
       <c r="D42" s="41">
-        <f>P33</f>
+        <f>O34</f>
         <v/>
       </c>
       <c r="E42" s="41" t="n">
@@ -8635,79 +8820,109 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="43" t="inlineStr">
+      <c r="A43" s="40" t="inlineStr">
+        <is>
+          <t>Декабрь</t>
+        </is>
+      </c>
+      <c r="B43" s="42">
+        <f>$B$5+3*$B$6</f>
+        <v/>
+      </c>
+      <c r="C43" s="41">
+        <f>ROUND(B43*$D$34,0)</f>
+        <v/>
+      </c>
+      <c r="D43" s="41">
+        <f>P34</f>
+        <v/>
+      </c>
+      <c r="E43" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="41">
+        <f>D43-E43</f>
+        <v/>
+      </c>
+      <c r="G43" s="41">
+        <f>G42+F43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="44" t="inlineStr">
         <is>
           <t>Итого за период</t>
         </is>
       </c>
-      <c r="B43" s="43" t="n"/>
-      <c r="C43" s="44">
-        <f>SUM(C38:C42)</f>
-        <v/>
-      </c>
-      <c r="D43" s="44">
-        <f>SUM(D38:D42)</f>
-        <v/>
-      </c>
-      <c r="E43" s="44">
-        <f>SUM(E38:E42)</f>
-        <v/>
-      </c>
-      <c r="F43" s="44">
-        <f>SUM(F38:F42)</f>
-        <v/>
-      </c>
-      <c r="G43" s="44">
-        <f>G42</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="34" t="inlineStr">
-        <is>
-          <t>Разовые расходы на раскрутку (август), ₽</t>
-        </is>
-      </c>
-      <c r="B45" s="44">
-        <f>$K$33</f>
+      <c r="B44" s="44" t="n"/>
+      <c r="C44" s="45">
+        <f>SUM(C39:C43)</f>
+        <v/>
+      </c>
+      <c r="D44" s="45">
+        <f>SUM(D39:D43)</f>
+        <v/>
+      </c>
+      <c r="E44" s="45">
+        <f>SUM(E39:E43)</f>
+        <v/>
+      </c>
+      <c r="F44" s="45">
+        <f>SUM(F39:F43)</f>
+        <v/>
+      </c>
+      <c r="G44" s="45">
+        <f>G43</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="34" t="inlineStr">
         <is>
-          <t>Прибыль при 100% продаж конкурента, ₽/мес</t>
-        </is>
-      </c>
-      <c r="B46" s="44">
-        <f>SUMPRODUCT(D10:D32,L10:L32)</f>
+          <t>Разовые расходы на раскрутку (август), ₽</t>
+        </is>
+      </c>
+      <c r="B46" s="45">
+        <f>$K$34</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="34" t="inlineStr">
         <is>
-          <t>Накопительный поток к декабрю, ₽</t>
-        </is>
-      </c>
-      <c r="B47" s="44">
-        <f>G42</f>
+          <t>Прибыль при 100% продаж конкурента, ₽/мес</t>
+        </is>
+      </c>
+      <c r="B47" s="45">
+        <f>SUMPRODUCT(D11:D33,L11:L33)</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="34" t="inlineStr">
         <is>
+          <t>Накопительный поток к декабрю, ₽</t>
+        </is>
+      </c>
+      <c r="B48" s="45">
+        <f>G43</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="34" t="inlineStr">
+        <is>
           <t>Окупаемость раскрутки, мес продаж (при 100%)</t>
         </is>
       </c>
-      <c r="B48" s="47">
-        <f>IF(SUMPRODUCT(D10:D32,L10:L32)&gt;0,$K$33/SUMPRODUCT(D10:D32,L10:L32),"—")</f>
+      <c r="B49" s="47">
+        <f>IF(SUMPRODUCT(D11:D33,L11:L33)&gt;0,$K$34/SUMPRODUCT(D11:D33,L11:L33),"—")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="Q10:Q33">
+  <conditionalFormatting sqref="Q11:Q34">
     <cfRule type="cellIs" priority="1" operator="lessThan" dxfId="0">
       <formula>0</formula>
     </cfRule>
